--- a/data/Recognitions_latest.xlsx
+++ b/data/Recognitions_latest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30524"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aphrcorg-my.sharepoint.com/personal/nnjenga_aphrc_org/Documents/CARTA Dashboard/ECRS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="728" documentId="13_ncr:1_{74C5384D-9D49-4106-BD43-FCAED859190D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DC68D8B-E9A3-4D4A-9D45-1A631DB02DDA}"/>
+  <xr:revisionPtr revIDLastSave="746" documentId="13_ncr:1_{74C5384D-9D49-4106-BD43-FCAED859190D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4810BA06-6DCB-4B0B-9070-65E5FDBD30E7}"/>
   <bookViews>
     <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,10 +24,10 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="12" r:id="rId6"/>
-    <pivotCache cacheId="13" r:id="rId7"/>
-    <pivotCache cacheId="14" r:id="rId8"/>
-    <pivotCache cacheId="15" r:id="rId9"/>
+    <pivotCache cacheId="330" r:id="rId6"/>
+    <pivotCache cacheId="331" r:id="rId7"/>
+    <pivotCache cacheId="332" r:id="rId8"/>
+    <pivotCache cacheId="333" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -121,7 +121,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3064" uniqueCount="806">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3080" uniqueCount="808">
   <si>
     <t>No</t>
   </si>
@@ -2514,6 +2514,12 @@
   </si>
   <si>
     <t>Promoted from Senior Lecturer</t>
+  </si>
+  <si>
+    <t>Appointed as a Subject Matter Expert on the Manuscript Technical Evaluators team of the Uganda Textbook Academic and Non-Fiction Authors Association (UTANA) on August 31, 2026</t>
+  </si>
+  <si>
+    <t>Appointed Extraordinary Research Fellow at the Africa Center for Inclusive Health Management at Stellenbosch University, South Africa, from July 1, 2026, to June 30, 2029. I</t>
   </si>
   <si>
     <t>(All)</t>
@@ -3090,6 +3096,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
       <x14:pivotCacheDefinition/>
     </ext>
+    <ext xmlns:xlpdsc="http://schemas.microsoft.com/office/spreadsheetml/2026/pivotDataSourceClean" uri="{F4336242-56EE-4DD3-A5F7-E900642BF6E9}">
+      <xlpdsc:dataSourceClean>1</xlpdsc:dataSourceClean>
+    </ext>
   </extLst>
 </pivotCacheDefinition>
 </file>
@@ -3576,6 +3585,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
       <x14:pivotCacheDefinition/>
     </ext>
+    <ext xmlns:xlpdsc="http://schemas.microsoft.com/office/spreadsheetml/2026/pivotDataSourceClean" uri="{F4336242-56EE-4DD3-A5F7-E900642BF6E9}">
+      <xlpdsc:dataSourceClean>1</xlpdsc:dataSourceClean>
+    </ext>
   </extLst>
 </pivotCacheDefinition>
 </file>
@@ -3867,6 +3879,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
       <x14:pivotCacheDefinition/>
+    </ext>
+    <ext xmlns:xlpdsc="http://schemas.microsoft.com/office/spreadsheetml/2026/pivotDataSourceClean" uri="{F4336242-56EE-4DD3-A5F7-E900642BF6E9}">
+      <xlpdsc:dataSourceClean>1</xlpdsc:dataSourceClean>
     </ext>
   </extLst>
 </pivotCacheDefinition>
@@ -4235,6 +4250,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
       <x14:pivotCacheDefinition/>
     </ext>
+    <ext xmlns:xlpdsc="http://schemas.microsoft.com/office/spreadsheetml/2026/pivotDataSourceClean" uri="{F4336242-56EE-4DD3-A5F7-E900642BF6E9}">
+      <xlpdsc:dataSourceClean>1</xlpdsc:dataSourceClean>
+    </ext>
   </extLst>
 </pivotCacheDefinition>
 </file>
@@ -26954,7 +26972,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{55E369D5-46AA-45F8-B4A0-AC6C0CED6464}" name="PivotTable2" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{55E369D5-46AA-45F8-B4A0-AC6C0CED6464}" name="PivotTable2" cacheId="330" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:D9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="16">
     <pivotField dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -27053,7 +27071,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{414D3242-6D58-4EC3-BE1F-E4596803BECC}" name="PivotTable10" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{414D3242-6D58-4EC3-BE1F-E4596803BECC}" name="PivotTable10" cacheId="330" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A16:H19" firstHeaderRow="1" firstDataRow="3" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="16">
     <pivotField dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -27196,715 +27214,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{90770DB3-F829-4E9E-88FA-FB5C22EB6463}" name="PivotTable2" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="D4:E146" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="18">
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="142">
-        <item x="57"/>
-        <item x="116"/>
-        <item x="10"/>
-        <item x="27"/>
-        <item x="88"/>
-        <item x="19"/>
-        <item x="14"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="125"/>
-        <item x="128"/>
-        <item x="121"/>
-        <item x="41"/>
-        <item x="80"/>
-        <item x="93"/>
-        <item x="81"/>
-        <item x="111"/>
-        <item x="82"/>
-        <item x="49"/>
-        <item x="48"/>
-        <item x="68"/>
-        <item x="107"/>
-        <item x="83"/>
-        <item x="42"/>
-        <item x="97"/>
-        <item x="5"/>
-        <item x="11"/>
-        <item x="8"/>
-        <item x="35"/>
-        <item x="25"/>
-        <item x="99"/>
-        <item x="32"/>
-        <item x="22"/>
-        <item x="9"/>
-        <item x="13"/>
-        <item x="126"/>
-        <item x="54"/>
-        <item x="28"/>
-        <item x="53"/>
-        <item x="21"/>
-        <item x="84"/>
-        <item x="20"/>
-        <item x="12"/>
-        <item x="1"/>
-        <item x="86"/>
-        <item x="102"/>
-        <item x="127"/>
-        <item x="30"/>
-        <item x="43"/>
-        <item x="85"/>
-        <item x="112"/>
-        <item x="62"/>
-        <item x="50"/>
-        <item x="98"/>
-        <item x="36"/>
-        <item x="106"/>
-        <item x="17"/>
-        <item x="6"/>
-        <item x="122"/>
-        <item x="52"/>
-        <item x="104"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="18"/>
-        <item x="26"/>
-        <item x="103"/>
-        <item x="31"/>
-        <item x="89"/>
-        <item x="118"/>
-        <item x="2"/>
-        <item x="16"/>
-        <item x="55"/>
-        <item x="58"/>
-        <item x="114"/>
-        <item x="33"/>
-        <item x="87"/>
-        <item x="113"/>
-        <item x="69"/>
-        <item x="51"/>
-        <item x="59"/>
-        <item x="101"/>
-        <item x="34"/>
-        <item x="109"/>
-        <item x="61"/>
-        <item x="132"/>
-        <item x="56"/>
-        <item x="64"/>
-        <item x="117"/>
-        <item x="63"/>
-        <item x="100"/>
-        <item x="124"/>
-        <item x="108"/>
-        <item x="115"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="4"/>
-        <item x="15"/>
-        <item x="65"/>
-        <item x="44"/>
-        <item x="119"/>
-        <item x="105"/>
-        <item x="66"/>
-        <item x="120"/>
-        <item x="123"/>
-        <item x="45"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="39"/>
-        <item x="73"/>
-        <item x="110"/>
-        <item x="46"/>
-        <item x="94"/>
-        <item x="74"/>
-        <item x="29"/>
-        <item x="75"/>
-        <item x="90"/>
-        <item x="67"/>
-        <item x="76"/>
-        <item x="38"/>
-        <item x="91"/>
-        <item x="37"/>
-        <item x="40"/>
-        <item x="60"/>
-        <item x="95"/>
-        <item x="77"/>
-        <item x="47"/>
-        <item x="78"/>
-        <item x="131"/>
-        <item x="96"/>
-        <item x="92"/>
-        <item x="79"/>
-        <item x="0"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
-      <items count="12">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="9"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="1"/>
-        <item x="10"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisPage" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="69">
-        <item x="57"/>
-        <item x="56"/>
-        <item x="55"/>
-        <item x="39"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="43"/>
-        <item x="20"/>
-        <item x="35"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="50"/>
-        <item x="23"/>
-        <item x="16"/>
-        <item x="52"/>
-        <item x="30"/>
-        <item x="12"/>
-        <item x="24"/>
-        <item x="63"/>
-        <item x="31"/>
-        <item x="17"/>
-        <item x="28"/>
-        <item x="37"/>
-        <item x="48"/>
-        <item x="13"/>
-        <item x="32"/>
-        <item x="51"/>
-        <item x="22"/>
-        <item x="36"/>
-        <item x="54"/>
-        <item x="49"/>
-        <item x="18"/>
-        <item x="53"/>
-        <item x="19"/>
-        <item x="26"/>
-        <item x="45"/>
-        <item x="64"/>
-        <item x="42"/>
-        <item x="62"/>
-        <item x="29"/>
-        <item x="38"/>
-        <item x="15"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="44"/>
-        <item x="21"/>
-        <item x="25"/>
-        <item x="27"/>
-        <item x="41"/>
-        <item x="61"/>
-        <item x="58"/>
-        <item x="60"/>
-        <item x="6"/>
-        <item x="9"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="11"/>
-        <item x="10"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="40"/>
-        <item x="1"/>
-        <item x="14"/>
-        <item x="59"/>
-        <item x="0"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="142">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="19"/>
-    </i>
-    <i>
-      <x v="20"/>
-    </i>
-    <i>
-      <x v="21"/>
-    </i>
-    <i>
-      <x v="22"/>
-    </i>
-    <i>
-      <x v="23"/>
-    </i>
-    <i>
-      <x v="24"/>
-    </i>
-    <i>
-      <x v="25"/>
-    </i>
-    <i>
-      <x v="26"/>
-    </i>
-    <i>
-      <x v="27"/>
-    </i>
-    <i>
-      <x v="28"/>
-    </i>
-    <i>
-      <x v="29"/>
-    </i>
-    <i>
-      <x v="30"/>
-    </i>
-    <i>
-      <x v="31"/>
-    </i>
-    <i>
-      <x v="32"/>
-    </i>
-    <i>
-      <x v="33"/>
-    </i>
-    <i>
-      <x v="34"/>
-    </i>
-    <i>
-      <x v="35"/>
-    </i>
-    <i>
-      <x v="36"/>
-    </i>
-    <i>
-      <x v="37"/>
-    </i>
-    <i>
-      <x v="38"/>
-    </i>
-    <i>
-      <x v="39"/>
-    </i>
-    <i>
-      <x v="40"/>
-    </i>
-    <i>
-      <x v="41"/>
-    </i>
-    <i>
-      <x v="42"/>
-    </i>
-    <i>
-      <x v="43"/>
-    </i>
-    <i>
-      <x v="44"/>
-    </i>
-    <i>
-      <x v="45"/>
-    </i>
-    <i>
-      <x v="46"/>
-    </i>
-    <i>
-      <x v="47"/>
-    </i>
-    <i>
-      <x v="48"/>
-    </i>
-    <i>
-      <x v="49"/>
-    </i>
-    <i>
-      <x v="50"/>
-    </i>
-    <i>
-      <x v="51"/>
-    </i>
-    <i>
-      <x v="52"/>
-    </i>
-    <i>
-      <x v="53"/>
-    </i>
-    <i>
-      <x v="54"/>
-    </i>
-    <i>
-      <x v="55"/>
-    </i>
-    <i>
-      <x v="56"/>
-    </i>
-    <i>
-      <x v="57"/>
-    </i>
-    <i>
-      <x v="58"/>
-    </i>
-    <i>
-      <x v="59"/>
-    </i>
-    <i>
-      <x v="60"/>
-    </i>
-    <i>
-      <x v="61"/>
-    </i>
-    <i>
-      <x v="62"/>
-    </i>
-    <i>
-      <x v="63"/>
-    </i>
-    <i>
-      <x v="64"/>
-    </i>
-    <i>
-      <x v="65"/>
-    </i>
-    <i>
-      <x v="66"/>
-    </i>
-    <i>
-      <x v="67"/>
-    </i>
-    <i>
-      <x v="68"/>
-    </i>
-    <i>
-      <x v="69"/>
-    </i>
-    <i>
-      <x v="70"/>
-    </i>
-    <i>
-      <x v="71"/>
-    </i>
-    <i>
-      <x v="72"/>
-    </i>
-    <i>
-      <x v="73"/>
-    </i>
-    <i>
-      <x v="74"/>
-    </i>
-    <i>
-      <x v="75"/>
-    </i>
-    <i>
-      <x v="76"/>
-    </i>
-    <i>
-      <x v="77"/>
-    </i>
-    <i>
-      <x v="78"/>
-    </i>
-    <i>
-      <x v="79"/>
-    </i>
-    <i>
-      <x v="80"/>
-    </i>
-    <i>
-      <x v="81"/>
-    </i>
-    <i>
-      <x v="82"/>
-    </i>
-    <i>
-      <x v="83"/>
-    </i>
-    <i>
-      <x v="84"/>
-    </i>
-    <i>
-      <x v="85"/>
-    </i>
-    <i>
-      <x v="86"/>
-    </i>
-    <i>
-      <x v="87"/>
-    </i>
-    <i>
-      <x v="88"/>
-    </i>
-    <i>
-      <x v="89"/>
-    </i>
-    <i>
-      <x v="90"/>
-    </i>
-    <i>
-      <x v="91"/>
-    </i>
-    <i>
-      <x v="92"/>
-    </i>
-    <i>
-      <x v="93"/>
-    </i>
-    <i>
-      <x v="94"/>
-    </i>
-    <i>
-      <x v="95"/>
-    </i>
-    <i>
-      <x v="96"/>
-    </i>
-    <i>
-      <x v="97"/>
-    </i>
-    <i>
-      <x v="98"/>
-    </i>
-    <i>
-      <x v="99"/>
-    </i>
-    <i>
-      <x v="100"/>
-    </i>
-    <i>
-      <x v="101"/>
-    </i>
-    <i>
-      <x v="102"/>
-    </i>
-    <i>
-      <x v="103"/>
-    </i>
-    <i>
-      <x v="104"/>
-    </i>
-    <i>
-      <x v="105"/>
-    </i>
-    <i>
-      <x v="106"/>
-    </i>
-    <i>
-      <x v="107"/>
-    </i>
-    <i>
-      <x v="108"/>
-    </i>
-    <i>
-      <x v="109"/>
-    </i>
-    <i>
-      <x v="110"/>
-    </i>
-    <i>
-      <x v="111"/>
-    </i>
-    <i>
-      <x v="112"/>
-    </i>
-    <i>
-      <x v="113"/>
-    </i>
-    <i>
-      <x v="114"/>
-    </i>
-    <i>
-      <x v="115"/>
-    </i>
-    <i>
-      <x v="116"/>
-    </i>
-    <i>
-      <x v="117"/>
-    </i>
-    <i>
-      <x v="118"/>
-    </i>
-    <i>
-      <x v="119"/>
-    </i>
-    <i>
-      <x v="120"/>
-    </i>
-    <i>
-      <x v="121"/>
-    </i>
-    <i>
-      <x v="122"/>
-    </i>
-    <i>
-      <x v="123"/>
-    </i>
-    <i>
-      <x v="124"/>
-    </i>
-    <i>
-      <x v="125"/>
-    </i>
-    <i>
-      <x v="126"/>
-    </i>
-    <i>
-      <x v="127"/>
-    </i>
-    <i>
-      <x v="128"/>
-    </i>
-    <i>
-      <x v="129"/>
-    </i>
-    <i>
-      <x v="130"/>
-    </i>
-    <i>
-      <x v="131"/>
-    </i>
-    <i>
-      <x v="132"/>
-    </i>
-    <i>
-      <x v="133"/>
-    </i>
-    <i>
-      <x v="134"/>
-    </i>
-    <i>
-      <x v="135"/>
-    </i>
-    <i>
-      <x v="136"/>
-    </i>
-    <i>
-      <x v="137"/>
-    </i>
-    <i>
-      <x v="138"/>
-    </i>
-    <i>
-      <x v="139"/>
-    </i>
-    <i>
-      <x v="140"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="11" hier="-1"/>
-    <pageField fld="9" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Count of Promotion" fld="11" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C759C715-A218-40D6-B8AD-8DD0CC6815DF}" name="PivotTable1" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C759C715-A218-40D6-B8AD-8DD0CC6815DF}" name="PivotTable1" cacheId="333" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:B146" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="18">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -28686,8 +27996,1021 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{90770DB3-F829-4E9E-88FA-FB5C22EB6463}" name="PivotTable2" cacheId="332" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="D4:E146" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="18">
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="142">
+        <item x="57"/>
+        <item x="116"/>
+        <item x="10"/>
+        <item x="27"/>
+        <item x="88"/>
+        <item x="19"/>
+        <item x="14"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="125"/>
+        <item x="128"/>
+        <item x="121"/>
+        <item x="41"/>
+        <item x="80"/>
+        <item x="93"/>
+        <item x="81"/>
+        <item x="111"/>
+        <item x="82"/>
+        <item x="49"/>
+        <item x="48"/>
+        <item x="68"/>
+        <item x="107"/>
+        <item x="83"/>
+        <item x="42"/>
+        <item x="97"/>
+        <item x="5"/>
+        <item x="11"/>
+        <item x="8"/>
+        <item x="35"/>
+        <item x="25"/>
+        <item x="99"/>
+        <item x="32"/>
+        <item x="22"/>
+        <item x="9"/>
+        <item x="13"/>
+        <item x="126"/>
+        <item x="54"/>
+        <item x="28"/>
+        <item x="53"/>
+        <item x="21"/>
+        <item x="84"/>
+        <item x="20"/>
+        <item x="12"/>
+        <item x="1"/>
+        <item x="86"/>
+        <item x="102"/>
+        <item x="127"/>
+        <item x="30"/>
+        <item x="43"/>
+        <item x="85"/>
+        <item x="112"/>
+        <item x="62"/>
+        <item x="50"/>
+        <item x="98"/>
+        <item x="36"/>
+        <item x="106"/>
+        <item x="17"/>
+        <item x="6"/>
+        <item x="122"/>
+        <item x="52"/>
+        <item x="104"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="18"/>
+        <item x="26"/>
+        <item x="103"/>
+        <item x="31"/>
+        <item x="89"/>
+        <item x="118"/>
+        <item x="2"/>
+        <item x="16"/>
+        <item x="55"/>
+        <item x="58"/>
+        <item x="114"/>
+        <item x="33"/>
+        <item x="87"/>
+        <item x="113"/>
+        <item x="69"/>
+        <item x="51"/>
+        <item x="59"/>
+        <item x="101"/>
+        <item x="34"/>
+        <item x="109"/>
+        <item x="61"/>
+        <item x="132"/>
+        <item x="56"/>
+        <item x="64"/>
+        <item x="117"/>
+        <item x="63"/>
+        <item x="100"/>
+        <item x="124"/>
+        <item x="108"/>
+        <item x="115"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="4"/>
+        <item x="15"/>
+        <item x="65"/>
+        <item x="44"/>
+        <item x="119"/>
+        <item x="105"/>
+        <item x="66"/>
+        <item x="120"/>
+        <item x="123"/>
+        <item x="45"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="39"/>
+        <item x="73"/>
+        <item x="110"/>
+        <item x="46"/>
+        <item x="94"/>
+        <item x="74"/>
+        <item x="29"/>
+        <item x="75"/>
+        <item x="90"/>
+        <item x="67"/>
+        <item x="76"/>
+        <item x="38"/>
+        <item x="91"/>
+        <item x="37"/>
+        <item x="40"/>
+        <item x="60"/>
+        <item x="95"/>
+        <item x="77"/>
+        <item x="47"/>
+        <item x="78"/>
+        <item x="131"/>
+        <item x="96"/>
+        <item x="92"/>
+        <item x="79"/>
+        <item x="0"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
+      <items count="12">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="1"/>
+        <item x="10"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="69">
+        <item x="57"/>
+        <item x="56"/>
+        <item x="55"/>
+        <item x="39"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="43"/>
+        <item x="20"/>
+        <item x="35"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="50"/>
+        <item x="23"/>
+        <item x="16"/>
+        <item x="52"/>
+        <item x="30"/>
+        <item x="12"/>
+        <item x="24"/>
+        <item x="63"/>
+        <item x="31"/>
+        <item x="17"/>
+        <item x="28"/>
+        <item x="37"/>
+        <item x="48"/>
+        <item x="13"/>
+        <item x="32"/>
+        <item x="51"/>
+        <item x="22"/>
+        <item x="36"/>
+        <item x="54"/>
+        <item x="49"/>
+        <item x="18"/>
+        <item x="53"/>
+        <item x="19"/>
+        <item x="26"/>
+        <item x="45"/>
+        <item x="64"/>
+        <item x="42"/>
+        <item x="62"/>
+        <item x="29"/>
+        <item x="38"/>
+        <item x="15"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="44"/>
+        <item x="21"/>
+        <item x="25"/>
+        <item x="27"/>
+        <item x="41"/>
+        <item x="61"/>
+        <item x="58"/>
+        <item x="60"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="40"/>
+        <item x="1"/>
+        <item x="14"/>
+        <item x="59"/>
+        <item x="0"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="142">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="26"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="29"/>
+    </i>
+    <i>
+      <x v="30"/>
+    </i>
+    <i>
+      <x v="31"/>
+    </i>
+    <i>
+      <x v="32"/>
+    </i>
+    <i>
+      <x v="33"/>
+    </i>
+    <i>
+      <x v="34"/>
+    </i>
+    <i>
+      <x v="35"/>
+    </i>
+    <i>
+      <x v="36"/>
+    </i>
+    <i>
+      <x v="37"/>
+    </i>
+    <i>
+      <x v="38"/>
+    </i>
+    <i>
+      <x v="39"/>
+    </i>
+    <i>
+      <x v="40"/>
+    </i>
+    <i>
+      <x v="41"/>
+    </i>
+    <i>
+      <x v="42"/>
+    </i>
+    <i>
+      <x v="43"/>
+    </i>
+    <i>
+      <x v="44"/>
+    </i>
+    <i>
+      <x v="45"/>
+    </i>
+    <i>
+      <x v="46"/>
+    </i>
+    <i>
+      <x v="47"/>
+    </i>
+    <i>
+      <x v="48"/>
+    </i>
+    <i>
+      <x v="49"/>
+    </i>
+    <i>
+      <x v="50"/>
+    </i>
+    <i>
+      <x v="51"/>
+    </i>
+    <i>
+      <x v="52"/>
+    </i>
+    <i>
+      <x v="53"/>
+    </i>
+    <i>
+      <x v="54"/>
+    </i>
+    <i>
+      <x v="55"/>
+    </i>
+    <i>
+      <x v="56"/>
+    </i>
+    <i>
+      <x v="57"/>
+    </i>
+    <i>
+      <x v="58"/>
+    </i>
+    <i>
+      <x v="59"/>
+    </i>
+    <i>
+      <x v="60"/>
+    </i>
+    <i>
+      <x v="61"/>
+    </i>
+    <i>
+      <x v="62"/>
+    </i>
+    <i>
+      <x v="63"/>
+    </i>
+    <i>
+      <x v="64"/>
+    </i>
+    <i>
+      <x v="65"/>
+    </i>
+    <i>
+      <x v="66"/>
+    </i>
+    <i>
+      <x v="67"/>
+    </i>
+    <i>
+      <x v="68"/>
+    </i>
+    <i>
+      <x v="69"/>
+    </i>
+    <i>
+      <x v="70"/>
+    </i>
+    <i>
+      <x v="71"/>
+    </i>
+    <i>
+      <x v="72"/>
+    </i>
+    <i>
+      <x v="73"/>
+    </i>
+    <i>
+      <x v="74"/>
+    </i>
+    <i>
+      <x v="75"/>
+    </i>
+    <i>
+      <x v="76"/>
+    </i>
+    <i>
+      <x v="77"/>
+    </i>
+    <i>
+      <x v="78"/>
+    </i>
+    <i>
+      <x v="79"/>
+    </i>
+    <i>
+      <x v="80"/>
+    </i>
+    <i>
+      <x v="81"/>
+    </i>
+    <i>
+      <x v="82"/>
+    </i>
+    <i>
+      <x v="83"/>
+    </i>
+    <i>
+      <x v="84"/>
+    </i>
+    <i>
+      <x v="85"/>
+    </i>
+    <i>
+      <x v="86"/>
+    </i>
+    <i>
+      <x v="87"/>
+    </i>
+    <i>
+      <x v="88"/>
+    </i>
+    <i>
+      <x v="89"/>
+    </i>
+    <i>
+      <x v="90"/>
+    </i>
+    <i>
+      <x v="91"/>
+    </i>
+    <i>
+      <x v="92"/>
+    </i>
+    <i>
+      <x v="93"/>
+    </i>
+    <i>
+      <x v="94"/>
+    </i>
+    <i>
+      <x v="95"/>
+    </i>
+    <i>
+      <x v="96"/>
+    </i>
+    <i>
+      <x v="97"/>
+    </i>
+    <i>
+      <x v="98"/>
+    </i>
+    <i>
+      <x v="99"/>
+    </i>
+    <i>
+      <x v="100"/>
+    </i>
+    <i>
+      <x v="101"/>
+    </i>
+    <i>
+      <x v="102"/>
+    </i>
+    <i>
+      <x v="103"/>
+    </i>
+    <i>
+      <x v="104"/>
+    </i>
+    <i>
+      <x v="105"/>
+    </i>
+    <i>
+      <x v="106"/>
+    </i>
+    <i>
+      <x v="107"/>
+    </i>
+    <i>
+      <x v="108"/>
+    </i>
+    <i>
+      <x v="109"/>
+    </i>
+    <i>
+      <x v="110"/>
+    </i>
+    <i>
+      <x v="111"/>
+    </i>
+    <i>
+      <x v="112"/>
+    </i>
+    <i>
+      <x v="113"/>
+    </i>
+    <i>
+      <x v="114"/>
+    </i>
+    <i>
+      <x v="115"/>
+    </i>
+    <i>
+      <x v="116"/>
+    </i>
+    <i>
+      <x v="117"/>
+    </i>
+    <i>
+      <x v="118"/>
+    </i>
+    <i>
+      <x v="119"/>
+    </i>
+    <i>
+      <x v="120"/>
+    </i>
+    <i>
+      <x v="121"/>
+    </i>
+    <i>
+      <x v="122"/>
+    </i>
+    <i>
+      <x v="123"/>
+    </i>
+    <i>
+      <x v="124"/>
+    </i>
+    <i>
+      <x v="125"/>
+    </i>
+    <i>
+      <x v="126"/>
+    </i>
+    <i>
+      <x v="127"/>
+    </i>
+    <i>
+      <x v="128"/>
+    </i>
+    <i>
+      <x v="129"/>
+    </i>
+    <i>
+      <x v="130"/>
+    </i>
+    <i>
+      <x v="131"/>
+    </i>
+    <i>
+      <x v="132"/>
+    </i>
+    <i>
+      <x v="133"/>
+    </i>
+    <i>
+      <x v="134"/>
+    </i>
+    <i>
+      <x v="135"/>
+    </i>
+    <i>
+      <x v="136"/>
+    </i>
+    <i>
+      <x v="137"/>
+    </i>
+    <i>
+      <x v="138"/>
+    </i>
+    <i>
+      <x v="139"/>
+    </i>
+    <i>
+      <x v="140"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="11" hier="-1"/>
+    <pageField fld="9" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Count of Promotion" fld="11" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FC177463-ECB6-493F-84C5-BD2B6B5E3667}" name="PivotTable1" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{166599A4-10FF-421A-AFB4-AE0C311C3DFB}" name="PivotTable2" cacheId="331" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="C3:D30" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="18">
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="134">
+        <item x="57"/>
+        <item x="116"/>
+        <item x="10"/>
+        <item x="27"/>
+        <item x="88"/>
+        <item x="19"/>
+        <item x="14"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="125"/>
+        <item x="128"/>
+        <item x="121"/>
+        <item x="41"/>
+        <item x="80"/>
+        <item x="93"/>
+        <item x="81"/>
+        <item x="111"/>
+        <item x="82"/>
+        <item x="49"/>
+        <item x="48"/>
+        <item x="68"/>
+        <item x="107"/>
+        <item x="83"/>
+        <item x="42"/>
+        <item x="97"/>
+        <item x="5"/>
+        <item x="11"/>
+        <item x="8"/>
+        <item x="35"/>
+        <item x="25"/>
+        <item x="99"/>
+        <item x="32"/>
+        <item x="22"/>
+        <item x="9"/>
+        <item x="13"/>
+        <item x="126"/>
+        <item x="54"/>
+        <item x="28"/>
+        <item x="53"/>
+        <item x="21"/>
+        <item x="84"/>
+        <item x="20"/>
+        <item x="12"/>
+        <item x="1"/>
+        <item x="86"/>
+        <item x="102"/>
+        <item x="127"/>
+        <item x="30"/>
+        <item x="43"/>
+        <item x="85"/>
+        <item x="112"/>
+        <item x="62"/>
+        <item x="50"/>
+        <item x="98"/>
+        <item x="36"/>
+        <item x="106"/>
+        <item x="17"/>
+        <item x="6"/>
+        <item x="122"/>
+        <item x="52"/>
+        <item x="104"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="18"/>
+        <item x="26"/>
+        <item x="103"/>
+        <item x="31"/>
+        <item x="89"/>
+        <item x="118"/>
+        <item x="2"/>
+        <item x="16"/>
+        <item x="55"/>
+        <item x="58"/>
+        <item x="114"/>
+        <item x="33"/>
+        <item x="87"/>
+        <item x="113"/>
+        <item x="69"/>
+        <item x="51"/>
+        <item x="59"/>
+        <item x="101"/>
+        <item x="34"/>
+        <item x="109"/>
+        <item x="61"/>
+        <item x="132"/>
+        <item x="56"/>
+        <item x="64"/>
+        <item x="117"/>
+        <item x="63"/>
+        <item x="100"/>
+        <item x="124"/>
+        <item x="108"/>
+        <item x="115"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="4"/>
+        <item x="15"/>
+        <item x="65"/>
+        <item x="44"/>
+        <item x="119"/>
+        <item x="105"/>
+        <item x="66"/>
+        <item x="120"/>
+        <item x="123"/>
+        <item x="45"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="39"/>
+        <item x="73"/>
+        <item x="110"/>
+        <item x="46"/>
+        <item x="94"/>
+        <item x="74"/>
+        <item x="29"/>
+        <item x="75"/>
+        <item x="90"/>
+        <item x="67"/>
+        <item x="76"/>
+        <item x="38"/>
+        <item x="91"/>
+        <item x="37"/>
+        <item x="40"/>
+        <item x="60"/>
+        <item x="95"/>
+        <item x="77"/>
+        <item x="47"/>
+        <item x="78"/>
+        <item x="131"/>
+        <item x="96"/>
+        <item x="92"/>
+        <item x="79"/>
+        <item h="1" x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="35">
+        <item x="15"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="12"/>
+        <item x="30"/>
+        <item x="13"/>
+        <item x="19"/>
+        <item x="3"/>
+        <item x="28"/>
+        <item x="1"/>
+        <item x="22"/>
+        <item x="31"/>
+        <item x="16"/>
+        <item x="18"/>
+        <item x="24"/>
+        <item x="26"/>
+        <item x="11"/>
+        <item x="14"/>
+        <item x="27"/>
+        <item x="23"/>
+        <item x="8"/>
+        <item x="21"/>
+        <item x="25"/>
+        <item x="17"/>
+        <item x="10"/>
+        <item x="5"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="29"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item x="20"/>
+        <item x="6"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="27">
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="33"/>
+    </i>
+    <i>
+      <x v="42"/>
+    </i>
+    <i>
+      <x v="47"/>
+    </i>
+    <i>
+      <x v="49"/>
+    </i>
+    <i>
+      <x v="56"/>
+    </i>
+    <i>
+      <x v="61"/>
+    </i>
+    <i>
+      <x v="69"/>
+    </i>
+    <i>
+      <x v="70"/>
+    </i>
+    <i>
+      <x v="72"/>
+    </i>
+    <i>
+      <x v="74"/>
+    </i>
+    <i>
+      <x v="86"/>
+    </i>
+    <i>
+      <x v="94"/>
+    </i>
+    <i>
+      <x v="96"/>
+    </i>
+    <i>
+      <x v="101"/>
+    </i>
+    <i>
+      <x v="104"/>
+    </i>
+    <i>
+      <x v="108"/>
+    </i>
+    <i>
+      <x v="112"/>
+    </i>
+    <i>
+      <x v="119"/>
+    </i>
+    <i>
+      <x v="120"/>
+    </i>
+    <i>
+      <x v="121"/>
+    </i>
+    <i>
+      <x v="122"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="14" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Count of Recognition (Award" fld="14" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FC177463-ECB6-493F-84C5-BD2B6B5E3667}" name="PivotTable1" cacheId="331" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:B35" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="18">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -29021,311 +29344,6 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{166599A4-10FF-421A-AFB4-AE0C311C3DFB}" name="PivotTable2" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="C3:D30" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="18">
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="134">
-        <item x="57"/>
-        <item x="116"/>
-        <item x="10"/>
-        <item x="27"/>
-        <item x="88"/>
-        <item x="19"/>
-        <item x="14"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="125"/>
-        <item x="128"/>
-        <item x="121"/>
-        <item x="41"/>
-        <item x="80"/>
-        <item x="93"/>
-        <item x="81"/>
-        <item x="111"/>
-        <item x="82"/>
-        <item x="49"/>
-        <item x="48"/>
-        <item x="68"/>
-        <item x="107"/>
-        <item x="83"/>
-        <item x="42"/>
-        <item x="97"/>
-        <item x="5"/>
-        <item x="11"/>
-        <item x="8"/>
-        <item x="35"/>
-        <item x="25"/>
-        <item x="99"/>
-        <item x="32"/>
-        <item x="22"/>
-        <item x="9"/>
-        <item x="13"/>
-        <item x="126"/>
-        <item x="54"/>
-        <item x="28"/>
-        <item x="53"/>
-        <item x="21"/>
-        <item x="84"/>
-        <item x="20"/>
-        <item x="12"/>
-        <item x="1"/>
-        <item x="86"/>
-        <item x="102"/>
-        <item x="127"/>
-        <item x="30"/>
-        <item x="43"/>
-        <item x="85"/>
-        <item x="112"/>
-        <item x="62"/>
-        <item x="50"/>
-        <item x="98"/>
-        <item x="36"/>
-        <item x="106"/>
-        <item x="17"/>
-        <item x="6"/>
-        <item x="122"/>
-        <item x="52"/>
-        <item x="104"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="18"/>
-        <item x="26"/>
-        <item x="103"/>
-        <item x="31"/>
-        <item x="89"/>
-        <item x="118"/>
-        <item x="2"/>
-        <item x="16"/>
-        <item x="55"/>
-        <item x="58"/>
-        <item x="114"/>
-        <item x="33"/>
-        <item x="87"/>
-        <item x="113"/>
-        <item x="69"/>
-        <item x="51"/>
-        <item x="59"/>
-        <item x="101"/>
-        <item x="34"/>
-        <item x="109"/>
-        <item x="61"/>
-        <item x="132"/>
-        <item x="56"/>
-        <item x="64"/>
-        <item x="117"/>
-        <item x="63"/>
-        <item x="100"/>
-        <item x="124"/>
-        <item x="108"/>
-        <item x="115"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="4"/>
-        <item x="15"/>
-        <item x="65"/>
-        <item x="44"/>
-        <item x="119"/>
-        <item x="105"/>
-        <item x="66"/>
-        <item x="120"/>
-        <item x="123"/>
-        <item x="45"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="39"/>
-        <item x="73"/>
-        <item x="110"/>
-        <item x="46"/>
-        <item x="94"/>
-        <item x="74"/>
-        <item x="29"/>
-        <item x="75"/>
-        <item x="90"/>
-        <item x="67"/>
-        <item x="76"/>
-        <item x="38"/>
-        <item x="91"/>
-        <item x="37"/>
-        <item x="40"/>
-        <item x="60"/>
-        <item x="95"/>
-        <item x="77"/>
-        <item x="47"/>
-        <item x="78"/>
-        <item x="131"/>
-        <item x="96"/>
-        <item x="92"/>
-        <item x="79"/>
-        <item h="1" x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisPage" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="35">
-        <item x="15"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="12"/>
-        <item x="30"/>
-        <item x="13"/>
-        <item x="19"/>
-        <item x="3"/>
-        <item x="28"/>
-        <item x="1"/>
-        <item x="22"/>
-        <item x="31"/>
-        <item x="16"/>
-        <item x="18"/>
-        <item x="24"/>
-        <item x="26"/>
-        <item x="11"/>
-        <item x="14"/>
-        <item x="27"/>
-        <item x="23"/>
-        <item x="8"/>
-        <item x="21"/>
-        <item x="25"/>
-        <item x="17"/>
-        <item x="10"/>
-        <item x="5"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="29"/>
-        <item x="9"/>
-        <item x="7"/>
-        <item x="20"/>
-        <item x="6"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="27">
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="23"/>
-    </i>
-    <i>
-      <x v="27"/>
-    </i>
-    <i>
-      <x v="33"/>
-    </i>
-    <i>
-      <x v="42"/>
-    </i>
-    <i>
-      <x v="47"/>
-    </i>
-    <i>
-      <x v="49"/>
-    </i>
-    <i>
-      <x v="56"/>
-    </i>
-    <i>
-      <x v="61"/>
-    </i>
-    <i>
-      <x v="69"/>
-    </i>
-    <i>
-      <x v="70"/>
-    </i>
-    <i>
-      <x v="72"/>
-    </i>
-    <i>
-      <x v="74"/>
-    </i>
-    <i>
-      <x v="86"/>
-    </i>
-    <i>
-      <x v="94"/>
-    </i>
-    <i>
-      <x v="96"/>
-    </i>
-    <i>
-      <x v="101"/>
-    </i>
-    <i>
-      <x v="104"/>
-    </i>
-    <i>
-      <x v="108"/>
-    </i>
-    <i>
-      <x v="112"/>
-    </i>
-    <i>
-      <x v="119"/>
-    </i>
-    <i>
-      <x v="120"/>
-    </i>
-    <i>
-      <x v="121"/>
-    </i>
-    <i>
-      <x v="122"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="14" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Count of Recognition (Award" fld="14" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -29617,23 +29635,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:U364"/>
+  <dimension ref="A1:U366"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="17.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="15.5703125" style="1" customWidth="1"/>
     <col min="4" max="4" width="25.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" style="1" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="22.28515625" style="1" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" style="1" hidden="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="17.42578125" style="1" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="20.28515625" style="1" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="49.28515625" style="1" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="22.28515625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="17.42578125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="20.28515625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="49.28515625" style="1" customWidth="1"/>
     <col min="15" max="15" width="40.85546875" style="1" customWidth="1"/>
     <col min="16" max="16" width="31.140625" style="1" customWidth="1"/>
     <col min="17" max="17" width="28.42578125" style="1" customWidth="1"/>
@@ -29797,7 +29814,7 @@
       <c r="R4" s="12"/>
       <c r="S4" s="12"/>
     </row>
-    <row r="5" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="5" spans="1:19" ht="15.95" customHeight="1">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -29875,7 +29892,7 @@
       <c r="R6" s="12"/>
       <c r="S6" s="12"/>
     </row>
-    <row r="7" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="7" spans="1:19" ht="15.95" customHeight="1">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -29916,7 +29933,7 @@
       <c r="R7" s="12"/>
       <c r="S7" s="12"/>
     </row>
-    <row r="8" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="8" spans="1:19" ht="15.95" customHeight="1">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -29955,7 +29972,7 @@
       <c r="R8" s="12"/>
       <c r="S8" s="12"/>
     </row>
-    <row r="9" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="9" spans="1:19" ht="15.95" customHeight="1">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -29996,7 +30013,7 @@
       <c r="R9" s="12"/>
       <c r="S9" s="12"/>
     </row>
-    <row r="10" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="10" spans="1:19" ht="15.95" customHeight="1">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -30033,7 +30050,7 @@
       <c r="R10" s="12"/>
       <c r="S10" s="12"/>
     </row>
-    <row r="11" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="11" spans="1:19" ht="15.95" customHeight="1">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -30150,7 +30167,7 @@
       <c r="R13" s="12"/>
       <c r="S13" s="12"/>
     </row>
-    <row r="14" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="14" spans="1:19" ht="15.95" customHeight="1">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -30189,7 +30206,7 @@
       <c r="R14" s="12"/>
       <c r="S14" s="12"/>
     </row>
-    <row r="15" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="15" spans="1:19" ht="15.95" customHeight="1">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -30228,7 +30245,7 @@
       <c r="R15" s="12"/>
       <c r="S15" s="12"/>
     </row>
-    <row r="16" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="16" spans="1:19" ht="15.95" customHeight="1">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -30269,7 +30286,7 @@
       <c r="R16" s="12"/>
       <c r="S16" s="12"/>
     </row>
-    <row r="17" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="17" spans="1:19" ht="15.95" customHeight="1">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -30308,7 +30325,7 @@
       <c r="R17" s="12"/>
       <c r="S17" s="12"/>
     </row>
-    <row r="18" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="18" spans="1:19" ht="15.95" customHeight="1">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -30386,7 +30403,7 @@
       <c r="R19" s="12"/>
       <c r="S19" s="12"/>
     </row>
-    <row r="20" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="20" spans="1:19" ht="15.95" customHeight="1">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -30425,7 +30442,7 @@
       <c r="R20" s="12"/>
       <c r="S20" s="12"/>
     </row>
-    <row r="21" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="21" spans="1:19" ht="15.95" customHeight="1">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -30466,7 +30483,7 @@
       <c r="R21" s="12"/>
       <c r="S21" s="12"/>
     </row>
-    <row r="22" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="22" spans="1:19" ht="15.95" customHeight="1">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -30544,7 +30561,7 @@
       <c r="R23" s="12"/>
       <c r="S23" s="12"/>
     </row>
-    <row r="24" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="24" spans="1:19" ht="15.95" customHeight="1">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -30622,7 +30639,7 @@
       <c r="R25" s="12"/>
       <c r="S25" s="12"/>
     </row>
-    <row r="26" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="26" spans="1:19" ht="15.95" customHeight="1">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -30700,7 +30717,7 @@
       <c r="R27" s="12"/>
       <c r="S27" s="12"/>
     </row>
-    <row r="28" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="28" spans="1:19" ht="15.95" customHeight="1">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -30737,7 +30754,7 @@
       <c r="R28" s="12"/>
       <c r="S28" s="12"/>
     </row>
-    <row r="29" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="29" spans="1:19" ht="15.95" customHeight="1">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -30774,7 +30791,7 @@
       <c r="R29" s="12"/>
       <c r="S29" s="12"/>
     </row>
-    <row r="30" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="30" spans="1:19" ht="15.95" customHeight="1">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -30811,7 +30828,7 @@
       <c r="R30" s="12"/>
       <c r="S30" s="12"/>
     </row>
-    <row r="31" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="31" spans="1:19" ht="15.95" customHeight="1">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -30850,7 +30867,7 @@
       <c r="R31" s="12"/>
       <c r="S31" s="12"/>
     </row>
-    <row r="32" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="32" spans="1:19" ht="15.95" customHeight="1">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -30889,7 +30906,7 @@
       <c r="R32" s="12"/>
       <c r="S32" s="12"/>
     </row>
-    <row r="33" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="33" spans="1:19" ht="15.95" customHeight="1">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -30926,7 +30943,7 @@
       <c r="R33" s="12"/>
       <c r="S33" s="12"/>
     </row>
-    <row r="34" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="34" spans="1:19" ht="15.95" customHeight="1">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -30963,7 +30980,7 @@
       <c r="R34" s="12"/>
       <c r="S34" s="12"/>
     </row>
-    <row r="35" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="35" spans="1:19" ht="15.95" customHeight="1">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -31002,7 +31019,7 @@
       <c r="R35" s="12"/>
       <c r="S35" s="12"/>
     </row>
-    <row r="36" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="36" spans="1:19" ht="15.95" customHeight="1">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -31039,7 +31056,7 @@
       <c r="R36" s="12"/>
       <c r="S36" s="12"/>
     </row>
-    <row r="37" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="37" spans="1:19" ht="15.95" customHeight="1">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -31115,7 +31132,7 @@
       <c r="R38" s="12"/>
       <c r="S38" s="12"/>
     </row>
-    <row r="39" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="39" spans="1:19" ht="15.95" customHeight="1">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -31193,7 +31210,7 @@
       <c r="R40" s="12"/>
       <c r="S40" s="12"/>
     </row>
-    <row r="41" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="41" spans="1:19" ht="15.95" customHeight="1">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -31273,7 +31290,7 @@
       <c r="R42" s="12"/>
       <c r="S42" s="12"/>
     </row>
-    <row r="43" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="43" spans="1:19" ht="15.95" customHeight="1">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -31312,7 +31329,7 @@
       <c r="R43" s="12"/>
       <c r="S43" s="12"/>
     </row>
-    <row r="44" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="44" spans="1:19" ht="15.95" customHeight="1">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -31351,7 +31368,7 @@
       <c r="R44" s="12"/>
       <c r="S44" s="12"/>
     </row>
-    <row r="45" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="45" spans="1:19" ht="15.95" customHeight="1">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -31392,7 +31409,7 @@
       <c r="R45" s="12"/>
       <c r="S45" s="12"/>
     </row>
-    <row r="46" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="46" spans="1:19" ht="15.95" customHeight="1">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -31431,7 +31448,7 @@
       <c r="R46" s="12"/>
       <c r="S46" s="12"/>
     </row>
-    <row r="47" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="47" spans="1:19" ht="15.95" customHeight="1">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -31472,7 +31489,7 @@
       <c r="R47" s="12"/>
       <c r="S47" s="12"/>
     </row>
-    <row r="48" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="48" spans="1:19" ht="15.95" customHeight="1">
       <c r="A48" s="3">
         <v>47</v>
       </c>
@@ -31511,7 +31528,7 @@
       <c r="R48" s="12"/>
       <c r="S48" s="12"/>
     </row>
-    <row r="49" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="49" spans="1:19" ht="15.95" customHeight="1">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -31550,7 +31567,7 @@
       <c r="R49" s="12"/>
       <c r="S49" s="12"/>
     </row>
-    <row r="50" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="50" spans="1:19" ht="15.95" customHeight="1">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -31591,7 +31608,7 @@
       <c r="R50" s="12"/>
       <c r="S50" s="12"/>
     </row>
-    <row r="51" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="51" spans="1:19" ht="15.95" customHeight="1">
       <c r="A51" s="3">
         <v>50</v>
       </c>
@@ -31630,7 +31647,7 @@
       <c r="R51" s="12"/>
       <c r="S51" s="12"/>
     </row>
-    <row r="52" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="52" spans="1:19" ht="15.95" customHeight="1">
       <c r="A52" s="3">
         <v>51</v>
       </c>
@@ -31669,7 +31686,7 @@
       <c r="R52" s="12"/>
       <c r="S52" s="12"/>
     </row>
-    <row r="53" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="53" spans="1:19" ht="15.95" customHeight="1">
       <c r="A53" s="3">
         <v>53</v>
       </c>
@@ -31708,7 +31725,7 @@
       <c r="R53" s="12"/>
       <c r="S53" s="12"/>
     </row>
-    <row r="54" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="54" spans="1:19" ht="15.95" customHeight="1">
       <c r="A54" s="3">
         <v>54</v>
       </c>
@@ -31786,7 +31803,7 @@
       <c r="R55" s="12"/>
       <c r="S55" s="12"/>
     </row>
-    <row r="56" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="56" spans="1:19" ht="15.95" customHeight="1">
       <c r="A56" s="3">
         <v>56</v>
       </c>
@@ -31825,7 +31842,7 @@
       <c r="R56" s="12"/>
       <c r="S56" s="12"/>
     </row>
-    <row r="57" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="57" spans="1:19" ht="15.95" customHeight="1">
       <c r="A57" s="3">
         <v>57</v>
       </c>
@@ -31981,7 +31998,7 @@
       <c r="R60" s="12"/>
       <c r="S60" s="12"/>
     </row>
-    <row r="61" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="61" spans="1:19" ht="15.95" customHeight="1">
       <c r="A61" s="3">
         <v>61</v>
       </c>
@@ -32100,7 +32117,7 @@
       <c r="R63" s="3"/>
       <c r="S63" s="3"/>
     </row>
-    <row r="64" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="64" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A64" s="3">
         <v>64</v>
       </c>
@@ -32141,7 +32158,7 @@
       <c r="R64" s="3"/>
       <c r="S64" s="3"/>
     </row>
-    <row r="65" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="65" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A65" s="3">
         <v>65</v>
       </c>
@@ -32182,7 +32199,7 @@
       <c r="R65" s="3"/>
       <c r="S65" s="3"/>
     </row>
-    <row r="66" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="66" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A66" s="3">
         <v>66</v>
       </c>
@@ -32223,7 +32240,7 @@
       <c r="R66" s="3"/>
       <c r="S66" s="3"/>
     </row>
-    <row r="67" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="67" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A67" s="3">
         <v>67</v>
       </c>
@@ -32264,7 +32281,7 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
     </row>
-    <row r="68" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="68" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A68" s="3">
         <v>68</v>
       </c>
@@ -32305,7 +32322,7 @@
       <c r="R68" s="3"/>
       <c r="S68" s="3"/>
     </row>
-    <row r="69" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="69" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A69" s="3">
         <v>69</v>
       </c>
@@ -32348,7 +32365,7 @@
       <c r="R69" s="3"/>
       <c r="S69" s="3"/>
     </row>
-    <row r="70" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="70" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A70" s="3">
         <v>70</v>
       </c>
@@ -32389,7 +32406,7 @@
       <c r="R70" s="3"/>
       <c r="S70" s="3"/>
     </row>
-    <row r="71" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="71" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A71" s="3">
         <v>71</v>
       </c>
@@ -32428,7 +32445,7 @@
       <c r="R71" s="3"/>
       <c r="S71" s="3"/>
     </row>
-    <row r="72" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="72" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A72" s="3">
         <v>72</v>
       </c>
@@ -32467,7 +32484,7 @@
       <c r="R72" s="3"/>
       <c r="S72" s="3"/>
     </row>
-    <row r="73" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="73" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A73" s="3">
         <v>73</v>
       </c>
@@ -32508,7 +32525,7 @@
       <c r="R73" s="3"/>
       <c r="S73" s="3"/>
     </row>
-    <row r="74" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="74" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A74" s="3">
         <v>74</v>
       </c>
@@ -32549,7 +32566,7 @@
       <c r="R74" s="3"/>
       <c r="S74" s="3"/>
     </row>
-    <row r="75" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="75" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A75" s="3">
         <v>75</v>
       </c>
@@ -32588,7 +32605,7 @@
       <c r="R75" s="3"/>
       <c r="S75" s="3"/>
     </row>
-    <row r="76" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="76" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A76" s="3">
         <v>76</v>
       </c>
@@ -32629,7 +32646,7 @@
       <c r="R76" s="3"/>
       <c r="S76" s="3"/>
     </row>
-    <row r="77" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="77" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A77" s="3">
         <v>77</v>
       </c>
@@ -32668,7 +32685,7 @@
       <c r="R77" s="3"/>
       <c r="S77" s="3"/>
     </row>
-    <row r="78" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="78" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A78" s="3">
         <v>78</v>
       </c>
@@ -32707,7 +32724,7 @@
       <c r="R78" s="3"/>
       <c r="S78" s="3"/>
     </row>
-    <row r="79" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="79" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A79" s="3">
         <v>79</v>
       </c>
@@ -32746,7 +32763,7 @@
       <c r="R79" s="3"/>
       <c r="S79" s="3"/>
     </row>
-    <row r="80" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="80" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A80" s="3">
         <v>80</v>
       </c>
@@ -32787,7 +32804,7 @@
       <c r="R80" s="3"/>
       <c r="S80" s="3"/>
     </row>
-    <row r="81" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="81" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A81" s="3">
         <v>81</v>
       </c>
@@ -32826,7 +32843,7 @@
       <c r="R81" s="3"/>
       <c r="S81" s="3"/>
     </row>
-    <row r="82" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="82" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A82" s="3">
         <v>82</v>
       </c>
@@ -32871,7 +32888,7 @@
       </c>
       <c r="S82" s="3"/>
     </row>
-    <row r="83" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="83" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A83" s="3">
         <v>83</v>
       </c>
@@ -32914,7 +32931,7 @@
       <c r="R83" s="3"/>
       <c r="S83" s="3"/>
     </row>
-    <row r="84" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="84" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A84" s="3">
         <v>84</v>
       </c>
@@ -33031,7 +33048,7 @@
       <c r="R86" s="3"/>
       <c r="S86" s="3"/>
     </row>
-    <row r="87" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="87" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A87" s="3">
         <v>87</v>
       </c>
@@ -33072,7 +33089,7 @@
       <c r="R87" s="3"/>
       <c r="S87" s="3"/>
     </row>
-    <row r="88" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="88" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A88" s="3">
         <v>88</v>
       </c>
@@ -33113,7 +33130,7 @@
       <c r="R88" s="3"/>
       <c r="S88" s="3"/>
     </row>
-    <row r="89" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="89" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A89" s="3">
         <v>89</v>
       </c>
@@ -33156,7 +33173,7 @@
       </c>
       <c r="S89" s="3"/>
     </row>
-    <row r="90" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="90" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A90" s="3">
         <v>90</v>
       </c>
@@ -33197,7 +33214,7 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
     </row>
-    <row r="91" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="91" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A91" s="3">
         <v>91</v>
       </c>
@@ -33238,7 +33255,7 @@
       </c>
       <c r="S91" s="3"/>
     </row>
-    <row r="92" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="92" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A92" s="3">
         <v>92</v>
       </c>
@@ -33277,7 +33294,7 @@
       <c r="R92" s="3"/>
       <c r="S92" s="3"/>
     </row>
-    <row r="93" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="93" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A93" s="3">
         <v>93</v>
       </c>
@@ -33318,7 +33335,7 @@
       <c r="R93" s="3"/>
       <c r="S93" s="3"/>
     </row>
-    <row r="94" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="94" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A94" s="3">
         <v>94</v>
       </c>
@@ -33357,7 +33374,7 @@
       <c r="R94" s="3"/>
       <c r="S94" s="3"/>
     </row>
-    <row r="95" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="95" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A95" s="3">
         <v>95</v>
       </c>
@@ -33400,7 +33417,7 @@
       </c>
       <c r="S95" s="3"/>
     </row>
-    <row r="96" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="96" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A96" s="3">
         <v>96</v>
       </c>
@@ -33443,7 +33460,7 @@
       </c>
       <c r="S96" s="3"/>
     </row>
-    <row r="97" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="97" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A97" s="3">
         <v>97</v>
       </c>
@@ -33488,7 +33505,7 @@
       </c>
       <c r="S97" s="3"/>
     </row>
-    <row r="98" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="98" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A98" s="3">
         <v>223</v>
       </c>
@@ -33529,7 +33546,7 @@
       <c r="R98" s="3"/>
       <c r="S98" s="3"/>
     </row>
-    <row r="99" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="99" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A99" s="3">
         <v>99</v>
       </c>
@@ -33568,7 +33585,7 @@
       <c r="R99" s="3"/>
       <c r="S99" s="3"/>
     </row>
-    <row r="100" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="100" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A100" s="3">
         <v>100</v>
       </c>
@@ -33607,7 +33624,7 @@
       <c r="R100" s="3"/>
       <c r="S100" s="3"/>
     </row>
-    <row r="101" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="101" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A101" s="3">
         <v>101</v>
       </c>
@@ -33646,7 +33663,7 @@
       <c r="R101" s="3"/>
       <c r="S101" s="3"/>
     </row>
-    <row r="102" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="102" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A102" s="3">
         <v>102</v>
       </c>
@@ -33685,7 +33702,7 @@
       <c r="R102" s="3"/>
       <c r="S102" s="3"/>
     </row>
-    <row r="103" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="103" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A103" s="3">
         <v>103</v>
       </c>
@@ -33728,7 +33745,7 @@
       </c>
       <c r="S103" s="3"/>
     </row>
-    <row r="104" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="104" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A104" s="3">
         <v>104</v>
       </c>
@@ -33765,7 +33782,7 @@
       <c r="R104" s="3"/>
       <c r="S104" s="3"/>
     </row>
-    <row r="105" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="105" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A105" s="3">
         <v>105</v>
       </c>
@@ -33804,7 +33821,7 @@
       <c r="R105" s="3"/>
       <c r="S105" s="3"/>
     </row>
-    <row r="106" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="106" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A106" s="3">
         <v>106</v>
       </c>
@@ -33843,7 +33860,7 @@
       <c r="R106" s="3"/>
       <c r="S106" s="3"/>
     </row>
-    <row r="107" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="107" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A107" s="3">
         <v>107</v>
       </c>
@@ -33882,7 +33899,7 @@
       <c r="R107" s="3"/>
       <c r="S107" s="3"/>
     </row>
-    <row r="108" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="108" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A108" s="3">
         <v>108</v>
       </c>
@@ -33921,7 +33938,7 @@
       <c r="R108" s="3"/>
       <c r="S108" s="3"/>
     </row>
-    <row r="109" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="109" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A109" s="3">
         <v>109</v>
       </c>
@@ -33960,7 +33977,7 @@
       <c r="R109" s="3"/>
       <c r="S109" s="3"/>
     </row>
-    <row r="110" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="110" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A110" s="3">
         <v>110</v>
       </c>
@@ -33999,7 +34016,7 @@
       <c r="R110" s="3"/>
       <c r="S110" s="3"/>
     </row>
-    <row r="111" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="111" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A111" s="3">
         <v>111</v>
       </c>
@@ -34038,7 +34055,7 @@
       <c r="R111" s="3"/>
       <c r="S111" s="3"/>
     </row>
-    <row r="112" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="112" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A112" s="3">
         <v>112</v>
       </c>
@@ -34077,7 +34094,7 @@
       <c r="R112" s="3"/>
       <c r="S112" s="3"/>
     </row>
-    <row r="113" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="113" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A113" s="3">
         <v>113</v>
       </c>
@@ -34116,7 +34133,7 @@
       <c r="R113" s="3"/>
       <c r="S113" s="3"/>
     </row>
-    <row r="114" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="114" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A114" s="3">
         <v>114</v>
       </c>
@@ -34155,7 +34172,7 @@
       <c r="R114" s="3"/>
       <c r="S114" s="3"/>
     </row>
-    <row r="115" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="115" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A115" s="3">
         <v>115</v>
       </c>
@@ -34194,7 +34211,7 @@
       <c r="R115" s="3"/>
       <c r="S115" s="3"/>
     </row>
-    <row r="116" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="116" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A116" s="3">
         <v>116</v>
       </c>
@@ -34233,7 +34250,7 @@
       <c r="R116" s="3"/>
       <c r="S116" s="3"/>
     </row>
-    <row r="117" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="117" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A117" s="3">
         <v>117</v>
       </c>
@@ -34272,7 +34289,7 @@
       <c r="R117" s="3"/>
       <c r="S117" s="3"/>
     </row>
-    <row r="118" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="118" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A118" s="3">
         <v>290</v>
       </c>
@@ -34315,7 +34332,7 @@
       <c r="R118" s="3"/>
       <c r="S118" s="3"/>
     </row>
-    <row r="119" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="119" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A119" s="3">
         <v>119</v>
       </c>
@@ -34354,7 +34371,7 @@
       <c r="R119" s="3"/>
       <c r="S119" s="3"/>
     </row>
-    <row r="120" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="120" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A120" s="3">
         <v>120</v>
       </c>
@@ -34434,7 +34451,7 @@
       </c>
       <c r="S121" s="3"/>
     </row>
-    <row r="122" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="122" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A122" s="3">
         <v>122</v>
       </c>
@@ -34477,7 +34494,7 @@
       </c>
       <c r="S122" s="3"/>
     </row>
-    <row r="123" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="123" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A123" s="3">
         <v>123</v>
       </c>
@@ -34557,7 +34574,7 @@
       <c r="R124" s="3"/>
       <c r="S124" s="3"/>
     </row>
-    <row r="125" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="125" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A125" s="3">
         <v>125</v>
       </c>
@@ -34596,7 +34613,7 @@
       <c r="R125" s="3"/>
       <c r="S125" s="3"/>
     </row>
-    <row r="126" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="126" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A126" s="3">
         <v>126</v>
       </c>
@@ -34637,7 +34654,7 @@
       <c r="R126" s="3"/>
       <c r="S126" s="3"/>
     </row>
-    <row r="127" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="127" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A127" s="3">
         <v>127</v>
       </c>
@@ -34676,7 +34693,7 @@
       <c r="R127" s="3"/>
       <c r="S127" s="3"/>
     </row>
-    <row r="128" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="128" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A128" s="3">
         <v>128</v>
       </c>
@@ -34721,7 +34738,7 @@
       </c>
       <c r="S128" s="3"/>
     </row>
-    <row r="129" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="129" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A129" s="3">
         <v>129</v>
       </c>
@@ -34764,7 +34781,7 @@
       <c r="R129" s="3"/>
       <c r="S129" s="3"/>
     </row>
-    <row r="130" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="130" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A130" s="3">
         <v>130</v>
       </c>
@@ -34803,7 +34820,7 @@
       <c r="R130" s="3"/>
       <c r="S130" s="3"/>
     </row>
-    <row r="131" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="131" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A131" s="3">
         <v>131</v>
       </c>
@@ -34844,7 +34861,7 @@
       <c r="R131" s="3"/>
       <c r="S131" s="3"/>
     </row>
-    <row r="132" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="132" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A132" s="3">
         <v>132</v>
       </c>
@@ -34883,7 +34900,7 @@
       <c r="R132" s="3"/>
       <c r="S132" s="3"/>
     </row>
-    <row r="133" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="133" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A133" s="3">
         <v>133</v>
       </c>
@@ -34928,7 +34945,7 @@
       </c>
       <c r="S133" s="3"/>
     </row>
-    <row r="134" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="134" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A134" s="3">
         <v>134</v>
       </c>
@@ -34969,7 +34986,7 @@
       <c r="R134" s="3"/>
       <c r="S134" s="3"/>
     </row>
-    <row r="135" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="135" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A135" s="3">
         <v>135</v>
       </c>
@@ -35006,7 +35023,7 @@
       <c r="R135" s="3"/>
       <c r="S135" s="3"/>
     </row>
-    <row r="136" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="136" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A136" s="3">
         <v>136</v>
       </c>
@@ -35047,7 +35064,7 @@
       </c>
       <c r="S136" s="3"/>
     </row>
-    <row r="137" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="137" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A137" s="3">
         <v>137</v>
       </c>
@@ -35088,7 +35105,7 @@
       <c r="R137" s="3"/>
       <c r="S137" s="3"/>
     </row>
-    <row r="138" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="138" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A138" s="3">
         <v>138</v>
       </c>
@@ -35131,7 +35148,7 @@
       <c r="R138" s="3"/>
       <c r="S138" s="3"/>
     </row>
-    <row r="139" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="139" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A139" s="3">
         <v>139</v>
       </c>
@@ -35172,7 +35189,7 @@
       <c r="R139" s="3"/>
       <c r="S139" s="3"/>
     </row>
-    <row r="140" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="140" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A140" s="3">
         <v>118</v>
       </c>
@@ -35211,7 +35228,7 @@
       <c r="R140" s="3"/>
       <c r="S140" s="3"/>
     </row>
-    <row r="141" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="141" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A141" s="3">
         <v>141</v>
       </c>
@@ -35250,7 +35267,7 @@
       <c r="R141" s="3"/>
       <c r="S141" s="3"/>
     </row>
-    <row r="142" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="142" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A142" s="3">
         <v>142</v>
       </c>
@@ -35289,7 +35306,7 @@
       <c r="R142" s="3"/>
       <c r="S142" s="3"/>
     </row>
-    <row r="143" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="143" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A143" s="3">
         <v>143</v>
       </c>
@@ -35328,7 +35345,7 @@
       <c r="R143" s="3"/>
       <c r="S143" s="3"/>
     </row>
-    <row r="144" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="144" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A144" s="3">
         <v>144</v>
       </c>
@@ -35367,7 +35384,7 @@
       <c r="R144" s="3"/>
       <c r="S144" s="3"/>
     </row>
-    <row r="145" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="145" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A145" s="3">
         <v>145</v>
       </c>
@@ -35406,7 +35423,7 @@
       <c r="R145" s="3"/>
       <c r="S145" s="3"/>
     </row>
-    <row r="146" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="146" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A146" s="3">
         <v>146</v>
       </c>
@@ -35443,7 +35460,7 @@
       <c r="R146" s="3"/>
       <c r="S146" s="3"/>
     </row>
-    <row r="147" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="147" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A147" s="3">
         <v>147</v>
       </c>
@@ -35482,7 +35499,7 @@
       <c r="R147" s="3"/>
       <c r="S147" s="3"/>
     </row>
-    <row r="148" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="148" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A148" s="3">
         <v>148</v>
       </c>
@@ -35716,7 +35733,7 @@
       <c r="R153" s="3"/>
       <c r="S153" s="3"/>
     </row>
-    <row r="154" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="154" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A154" s="3">
         <v>154</v>
       </c>
@@ -35755,7 +35772,7 @@
       <c r="R154" s="3"/>
       <c r="S154" s="3"/>
     </row>
-    <row r="155" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="155" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A155" s="3">
         <v>155</v>
       </c>
@@ -35794,7 +35811,7 @@
       <c r="R155" s="3"/>
       <c r="S155" s="3"/>
     </row>
-    <row r="156" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="156" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A156" s="3">
         <v>156</v>
       </c>
@@ -35833,7 +35850,7 @@
       <c r="R156" s="3"/>
       <c r="S156" s="3"/>
     </row>
-    <row r="157" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="157" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A157" s="3">
         <v>157</v>
       </c>
@@ -35872,7 +35889,7 @@
       <c r="R157" s="3"/>
       <c r="S157" s="3"/>
     </row>
-    <row r="158" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="158" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A158" s="3">
         <v>158</v>
       </c>
@@ -35911,7 +35928,7 @@
       <c r="R158" s="3"/>
       <c r="S158" s="3"/>
     </row>
-    <row r="159" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="159" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A159" s="3">
         <v>159</v>
       </c>
@@ -35950,7 +35967,7 @@
       <c r="R159" s="3"/>
       <c r="S159" s="3"/>
     </row>
-    <row r="160" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="160" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A160" s="3">
         <v>160</v>
       </c>
@@ -35991,7 +36008,7 @@
       <c r="R160" s="3"/>
       <c r="S160" s="3"/>
     </row>
-    <row r="161" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="161" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A161" s="3">
         <v>161</v>
       </c>
@@ -36030,7 +36047,7 @@
       <c r="R161" s="3"/>
       <c r="S161" s="3"/>
     </row>
-    <row r="162" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="162" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A162" s="3">
         <v>162</v>
       </c>
@@ -36069,7 +36086,7 @@
       <c r="R162" s="3"/>
       <c r="S162" s="3"/>
     </row>
-    <row r="163" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="163" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A163" s="3">
         <v>163</v>
       </c>
@@ -36110,7 +36127,7 @@
       </c>
       <c r="S163" s="3"/>
     </row>
-    <row r="164" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="164" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A164" s="3">
         <v>164</v>
       </c>
@@ -36153,7 +36170,7 @@
       <c r="R164" s="3"/>
       <c r="S164" s="3"/>
     </row>
-    <row r="165" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="165" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A165" s="3">
         <v>165</v>
       </c>
@@ -36194,7 +36211,7 @@
       <c r="R165" s="3"/>
       <c r="S165" s="3"/>
     </row>
-    <row r="166" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="166" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A166" s="3">
         <v>166</v>
       </c>
@@ -36235,7 +36252,7 @@
       <c r="R166" s="3"/>
       <c r="S166" s="3"/>
     </row>
-    <row r="167" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="167" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A167" s="3">
         <v>167</v>
       </c>
@@ -36276,7 +36293,7 @@
       <c r="R167" s="3"/>
       <c r="S167" s="3"/>
     </row>
-    <row r="168" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="168" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A168" s="3">
         <v>168</v>
       </c>
@@ -36323,7 +36340,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="169" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="169" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A169" s="3">
         <v>169</v>
       </c>
@@ -36366,7 +36383,7 @@
       <c r="R169" s="3"/>
       <c r="S169" s="3"/>
     </row>
-    <row r="170" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="170" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A170" s="3">
         <v>170</v>
       </c>
@@ -36407,7 +36424,7 @@
       <c r="R170" s="3"/>
       <c r="S170" s="3"/>
     </row>
-    <row r="171" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="171" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A171" s="3">
         <v>171</v>
       </c>
@@ -36448,7 +36465,7 @@
       <c r="R171" s="3"/>
       <c r="S171" s="3"/>
     </row>
-    <row r="172" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="172" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A172" s="3">
         <v>172</v>
       </c>
@@ -36530,7 +36547,7 @@
       <c r="R173" s="3"/>
       <c r="S173" s="3"/>
     </row>
-    <row r="174" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="174" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A174" s="3">
         <v>174</v>
       </c>
@@ -36569,7 +36586,7 @@
       <c r="R174" s="3"/>
       <c r="S174" s="3"/>
     </row>
-    <row r="175" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="175" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A175" s="3">
         <v>175</v>
       </c>
@@ -36610,7 +36627,7 @@
       <c r="R175" s="3"/>
       <c r="S175" s="3"/>
     </row>
-    <row r="176" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="176" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A176" s="3">
         <v>176</v>
       </c>
@@ -36692,7 +36709,7 @@
       <c r="R177" s="3"/>
       <c r="S177" s="3"/>
     </row>
-    <row r="178" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="178" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A178" s="3">
         <v>178</v>
       </c>
@@ -36731,7 +36748,7 @@
       <c r="R178" s="3"/>
       <c r="S178" s="3"/>
     </row>
-    <row r="179" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="179" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A179" s="3">
         <v>179</v>
       </c>
@@ -36772,7 +36789,7 @@
       <c r="R179" s="3"/>
       <c r="S179" s="3"/>
     </row>
-    <row r="180" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="180" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A180" s="3">
         <v>180</v>
       </c>
@@ -36813,7 +36830,7 @@
       <c r="R180" s="3"/>
       <c r="S180" s="3"/>
     </row>
-    <row r="181" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="181" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A181" s="3">
         <v>181</v>
       </c>
@@ -36854,7 +36871,7 @@
       <c r="R181" s="3"/>
       <c r="S181" s="3"/>
     </row>
-    <row r="182" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="182" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A182" s="3">
         <v>182</v>
       </c>
@@ -36895,7 +36912,7 @@
       <c r="R182" s="3"/>
       <c r="S182" s="3"/>
     </row>
-    <row r="183" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="183" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A183" s="3">
         <v>183</v>
       </c>
@@ -36944,7 +36961,7 @@
       </c>
       <c r="S183" s="3"/>
     </row>
-    <row r="184" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="184" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A184" s="3">
         <v>184</v>
       </c>
@@ -36985,7 +37002,7 @@
       <c r="R184" s="3"/>
       <c r="S184" s="3"/>
     </row>
-    <row r="185" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="185" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A185" s="3">
         <v>185</v>
       </c>
@@ -37026,7 +37043,7 @@
       <c r="R185" s="3"/>
       <c r="S185" s="3"/>
     </row>
-    <row r="186" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="186" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A186" s="3">
         <v>186</v>
       </c>
@@ -37071,7 +37088,7 @@
       </c>
       <c r="S186" s="3"/>
     </row>
-    <row r="187" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="187" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A187" s="3">
         <v>187</v>
       </c>
@@ -37112,7 +37129,7 @@
       <c r="R187" s="3"/>
       <c r="S187" s="3"/>
     </row>
-    <row r="188" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="188" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A188" s="3">
         <v>188</v>
       </c>
@@ -37153,7 +37170,7 @@
       <c r="R188" s="3"/>
       <c r="S188" s="3"/>
     </row>
-    <row r="189" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="189" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A189" s="3">
         <v>189</v>
       </c>
@@ -37198,7 +37215,7 @@
       <c r="R189" s="3"/>
       <c r="S189" s="3"/>
     </row>
-    <row r="190" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="190" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A190" s="3">
         <v>190</v>
       </c>
@@ -37239,7 +37256,7 @@
       <c r="R190" s="3"/>
       <c r="S190" s="3"/>
     </row>
-    <row r="191" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="191" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A191" s="3">
         <v>191</v>
       </c>
@@ -37284,7 +37301,7 @@
       <c r="R191" s="3"/>
       <c r="S191" s="3"/>
     </row>
-    <row r="192" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="192" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A192" s="3">
         <v>192</v>
       </c>
@@ -37325,7 +37342,7 @@
       <c r="R192" s="3"/>
       <c r="S192" s="3"/>
     </row>
-    <row r="193" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="193" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A193" s="3">
         <v>193</v>
       </c>
@@ -37366,7 +37383,7 @@
       <c r="R193" s="3"/>
       <c r="S193" s="3"/>
     </row>
-    <row r="194" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="194" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A194" s="3">
         <v>194</v>
       </c>
@@ -37407,7 +37424,7 @@
       <c r="R194" s="3"/>
       <c r="S194" s="3"/>
     </row>
-    <row r="195" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="195" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A195" s="3">
         <v>195</v>
       </c>
@@ -37450,7 +37467,7 @@
       <c r="R195" s="3"/>
       <c r="S195" s="3"/>
     </row>
-    <row r="196" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="196" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A196" s="3">
         <v>196</v>
       </c>
@@ -37493,7 +37510,7 @@
       <c r="R196" s="3"/>
       <c r="S196" s="3"/>
     </row>
-    <row r="197" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="197" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A197" s="3">
         <v>197</v>
       </c>
@@ -37534,7 +37551,7 @@
       <c r="R197" s="3"/>
       <c r="S197" s="3"/>
     </row>
-    <row r="198" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="198" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A198" s="3">
         <v>198</v>
       </c>
@@ -37577,7 +37594,7 @@
       <c r="R198" s="3"/>
       <c r="S198" s="3"/>
     </row>
-    <row r="199" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="199" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A199" s="3">
         <v>199</v>
       </c>
@@ -37620,7 +37637,7 @@
       <c r="R199" s="3"/>
       <c r="S199" s="3"/>
     </row>
-    <row r="200" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="200" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A200" s="3">
         <v>200</v>
       </c>
@@ -37663,7 +37680,7 @@
       <c r="R200" s="3"/>
       <c r="S200" s="3"/>
     </row>
-    <row r="201" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="201" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A201" s="3">
         <v>201</v>
       </c>
@@ -37706,7 +37723,7 @@
       <c r="R201" s="3"/>
       <c r="S201" s="3"/>
     </row>
-    <row r="202" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="202" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A202" s="3">
         <v>202</v>
       </c>
@@ -37751,7 +37768,7 @@
       </c>
       <c r="S202" s="3"/>
     </row>
-    <row r="203" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="203" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A203" s="3">
         <v>203</v>
       </c>
@@ -37794,7 +37811,7 @@
       <c r="R203" s="3"/>
       <c r="S203" s="3"/>
     </row>
-    <row r="204" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="204" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A204" s="3">
         <v>204</v>
       </c>
@@ -37835,7 +37852,7 @@
       <c r="R204" s="3"/>
       <c r="S204" s="3"/>
     </row>
-    <row r="205" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="205" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A205" s="3">
         <v>205</v>
       </c>
@@ -37876,7 +37893,7 @@
       <c r="R205" s="3"/>
       <c r="S205" s="3"/>
     </row>
-    <row r="206" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="206" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A206" s="3">
         <v>206</v>
       </c>
@@ -37917,7 +37934,7 @@
       <c r="R206" s="3"/>
       <c r="S206" s="3"/>
     </row>
-    <row r="207" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="207" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A207" s="3">
         <v>207</v>
       </c>
@@ -37999,7 +38016,7 @@
       <c r="R208" s="3"/>
       <c r="S208" s="3"/>
     </row>
-    <row r="209" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="209" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A209" s="3">
         <v>209</v>
       </c>
@@ -38044,7 +38061,7 @@
       </c>
       <c r="S209" s="3"/>
     </row>
-    <row r="210" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="210" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A210" s="3">
         <v>210</v>
       </c>
@@ -38085,7 +38102,7 @@
       <c r="R210" s="3"/>
       <c r="S210" s="3"/>
     </row>
-    <row r="211" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="211" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A211" s="3">
         <v>211</v>
       </c>
@@ -38128,7 +38145,7 @@
       <c r="R211" s="3"/>
       <c r="S211" s="3"/>
     </row>
-    <row r="212" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="212" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A212" s="3">
         <v>212</v>
       </c>
@@ -38171,7 +38188,7 @@
       <c r="R212" s="3"/>
       <c r="S212" s="3"/>
     </row>
-    <row r="213" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="213" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A213" s="3">
         <v>213</v>
       </c>
@@ -38212,7 +38229,7 @@
       <c r="R213" s="3"/>
       <c r="S213" s="3"/>
     </row>
-    <row r="214" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="214" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A214" s="3">
         <v>214</v>
       </c>
@@ -38253,7 +38270,7 @@
       <c r="R214" s="3"/>
       <c r="S214" s="3"/>
     </row>
-    <row r="215" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="215" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A215" s="3">
         <v>215</v>
       </c>
@@ -38294,7 +38311,7 @@
       <c r="R215" s="3"/>
       <c r="S215" s="3"/>
     </row>
-    <row r="216" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="216" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A216" s="3">
         <v>216</v>
       </c>
@@ -38335,7 +38352,7 @@
       <c r="R216" s="3"/>
       <c r="S216" s="3"/>
     </row>
-    <row r="217" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="217" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A217" s="3">
         <v>217</v>
       </c>
@@ -38376,7 +38393,7 @@
       <c r="R217" s="3"/>
       <c r="S217" s="3"/>
     </row>
-    <row r="218" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="218" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A218" s="3">
         <v>218</v>
       </c>
@@ -38417,7 +38434,7 @@
       <c r="R218" s="3"/>
       <c r="S218" s="3"/>
     </row>
-    <row r="219" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="219" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A219" s="3">
         <v>219</v>
       </c>
@@ -38458,7 +38475,7 @@
       <c r="R219" s="3"/>
       <c r="S219" s="3"/>
     </row>
-    <row r="220" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="220" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A220" s="3">
         <v>220</v>
       </c>
@@ -38499,7 +38516,7 @@
       <c r="R220" s="3"/>
       <c r="S220" s="3"/>
     </row>
-    <row r="221" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="221" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A221" s="3">
         <v>221</v>
       </c>
@@ -38540,7 +38557,7 @@
       <c r="R221" s="3"/>
       <c r="S221" s="3"/>
     </row>
-    <row r="222" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="222" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A222" s="3">
         <v>222</v>
       </c>
@@ -38581,7 +38598,7 @@
       <c r="R222" s="3"/>
       <c r="S222" s="3"/>
     </row>
-    <row r="223" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="223" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A223" s="3">
         <v>98</v>
       </c>
@@ -38624,7 +38641,7 @@
       </c>
       <c r="S223" s="3"/>
     </row>
-    <row r="224" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="224" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A224" s="3">
         <v>224</v>
       </c>
@@ -38665,7 +38682,7 @@
       <c r="R224" s="3"/>
       <c r="S224" s="3"/>
     </row>
-    <row r="225" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="225" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A225" s="3">
         <v>225</v>
       </c>
@@ -38708,7 +38725,7 @@
       <c r="R225" s="3"/>
       <c r="S225" s="3"/>
     </row>
-    <row r="226" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="226" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A226" s="3">
         <v>226</v>
       </c>
@@ -38751,7 +38768,7 @@
       <c r="R226" s="3"/>
       <c r="S226" s="3"/>
     </row>
-    <row r="227" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="227" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A227" s="3">
         <v>227</v>
       </c>
@@ -38796,7 +38813,7 @@
       <c r="R227" s="3"/>
       <c r="S227" s="3"/>
     </row>
-    <row r="228" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="228" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A228" s="3">
         <v>228</v>
       </c>
@@ -38841,7 +38858,7 @@
       <c r="R228" s="3"/>
       <c r="S228" s="3"/>
     </row>
-    <row r="229" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="229" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A229" s="3">
         <v>229</v>
       </c>
@@ -38886,7 +38903,7 @@
       <c r="R229" s="3"/>
       <c r="S229" s="3"/>
     </row>
-    <row r="230" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="230" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A230" s="3">
         <v>230</v>
       </c>
@@ -38931,7 +38948,7 @@
       <c r="R230" s="3"/>
       <c r="S230" s="3"/>
     </row>
-    <row r="231" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="231" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A231" s="3">
         <v>231</v>
       </c>
@@ -38976,7 +38993,7 @@
       <c r="R231" s="3"/>
       <c r="S231" s="3"/>
     </row>
-    <row r="232" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="232" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A232" s="3">
         <v>232</v>
       </c>
@@ -39021,7 +39038,7 @@
       <c r="R232" s="3"/>
       <c r="S232" s="3"/>
     </row>
-    <row r="233" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="233" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A233" s="3">
         <v>233</v>
       </c>
@@ -39066,7 +39083,7 @@
       <c r="R233" s="3"/>
       <c r="S233" s="3"/>
     </row>
-    <row r="234" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="234" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A234" s="3">
         <v>234</v>
       </c>
@@ -39111,7 +39128,7 @@
       <c r="R234" s="3"/>
       <c r="S234" s="3"/>
     </row>
-    <row r="235" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="235" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A235" s="3">
         <v>235</v>
       </c>
@@ -39154,7 +39171,7 @@
       <c r="R235" s="3"/>
       <c r="S235" s="3"/>
     </row>
-    <row r="236" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="236" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A236" s="3">
         <v>236</v>
       </c>
@@ -39197,7 +39214,7 @@
       <c r="R236" s="3"/>
       <c r="S236" s="3"/>
     </row>
-    <row r="237" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="237" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A237" s="3">
         <v>237</v>
       </c>
@@ -39289,7 +39306,7 @@
       <c r="R238" s="3"/>
       <c r="S238" s="3"/>
     </row>
-    <row r="239" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="239" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A239" s="3">
         <v>239</v>
       </c>
@@ -39332,7 +39349,7 @@
       <c r="R239" s="3"/>
       <c r="S239" s="3"/>
     </row>
-    <row r="240" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="240" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A240" s="3">
         <v>240</v>
       </c>
@@ -39375,7 +39392,7 @@
       <c r="R240" s="3"/>
       <c r="S240" s="3"/>
     </row>
-    <row r="241" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="241" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A241" s="3">
         <v>241</v>
       </c>
@@ -39420,7 +39437,7 @@
       <c r="R241" s="3"/>
       <c r="S241" s="3"/>
     </row>
-    <row r="242" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="242" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A242" s="3">
         <v>242</v>
       </c>
@@ -39467,7 +39484,7 @@
       <c r="R242" s="3"/>
       <c r="S242" s="3"/>
     </row>
-    <row r="243" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="243" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A243" s="3">
         <v>243</v>
       </c>
@@ -39510,7 +39527,7 @@
       <c r="R243" s="3"/>
       <c r="S243" s="3"/>
     </row>
-    <row r="244" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="244" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A244" s="3">
         <v>244</v>
       </c>
@@ -39555,7 +39572,7 @@
       <c r="R244" s="3"/>
       <c r="S244" s="3"/>
     </row>
-    <row r="245" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="245" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A245" s="3">
         <v>245</v>
       </c>
@@ -39598,7 +39615,7 @@
       <c r="R245" s="3"/>
       <c r="S245" s="3"/>
     </row>
-    <row r="246" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="246" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A246" s="3">
         <v>246</v>
       </c>
@@ -39641,7 +39658,7 @@
       <c r="R246" s="3"/>
       <c r="S246" s="3"/>
     </row>
-    <row r="247" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="247" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A247" s="3">
         <v>247</v>
       </c>
@@ -39684,7 +39701,7 @@
       <c r="R247" s="3"/>
       <c r="S247" s="3"/>
     </row>
-    <row r="248" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="248" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A248" s="3">
         <v>248</v>
       </c>
@@ -39727,7 +39744,7 @@
       <c r="R248" s="3"/>
       <c r="S248" s="3"/>
     </row>
-    <row r="249" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="249" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A249" s="3">
         <v>249</v>
       </c>
@@ -39770,7 +39787,7 @@
       <c r="R249" s="3"/>
       <c r="S249" s="3"/>
     </row>
-    <row r="250" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="250" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A250" s="3">
         <v>250</v>
       </c>
@@ -39813,7 +39830,7 @@
       <c r="R250" s="3"/>
       <c r="S250" s="3"/>
     </row>
-    <row r="251" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="251" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A251" s="3">
         <v>251</v>
       </c>
@@ -39856,7 +39873,7 @@
       <c r="R251" s="3"/>
       <c r="S251" s="3"/>
     </row>
-    <row r="252" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="252" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A252" s="3">
         <v>252</v>
       </c>
@@ -39899,7 +39916,7 @@
       <c r="R252" s="3"/>
       <c r="S252" s="3"/>
     </row>
-    <row r="253" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="253" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A253" s="3">
         <v>253</v>
       </c>
@@ -39944,7 +39961,7 @@
       <c r="R253" s="3"/>
       <c r="S253" s="3"/>
     </row>
-    <row r="254" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="254" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A254" s="3">
         <v>254</v>
       </c>
@@ -39987,7 +40004,7 @@
       <c r="R254" s="3"/>
       <c r="S254" s="3"/>
     </row>
-    <row r="255" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="255" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A255" s="3">
         <v>255</v>
       </c>
@@ -40032,7 +40049,7 @@
       </c>
       <c r="S255" s="3"/>
     </row>
-    <row r="256" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="256" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A256" s="3">
         <v>256</v>
       </c>
@@ -40075,7 +40092,7 @@
       <c r="R256" s="3"/>
       <c r="S256" s="3"/>
     </row>
-    <row r="257" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="257" spans="1:19" ht="15.95" customHeight="1">
       <c r="A257" s="3">
         <v>257</v>
       </c>
@@ -40124,7 +40141,7 @@
       </c>
       <c r="S257" s="3"/>
     </row>
-    <row r="258" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="258" spans="1:19" ht="15.95" customHeight="1">
       <c r="A258" s="3">
         <v>258</v>
       </c>
@@ -40167,7 +40184,7 @@
       <c r="R258" s="3"/>
       <c r="S258" s="3"/>
     </row>
-    <row r="259" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="259" spans="1:19" ht="15.95" customHeight="1">
       <c r="A259" s="3">
         <v>259</v>
       </c>
@@ -40212,7 +40229,7 @@
       <c r="R259" s="3"/>
       <c r="S259" s="3"/>
     </row>
-    <row r="260" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="260" spans="1:19" ht="15.95" customHeight="1">
       <c r="A260" s="3">
         <v>260</v>
       </c>
@@ -40302,7 +40319,7 @@
       <c r="R261" s="3"/>
       <c r="S261" s="3"/>
     </row>
-    <row r="262" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="262" spans="1:19" ht="15.95" customHeight="1">
       <c r="A262" s="3">
         <v>262</v>
       </c>
@@ -40349,7 +40366,7 @@
       <c r="R262" s="3"/>
       <c r="S262" s="3"/>
     </row>
-    <row r="263" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="263" spans="1:19" ht="15.95" customHeight="1">
       <c r="A263" s="3">
         <v>263</v>
       </c>
@@ -40396,7 +40413,7 @@
       </c>
       <c r="S263" s="3"/>
     </row>
-    <row r="264" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="264" spans="1:19" ht="15.95" customHeight="1">
       <c r="A264" s="3">
         <v>264</v>
       </c>
@@ -40486,7 +40503,7 @@
       <c r="R265" s="3"/>
       <c r="S265" s="3"/>
     </row>
-    <row r="266" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="266" spans="1:19" ht="15.95" customHeight="1">
       <c r="A266" s="3">
         <v>266</v>
       </c>
@@ -40533,7 +40550,7 @@
       </c>
       <c r="S266" s="3"/>
     </row>
-    <row r="267" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="267" spans="1:19" ht="15.95" customHeight="1">
       <c r="A267" s="3">
         <v>267</v>
       </c>
@@ -40619,7 +40636,7 @@
       <c r="R268" s="3"/>
       <c r="S268" s="3"/>
     </row>
-    <row r="269" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="269" spans="1:19" ht="15.95" customHeight="1">
       <c r="A269" s="3">
         <v>269</v>
       </c>
@@ -40664,7 +40681,7 @@
       <c r="R269" s="3"/>
       <c r="S269" s="3"/>
     </row>
-    <row r="270" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="270" spans="1:19" ht="15.95" customHeight="1">
       <c r="A270" s="3">
         <v>270</v>
       </c>
@@ -40709,7 +40726,7 @@
       <c r="R270" s="3"/>
       <c r="S270" s="3"/>
     </row>
-    <row r="271" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="271" spans="1:19" ht="15.95" customHeight="1">
       <c r="A271" s="3">
         <v>271</v>
       </c>
@@ -40754,7 +40771,7 @@
       <c r="R271" s="3"/>
       <c r="S271" s="3"/>
     </row>
-    <row r="272" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="272" spans="1:19" ht="15.95" customHeight="1">
       <c r="A272" s="3">
         <v>272</v>
       </c>
@@ -40797,7 +40814,7 @@
       <c r="R272" s="3"/>
       <c r="S272" s="3"/>
     </row>
-    <row r="273" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="273" spans="1:19" ht="15.95" customHeight="1">
       <c r="A273" s="3">
         <v>273</v>
       </c>
@@ -40842,7 +40859,7 @@
       <c r="R273" s="3"/>
       <c r="S273" s="3"/>
     </row>
-    <row r="274" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="274" spans="1:19" ht="15.95" customHeight="1">
       <c r="A274" s="3">
         <v>274</v>
       </c>
@@ -40885,7 +40902,7 @@
       <c r="R274" s="3"/>
       <c r="S274" s="3"/>
     </row>
-    <row r="275" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="275" spans="1:19" ht="15.95" customHeight="1">
       <c r="A275" s="3">
         <v>275</v>
       </c>
@@ -40930,7 +40947,7 @@
       <c r="R275" s="3"/>
       <c r="S275" s="3"/>
     </row>
-    <row r="276" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="276" spans="1:19" ht="15.95" customHeight="1">
       <c r="A276" s="3">
         <v>277</v>
       </c>
@@ -40973,7 +40990,7 @@
       <c r="R276" s="3"/>
       <c r="S276" s="3"/>
     </row>
-    <row r="277" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="277" spans="1:19" ht="15.95" customHeight="1">
       <c r="A277" s="3">
         <v>278</v>
       </c>
@@ -41016,7 +41033,7 @@
       <c r="R277" s="3"/>
       <c r="S277" s="3"/>
     </row>
-    <row r="278" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="278" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A278" s="3">
         <v>279</v>
       </c>
@@ -41059,7 +41076,7 @@
       <c r="R278" s="3"/>
       <c r="S278" s="3"/>
     </row>
-    <row r="279" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="279" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A279" s="3">
         <v>280</v>
       </c>
@@ -41102,7 +41119,7 @@
       <c r="R279" s="3"/>
       <c r="S279" s="3"/>
     </row>
-    <row r="280" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="280" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A280" s="3">
         <v>281</v>
       </c>
@@ -41145,7 +41162,7 @@
       <c r="R280" s="3"/>
       <c r="S280" s="3"/>
     </row>
-    <row r="281" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="281" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A281" s="3">
         <v>282</v>
       </c>
@@ -41188,7 +41205,7 @@
       <c r="R281" s="3"/>
       <c r="S281" s="3"/>
     </row>
-    <row r="282" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="282" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A282" s="3">
         <v>283</v>
       </c>
@@ -41231,7 +41248,7 @@
       <c r="R282" s="3"/>
       <c r="S282" s="3"/>
     </row>
-    <row r="283" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="283" spans="1:19" ht="15.95" customHeight="1">
       <c r="A283" s="3">
         <v>284</v>
       </c>
@@ -41274,7 +41291,7 @@
       <c r="R283" s="3"/>
       <c r="S283" s="3"/>
     </row>
-    <row r="284" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="284" spans="1:19" ht="15.95" customHeight="1">
       <c r="A284" s="3">
         <v>285</v>
       </c>
@@ -41317,7 +41334,7 @@
       <c r="R284" s="3"/>
       <c r="S284" s="3"/>
     </row>
-    <row r="285" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="285" spans="1:19" ht="15.95" customHeight="1">
       <c r="A285" s="3">
         <v>286</v>
       </c>
@@ -41360,7 +41377,7 @@
       <c r="R285" s="3"/>
       <c r="S285" s="3"/>
     </row>
-    <row r="286" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="286" spans="1:19" ht="15.95" customHeight="1">
       <c r="A286" s="3">
         <v>287</v>
       </c>
@@ -41403,7 +41420,7 @@
       <c r="R286" s="3"/>
       <c r="S286" s="3"/>
     </row>
-    <row r="287" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="287" spans="1:19" ht="15.95" customHeight="1">
       <c r="A287" s="3">
         <v>288</v>
       </c>
@@ -41446,7 +41463,7 @@
       <c r="R287" s="3"/>
       <c r="S287" s="3"/>
     </row>
-    <row r="288" spans="1:19" ht="15.95" hidden="1" customHeight="1">
+    <row r="288" spans="1:19" ht="15.95" customHeight="1">
       <c r="A288" s="3">
         <v>289</v>
       </c>
@@ -41489,7 +41506,7 @@
       <c r="R288" s="3"/>
       <c r="S288" s="3"/>
     </row>
-    <row r="289" spans="1:20" ht="15.95" hidden="1" customHeight="1">
+    <row r="289" spans="1:20" ht="15.95" customHeight="1">
       <c r="A289" s="3">
         <v>140</v>
       </c>
@@ -41534,7 +41551,7 @@
       </c>
       <c r="S289" s="3"/>
     </row>
-    <row r="290" spans="1:20" ht="15.95" hidden="1" customHeight="1">
+    <row r="290" spans="1:20" ht="15.95" customHeight="1">
       <c r="A290" s="3">
         <v>291</v>
       </c>
@@ -41577,7 +41594,7 @@
       <c r="R290" s="3"/>
       <c r="S290" s="3"/>
     </row>
-    <row r="291" spans="1:20" ht="15.95" hidden="1" customHeight="1">
+    <row r="291" spans="1:20" ht="15.95" customHeight="1">
       <c r="A291" s="3">
         <v>293</v>
       </c>
@@ -41620,7 +41637,7 @@
       <c r="R291" s="3"/>
       <c r="S291" s="3"/>
     </row>
-    <row r="292" spans="1:20" ht="15.95" hidden="1" customHeight="1">
+    <row r="292" spans="1:20" ht="15.95" customHeight="1">
       <c r="A292" s="3">
         <v>294</v>
       </c>
@@ -41665,7 +41682,7 @@
       <c r="R292" s="3"/>
       <c r="S292" s="3"/>
     </row>
-    <row r="293" spans="1:20" ht="15.95" hidden="1" customHeight="1">
+    <row r="293" spans="1:20" ht="15.95" customHeight="1">
       <c r="A293" s="3">
         <v>295</v>
       </c>
@@ -41710,7 +41727,7 @@
       <c r="R293" s="3"/>
       <c r="S293" s="3"/>
     </row>
-    <row r="294" spans="1:20" ht="15.95" hidden="1" customHeight="1">
+    <row r="294" spans="1:20" ht="15.95" customHeight="1">
       <c r="A294" s="3">
         <v>296</v>
       </c>
@@ -41753,7 +41770,7 @@
       <c r="R294" s="3"/>
       <c r="S294" s="3"/>
     </row>
-    <row r="295" spans="1:20" ht="15.95" hidden="1" customHeight="1">
+    <row r="295" spans="1:20" ht="15.95" customHeight="1">
       <c r="A295" s="3">
         <v>297</v>
       </c>
@@ -41798,7 +41815,7 @@
       <c r="R295" s="3"/>
       <c r="S295" s="3"/>
     </row>
-    <row r="296" spans="1:20" ht="15.95" hidden="1" customHeight="1">
+    <row r="296" spans="1:20" ht="15.95" customHeight="1">
       <c r="A296" s="3">
         <v>299</v>
       </c>
@@ -41841,7 +41858,7 @@
       <c r="R296" s="3"/>
       <c r="S296" s="3"/>
     </row>
-    <row r="297" spans="1:20" ht="15.95" hidden="1" customHeight="1">
+    <row r="297" spans="1:20" ht="15.95" customHeight="1">
       <c r="A297" s="3">
         <v>300</v>
       </c>
@@ -41882,7 +41899,7 @@
       <c r="R297" s="3"/>
       <c r="S297" s="3"/>
     </row>
-    <row r="298" spans="1:20" ht="15.95" hidden="1" customHeight="1">
+    <row r="298" spans="1:20" ht="15.95" customHeight="1">
       <c r="A298" s="3">
         <v>301</v>
       </c>
@@ -41929,7 +41946,7 @@
       <c r="R298" s="3"/>
       <c r="S298" s="3"/>
     </row>
-    <row r="299" spans="1:20" ht="15.95" hidden="1" customHeight="1">
+    <row r="299" spans="1:20" ht="15.95" customHeight="1">
       <c r="A299" s="3">
         <v>302</v>
       </c>
@@ -41974,7 +41991,7 @@
       <c r="R299" s="3"/>
       <c r="S299" s="3"/>
     </row>
-    <row r="300" spans="1:20" ht="15.95" hidden="1" customHeight="1">
+    <row r="300" spans="1:20" ht="15.95" customHeight="1">
       <c r="A300" s="3">
         <v>303</v>
       </c>
@@ -42017,7 +42034,7 @@
       <c r="R300" s="3"/>
       <c r="S300" s="3"/>
     </row>
-    <row r="301" spans="1:20" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="301" spans="1:20" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A301" s="3">
         <v>304</v>
       </c>
@@ -42062,7 +42079,7 @@
       <c r="R301" s="3"/>
       <c r="S301" s="3"/>
     </row>
-    <row r="302" spans="1:20" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="302" spans="1:20" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A302" s="3">
         <v>305</v>
       </c>
@@ -42109,7 +42126,7 @@
       </c>
       <c r="S302" s="3"/>
     </row>
-    <row r="303" spans="1:20" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
+    <row r="303" spans="1:20" s="7" customFormat="1" ht="15.95" customHeight="1">
       <c r="A303" s="3">
         <v>306</v>
       </c>
@@ -42198,7 +42215,7 @@
       <c r="S304" s="16"/>
       <c r="T304" s="17"/>
     </row>
-    <row r="305" spans="1:20" ht="15.95" hidden="1" customHeight="1">
+    <row r="305" spans="1:20" ht="15.95" customHeight="1">
       <c r="A305" s="18">
         <v>308</v>
       </c>
@@ -42246,7 +42263,7 @@
       <c r="S305" s="23"/>
       <c r="T305" s="17"/>
     </row>
-    <row r="306" spans="1:20" ht="15.95" hidden="1" customHeight="1">
+    <row r="306" spans="1:20" ht="15.95" customHeight="1">
       <c r="A306" s="3">
         <v>309</v>
       </c>
@@ -42290,7 +42307,7 @@
       <c r="S306" s="16"/>
       <c r="T306" s="17"/>
     </row>
-    <row r="307" spans="1:20" ht="15.95" hidden="1" customHeight="1">
+    <row r="307" spans="1:20" ht="15.95" customHeight="1">
       <c r="A307" s="3">
         <v>310</v>
       </c>
@@ -42333,7 +42350,7 @@
       <c r="R307" s="16"/>
       <c r="S307" s="16"/>
     </row>
-    <row r="308" spans="1:20" ht="15.95" hidden="1" customHeight="1">
+    <row r="308" spans="1:20" ht="15.95" customHeight="1">
       <c r="A308" s="18">
         <v>311</v>
       </c>
@@ -42376,7 +42393,7 @@
       <c r="R308" s="3"/>
       <c r="S308" s="3"/>
     </row>
-    <row r="309" spans="1:20" ht="15.95" hidden="1" customHeight="1">
+    <row r="309" spans="1:20" ht="15.95" customHeight="1">
       <c r="A309" s="3">
         <v>312</v>
       </c>
@@ -42456,7 +42473,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="311" spans="1:20" ht="15.95" hidden="1" customHeight="1">
+    <row r="311" spans="1:20" ht="15.95" customHeight="1">
       <c r="A311" s="18">
         <v>314</v>
       </c>
@@ -42496,7 +42513,7 @@
       <c r="Q311" s="3"/>
       <c r="R311" s="3"/>
     </row>
-    <row r="312" spans="1:20" ht="15.95" hidden="1" customHeight="1">
+    <row r="312" spans="1:20" ht="15.95" customHeight="1">
       <c r="A312" s="3">
         <v>315</v>
       </c>
@@ -42538,7 +42555,7 @@
       <c r="Q312" s="18"/>
       <c r="R312" s="18"/>
     </row>
-    <row r="313" spans="1:20" ht="15.95" hidden="1" customHeight="1">
+    <row r="313" spans="1:20" ht="15.95" customHeight="1">
       <c r="A313" s="3">
         <v>316</v>
       </c>
@@ -42580,7 +42597,7 @@
       <c r="Q313" s="18"/>
       <c r="R313" s="18"/>
     </row>
-    <row r="314" spans="1:20" ht="15.95" hidden="1" customHeight="1">
+    <row r="314" spans="1:20" ht="15.95" customHeight="1">
       <c r="A314" s="18">
         <v>317</v>
       </c>
@@ -42622,7 +42639,7 @@
       <c r="Q314" s="18"/>
       <c r="R314" s="18"/>
     </row>
-    <row r="315" spans="1:20" ht="15.95" hidden="1" customHeight="1">
+    <row r="315" spans="1:20" ht="15.95" customHeight="1">
       <c r="A315" s="27">
         <v>318</v>
       </c>
@@ -42665,7 +42682,7 @@
       <c r="R315" s="14"/>
       <c r="S315" s="17"/>
     </row>
-    <row r="316" spans="1:20" ht="15.95" hidden="1" customHeight="1">
+    <row r="316" spans="1:20" ht="15.95" customHeight="1">
       <c r="A316" s="3">
         <v>319</v>
       </c>
@@ -42707,7 +42724,7 @@
       <c r="Q316" s="14"/>
       <c r="R316" s="14"/>
     </row>
-    <row r="317" spans="1:20" ht="15.95" hidden="1" customHeight="1">
+    <row r="317" spans="1:20" ht="15.95" customHeight="1">
       <c r="A317" s="18">
         <v>320</v>
       </c>
@@ -42749,7 +42766,7 @@
       <c r="Q317" s="14"/>
       <c r="R317" s="14"/>
     </row>
-    <row r="318" spans="1:20" ht="15.95" hidden="1" customHeight="1">
+    <row r="318" spans="1:20" ht="15.95" customHeight="1">
       <c r="A318" s="27">
         <v>321</v>
       </c>
@@ -42791,7 +42808,7 @@
       <c r="Q318" s="14"/>
       <c r="R318" s="14"/>
     </row>
-    <row r="319" spans="1:20" ht="15.95" hidden="1" customHeight="1">
+    <row r="319" spans="1:20" ht="15.95" customHeight="1">
       <c r="A319" s="3">
         <v>322</v>
       </c>
@@ -42833,7 +42850,7 @@
       <c r="Q319" s="14"/>
       <c r="R319" s="14"/>
     </row>
-    <row r="320" spans="1:20" ht="15.95" hidden="1" customHeight="1">
+    <row r="320" spans="1:20" ht="15.95" customHeight="1">
       <c r="A320" s="18">
         <v>323</v>
       </c>
@@ -42875,7 +42892,7 @@
       <c r="Q320" s="14"/>
       <c r="R320" s="14"/>
     </row>
-    <row r="321" spans="1:20" ht="15.95" hidden="1" customHeight="1">
+    <row r="321" spans="1:20" ht="15.95" customHeight="1">
       <c r="A321" s="27">
         <v>324</v>
       </c>
@@ -42917,7 +42934,7 @@
       <c r="Q321" s="14"/>
       <c r="R321" s="14"/>
     </row>
-    <row r="322" spans="1:20" ht="15.95" hidden="1" customHeight="1">
+    <row r="322" spans="1:20" ht="15.95" customHeight="1">
       <c r="A322" s="3">
         <v>325</v>
       </c>
@@ -43083,7 +43100,7 @@
       <c r="Q325" s="3"/>
       <c r="R325" s="3"/>
     </row>
-    <row r="326" spans="1:20" ht="15.95" hidden="1" customHeight="1">
+    <row r="326" spans="1:20" ht="15.95" customHeight="1">
       <c r="A326" s="18">
         <v>329</v>
       </c>
@@ -43123,7 +43140,7 @@
       <c r="Q326" s="3"/>
       <c r="R326" s="3"/>
     </row>
-    <row r="327" spans="1:20" ht="15.95" hidden="1" customHeight="1">
+    <row r="327" spans="1:20" ht="15.95" customHeight="1">
       <c r="A327" s="18">
         <v>330</v>
       </c>
@@ -43165,7 +43182,7 @@
       <c r="Q327" s="3"/>
       <c r="R327" s="3"/>
     </row>
-    <row r="328" spans="1:20" ht="15.95" hidden="1" customHeight="1">
+    <row r="328" spans="1:20" ht="15.95" customHeight="1">
       <c r="A328" s="18">
         <v>331</v>
       </c>
@@ -43292,7 +43309,7 @@
       <c r="Q330" s="16"/>
       <c r="R330" s="16"/>
     </row>
-    <row r="331" spans="1:20" ht="15.95" hidden="1" customHeight="1">
+    <row r="331" spans="1:20" ht="15.95" customHeight="1">
       <c r="A331" s="3">
         <v>334</v>
       </c>
@@ -43464,7 +43481,7 @@
       <c r="S334" s="23"/>
       <c r="T334" s="17"/>
     </row>
-    <row r="335" spans="1:20" ht="15.95" hidden="1" customHeight="1">
+    <row r="335" spans="1:20" ht="15.95" customHeight="1">
       <c r="A335" s="14">
         <v>338</v>
       </c>
@@ -43508,7 +43525,7 @@
       <c r="S335" s="16"/>
       <c r="T335" s="17"/>
     </row>
-    <row r="336" spans="1:20" ht="15.95" hidden="1" customHeight="1">
+    <row r="336" spans="1:20" ht="15.95" customHeight="1">
       <c r="A336" s="14">
         <v>339</v>
       </c>
@@ -43552,7 +43569,7 @@
       <c r="S336" s="16"/>
       <c r="T336" s="17"/>
     </row>
-    <row r="337" spans="1:21" ht="15.95" hidden="1" customHeight="1">
+    <row r="337" spans="1:21" ht="15.95" customHeight="1">
       <c r="A337" s="14">
         <v>340</v>
       </c>
@@ -43598,7 +43615,7 @@
       <c r="S337" s="23"/>
       <c r="T337" s="17"/>
     </row>
-    <row r="338" spans="1:21" ht="15.95" hidden="1" customHeight="1">
+    <row r="338" spans="1:21" ht="15.95" customHeight="1">
       <c r="A338" s="14">
         <v>341</v>
       </c>
@@ -43642,7 +43659,7 @@
       <c r="S338" s="23"/>
       <c r="T338" s="17"/>
     </row>
-    <row r="339" spans="1:21" ht="15.95" hidden="1" customHeight="1">
+    <row r="339" spans="1:21" ht="15.95" customHeight="1">
       <c r="A339" s="14">
         <v>342</v>
       </c>
@@ -43686,7 +43703,7 @@
       <c r="S339" s="23"/>
       <c r="T339" s="17"/>
     </row>
-    <row r="340" spans="1:21" ht="15.95" hidden="1" customHeight="1">
+    <row r="340" spans="1:21" ht="15.95" customHeight="1">
       <c r="A340" s="14">
         <v>343</v>
       </c>
@@ -43817,7 +43834,7 @@
       <c r="S342" s="16"/>
       <c r="T342" s="17"/>
     </row>
-    <row r="343" spans="1:21" ht="15.95" hidden="1" customHeight="1">
+    <row r="343" spans="1:21" ht="15.95" customHeight="1">
       <c r="A343" s="14">
         <v>346</v>
       </c>
@@ -43859,7 +43876,7 @@
       <c r="Q343" s="23"/>
       <c r="R343" s="17"/>
     </row>
-    <row r="344" spans="1:21" ht="15.95" hidden="1" customHeight="1">
+    <row r="344" spans="1:21" ht="15.95" customHeight="1">
       <c r="A344" s="21">
         <v>347</v>
       </c>
@@ -43902,7 +43919,7 @@
       <c r="R344" s="23"/>
       <c r="S344" s="17"/>
     </row>
-    <row r="345" spans="1:21" ht="15.95" hidden="1" customHeight="1">
+    <row r="345" spans="1:21" ht="15.95" customHeight="1">
       <c r="A345" s="34">
         <v>348</v>
       </c>
@@ -43990,7 +44007,7 @@
       <c r="S346" s="23"/>
       <c r="T346" s="17"/>
     </row>
-    <row r="347" spans="1:21" ht="15.95" hidden="1" customHeight="1">
+    <row r="347" spans="1:21" ht="15.95" customHeight="1">
       <c r="A347" s="21">
         <v>350</v>
       </c>
@@ -44035,7 +44052,7 @@
       <c r="T347" s="16"/>
       <c r="U347" s="17"/>
     </row>
-    <row r="348" spans="1:21" ht="15.95" hidden="1" customHeight="1">
+    <row r="348" spans="1:21" ht="15.95" customHeight="1">
       <c r="A348" s="34">
         <v>351</v>
       </c>
@@ -44080,7 +44097,7 @@
       <c r="T348" s="16"/>
       <c r="U348" s="17"/>
     </row>
-    <row r="349" spans="1:21" ht="15.95" hidden="1" customHeight="1">
+    <row r="349" spans="1:21" ht="15.95" customHeight="1">
       <c r="A349" s="37">
         <v>352</v>
       </c>
@@ -44125,7 +44142,7 @@
       <c r="T349" s="16"/>
       <c r="U349" s="17"/>
     </row>
-    <row r="350" spans="1:21" ht="15.95" hidden="1" customHeight="1">
+    <row r="350" spans="1:21" ht="15.95" customHeight="1">
       <c r="A350" s="21">
         <v>353</v>
       </c>
@@ -44170,7 +44187,7 @@
       <c r="T350" s="16"/>
       <c r="U350" s="17"/>
     </row>
-    <row r="351" spans="1:21" ht="15.95" hidden="1" customHeight="1">
+    <row r="351" spans="1:21" ht="15.95" customHeight="1">
       <c r="A351" s="34">
         <v>354</v>
       </c>
@@ -44215,7 +44232,7 @@
       <c r="T351" s="16"/>
       <c r="U351" s="17"/>
     </row>
-    <row r="352" spans="1:21" ht="15.95" hidden="1" customHeight="1">
+    <row r="352" spans="1:21" ht="15.95" customHeight="1">
       <c r="A352" s="37">
         <v>355</v>
       </c>
@@ -44260,7 +44277,7 @@
       <c r="T352" s="16"/>
       <c r="U352" s="17"/>
     </row>
-    <row r="353" spans="1:21" ht="15.95" hidden="1" customHeight="1">
+    <row r="353" spans="1:21" ht="15.95" customHeight="1">
       <c r="A353" s="37">
         <v>356</v>
       </c>
@@ -44305,7 +44322,7 @@
       <c r="T353" s="16"/>
       <c r="U353" s="17"/>
     </row>
-    <row r="354" spans="1:21" ht="15.95" hidden="1" customHeight="1">
+    <row r="354" spans="1:21" ht="15.95" customHeight="1">
       <c r="A354" s="34">
         <v>357</v>
       </c>
@@ -44349,7 +44366,7 @@
       <c r="S354" s="16"/>
       <c r="T354" s="17"/>
     </row>
-    <row r="355" spans="1:21" ht="15.95" hidden="1" customHeight="1">
+    <row r="355" spans="1:21" ht="15.95" customHeight="1">
       <c r="A355" s="37">
         <v>358</v>
       </c>
@@ -44394,7 +44411,7 @@
       <c r="R355" s="23"/>
       <c r="S355" s="17"/>
     </row>
-    <row r="356" spans="1:21" ht="15.95" hidden="1" customHeight="1">
+    <row r="356" spans="1:21" ht="15.95" customHeight="1">
       <c r="A356" s="21">
         <v>359</v>
       </c>
@@ -44437,7 +44454,7 @@
       <c r="R356" s="23"/>
       <c r="S356" s="17"/>
     </row>
-    <row r="357" spans="1:21" ht="15.95" hidden="1" customHeight="1">
+    <row r="357" spans="1:21" ht="15.95" customHeight="1">
       <c r="A357" s="34">
         <v>360</v>
       </c>
@@ -44480,7 +44497,7 @@
       <c r="R357" s="23"/>
       <c r="S357" s="17"/>
     </row>
-    <row r="358" spans="1:21" ht="15.95" hidden="1" customHeight="1">
+    <row r="358" spans="1:21" ht="15.95" customHeight="1">
       <c r="A358" s="37">
         <v>361</v>
       </c>
@@ -44523,7 +44540,7 @@
       <c r="R358" s="23"/>
       <c r="S358" s="17"/>
     </row>
-    <row r="359" spans="1:21" ht="15.95" hidden="1" customHeight="1">
+    <row r="359" spans="1:21" ht="15.95" customHeight="1">
       <c r="A359" s="34">
         <v>362</v>
       </c>
@@ -44566,7 +44583,7 @@
       <c r="R359" s="16"/>
       <c r="S359" s="17"/>
     </row>
-    <row r="360" spans="1:21" ht="15.95" hidden="1" customHeight="1">
+    <row r="360" spans="1:21" ht="15.95" customHeight="1">
       <c r="A360" s="37">
         <v>363</v>
       </c>
@@ -44609,7 +44626,7 @@
       <c r="R360" s="23"/>
       <c r="S360" s="17"/>
     </row>
-    <row r="361" spans="1:21" ht="15.95" hidden="1" customHeight="1">
+    <row r="361" spans="1:21" ht="15.95" customHeight="1">
       <c r="A361" s="14">
         <v>364</v>
       </c>
@@ -44652,7 +44669,7 @@
       <c r="R361" s="16"/>
       <c r="S361" s="17"/>
     </row>
-    <row r="362" spans="1:21" ht="15.95" hidden="1" customHeight="1">
+    <row r="362" spans="1:21" ht="15.95" customHeight="1">
       <c r="A362" s="21">
         <v>365</v>
       </c>
@@ -44695,7 +44712,7 @@
       <c r="R362" s="23"/>
       <c r="S362" s="17"/>
     </row>
-    <row r="363" spans="1:21" ht="15.95" hidden="1" customHeight="1">
+    <row r="363" spans="1:21" ht="15.95" customHeight="1">
       <c r="A363" s="37">
         <v>366</v>
       </c>
@@ -44738,150 +44755,137 @@
       <c r="R363" s="23"/>
       <c r="S363" s="17"/>
     </row>
-    <row r="364" spans="1:21" ht="15.95" hidden="1" customHeight="1">
-      <c r="A364" s="14">
+    <row r="364" spans="1:21" ht="15.95" customHeight="1">
+      <c r="A364" s="21">
         <v>367</v>
       </c>
-      <c r="B364" s="14" t="s">
+      <c r="B364" s="21" t="s">
         <v>791</v>
       </c>
-      <c r="C364" s="16" t="s">
+      <c r="C364" s="23" t="s">
         <v>238</v>
       </c>
-      <c r="D364" s="16" t="s">
+      <c r="D364" s="23" t="s">
         <v>794</v>
       </c>
-      <c r="E364" s="15" t="s">
+      <c r="E364" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="F364" s="14" t="s">
+      <c r="F364" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="G364" s="16">
+      <c r="G364" s="23">
         <v>7</v>
       </c>
-      <c r="H364" s="39" t="s">
+      <c r="H364" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="I364" s="16" t="s">
+      <c r="I364" s="23" t="s">
         <v>578</v>
       </c>
-      <c r="J364" s="16">
+      <c r="J364" s="23">
         <v>2026</v>
       </c>
-      <c r="K364" s="16"/>
-      <c r="L364" s="14" t="s">
+      <c r="K364" s="23"/>
+      <c r="L364" s="21" t="s">
         <v>795</v>
       </c>
-      <c r="M364" s="16"/>
-      <c r="N364" s="16"/>
-      <c r="O364" s="16"/>
-      <c r="P364" s="16"/>
-      <c r="Q364" s="16"/>
-      <c r="R364" s="16"/>
+      <c r="M364" s="23"/>
+      <c r="N364" s="23"/>
+      <c r="O364" s="23"/>
+      <c r="P364" s="23"/>
+      <c r="Q364" s="23"/>
+      <c r="R364" s="23"/>
       <c r="S364" s="17"/>
     </row>
+    <row r="365" spans="1:21" ht="15.95" customHeight="1">
+      <c r="A365" s="21">
+        <v>368</v>
+      </c>
+      <c r="B365" s="21" t="s">
+        <v>791</v>
+      </c>
+      <c r="C365" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="D365" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="E365" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="F365" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="G365" s="21">
+        <v>6</v>
+      </c>
+      <c r="H365" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I365" s="21" t="s">
+        <v>451</v>
+      </c>
+      <c r="J365" s="21">
+        <v>2026</v>
+      </c>
+      <c r="K365" s="23"/>
+      <c r="L365" s="23"/>
+      <c r="M365" s="23"/>
+      <c r="N365" s="23"/>
+      <c r="O365" s="23"/>
+      <c r="P365" s="23" t="s">
+        <v>796</v>
+      </c>
+      <c r="Q365" s="23"/>
+      <c r="R365" s="23"/>
+      <c r="S365" s="17"/>
+    </row>
+    <row r="366" spans="1:21" ht="15.95" customHeight="1">
+      <c r="A366" s="37">
+        <v>369</v>
+      </c>
+      <c r="B366" s="14" t="s">
+        <v>791</v>
+      </c>
+      <c r="C366" s="14" t="s">
+        <v>549</v>
+      </c>
+      <c r="D366" s="14" t="s">
+        <v>550</v>
+      </c>
+      <c r="E366" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="F366" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G366" s="14">
+        <v>8</v>
+      </c>
+      <c r="H366" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="I366" s="14" t="s">
+        <v>451</v>
+      </c>
+      <c r="J366" s="14">
+        <v>2026</v>
+      </c>
+      <c r="K366" s="16"/>
+      <c r="L366" s="16"/>
+      <c r="M366" s="16"/>
+      <c r="N366" s="16"/>
+      <c r="O366" s="16"/>
+      <c r="P366" s="14" t="s">
+        <v>797</v>
+      </c>
+      <c r="Q366" s="16"/>
+      <c r="R366" s="16"/>
+      <c r="S366" s="17"/>
+    </row>
   </sheetData>
-  <autoFilter xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" ref="A1:T364" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="14">
-      <filters>
-        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-          <mc:Choice Requires="x14">
-            <x14:filter val=" Award of Excellent Performance in Research awarded by the Intellectual Property and Technology Transfer Office (IPTTO), Obafemi Awolowo University, Ile – Ife, Osun State, Nigeria for outstanding achievements in research and exceptional contributions to promoting intellectual property assets in Obafemi Awolowo University."/>
-            <x14:filter val="Academic Citizenship Award"/>
-            <x14:filter val="Affiliate AAS"/>
-            <x14:filter val="Apointed  Research Lead at the Center for the Study of the Economies of Africa (CSEA)"/>
-            <x14:filter val="Appointed Guest Editor of the BMC Health Services Research special collection on HIV-related stigma as a barrier to accessing health care on August 8, 2025."/>
-            <x14:filter val="Appointed Joint Staff (Researcher) at the University of the Witwatersrand Reproductive Health and HIV Institute (Wits RHI), Faculty of Health Sciences, effective August 1, 2025."/>
-            <x14:filter val="Appointment as Hall Fellow_ Clinical Hostel"/>
-            <x14:filter val="Awarded ‘Outstanding German Academic Exchange Service (DAAD) alumnus"/>
-            <x14:filter val="Awarded by the Southwest Nigeria Education Awards as Southwest Nigeria outstanding lecturer of the year 2020"/>
-            <x14:filter val="Awarded the Atlantic Fellowship for Equity in Brain Health at the Global Brain Health Institute (GBHI)"/>
-            <x14:filter val="Awarded the Royal Society of Tropical Medicine anf Hygiene fund. He was also granted a complimentary RSTMH membership for the duration of the three years of the fund which aims to support potential RSTMH members from low- and low-middle income countries by paying awardees’ annual membership subscription for three years."/>
-            <x14:filter val="Awarded the Vice Chancellor’s Research Excellence Award in the category of Best Mid-Career Researcher in the College of Natural Sciences on February 25, 2026, during Makerere University’s 76th graduation ceremony."/>
-            <x14:filter val="Awarded the Vice Chancellor’s Research Excellence Award in the category of Mid-Career Researcher on February 24, 2026, during Makerere University’s 76th graduation ceremony."/>
-            <x14:filter val="Best Abstract Award"/>
-            <x14:filter val="Best Poster presentation at the Joint Annual Scientific Health Conference held in Kampala Uganda from September 23 - 25, 2022."/>
-            <x14:filter val="Claude- leone- Distinguished Scholars Award"/>
-            <x14:filter val="Distinguished Science and Technology Award worth 10.000 USD"/>
-            <x14:filter val="Elected Co-Chair of the African Diplomacy Group of the Global Young Academy  Elected to the Editorial Board of BMC Complementary &amp; Alternative Medicine"/>
-            <x14:filter val="Fellowship - FCS - Training Programme in Orthopaedic surgery (Orthopaedic Surgeon and Fellow of COSECSA)"/>
-            <x14:filter val="He was ranked among the top eight applicants of the Jennifer Ward Oppenheimer (JWO) Research Grant aimed at supporting early career African Scientists"/>
-            <x14:filter val="He was recognized as one of the best PhD student in the faculty of  Health Sciences for the 2023/2024 academic year."/>
-            <x14:filter val="He was selected to join the Emerging Leaders Programme by the World Heart Federation"/>
-            <x14:filter val="I have been awarded a recognition certificate as someone who promoted the CPD program among in-service professionals. The CPD program was about multi-discipline collaboration to manage infectious diseases."/>
-            <x14:filter val="I have received a two-year scholarship to attend a fellowship in epidemiology focused on TB and HIV. I also received a scholarship t attend short online research trainings with the University of Washington"/>
-            <x14:filter val="IADS-Rahamon Bello Award for Best Ph.D Thesis in African and Diaspora Studies-2020"/>
-            <x14:filter val="Iconic Award awarded by The Teen Awareness Movement in recognition of outstanding support for educational development for the less privileged young secondary students. 31st October 2020."/>
-            <x14:filter val="International Association for Dental Research-  South Africa (IADR-SA) Postgraduate divisional award."/>
-            <x14:filter val="ISN Travel Awards to attend the ISN-APSN 2022 meeting in Honolulu, USA from August 28 to September 1, 2022."/>
-            <x14:filter val="MG200Young"/>
-            <x14:filter val="nominated for the prestigious Vice Chancellor's Research Excellence Award 2025. This nomination recognizes his outstanding contributions to research excellence."/>
-            <x14:filter val="Prestigious Postgraduate Degree Award"/>
-            <x14:filter val="Research award. This was a seed grant for family planning and comprehensive abortion care. Offered by the University of Michigan."/>
-            <x14:filter val="she received a commendation award for diligent service from the management board of the hospital"/>
-            <x14:filter val="She was awarded a Postgraduate Certificate in Learning and Teaching in Higher Education (PGCLTHE) during a congregation ceremony held at the University of Rwanda on October 17, 2025. The certification recognizes her  commitment to enhancing teaching excellence and promoting innovative learning approaches in higher education."/>
-            <x14:filter val="she was inducted as a fellow of the International College of Dentists (FICD), an international recognition of her professional excellence, ethical standards, and commitment to improving oral health globally."/>
-            <x14:filter val="she was inducted as a fellow of the Nigerian Academy of Medicine (FNAMed), joining a distinguished body of experts dedicated to advancing medical research, shaping health policy, and mentoring the next generation of leaders in medicine and health."/>
-            <x14:filter val="Special recognition award of the World Glaucoma Association"/>
-            <x14:filter val="Top 25 World Heart Federation (WHF) Salim Yusuf Emerging Leaders."/>
-            <x14:filter val="Transition Award Professional Development [TAPROD] Program"/>
-            <x14:filter val="was appointed an Associate Fellow of interRAI, a collaborative network of researchers in over 35 countries committed to improving health care for vulnerable populations with complex needs on June 6, 2024. InterRAI aims to promote evidence-informed clinical practice and policy decisions by collecting and interpreting high-quality data about the characteristics and outcomes of persons served across various health and social services setting"/>
-            <x14:filter val="Was awarded a Senior Fellowship in Global Health Communications Leadership for 2025 - 2026 on July 14, 2025, by the Center for Communications Leadership and Policy (CCLP)"/>
-            <x14:filter val="Was selected as one of four recipients of this year’s Uganda Textbook Academic and Non-Fiction Authors’ Association (UTANA) Grant Scheme Award to complete and publish his book titled ‘A handbook on medicinal plants and HIV/AIDS’"/>
-            <x14:filter val="Winner of Vice Chancellor's Transformation Award (in the team category) at the University of the Witwatersrand"/>
-            <x14:filter val="Winning Poster"/>
-            <x14:filter val="Won the most supportive lecturer award for the 2019-2021 academic session, from the Library, Archival and Information Studies Students Association at the University of Ibadan."/>
-            <x14:filter val="Young Investigator Fellowship for the 19th International Congress of the International Society of Ethnopharmacology"/>
-          </mc:Choice>
-          <mc:Fallback>
-            <filter val="Academic Citizenship Award"/>
-            <filter val="Affiliate AAS"/>
-            <filter val="Apointed  Research Lead at the Center for the Study of the Economies of Africa (CSEA)"/>
-            <filter val="Appointed Guest Editor of the BMC Health Services Research special collection on HIV-related stigma as a barrier to accessing health care on August 8, 2025."/>
-            <filter val="Appointed Joint Staff (Researcher) at the University of the Witwatersrand Reproductive Health and HIV Institute (Wits RHI), Faculty of Health Sciences, effective August 1, 2025."/>
-            <filter val="Appointment as Hall Fellow_ Clinical Hostel"/>
-            <filter val="Awarded ‘Outstanding German Academic Exchange Service (DAAD) alumnus"/>
-            <filter val="Awarded by the Southwest Nigeria Education Awards as Southwest Nigeria outstanding lecturer of the year 2020"/>
-            <filter val="Awarded the Atlantic Fellowship for Equity in Brain Health at the Global Brain Health Institute (GBHI)"/>
-            <filter val="Awarded the Vice Chancellor’s Research Excellence Award in the category of Best Mid-Career Researcher in the College of Natural Sciences on February 25, 2026, during Makerere University’s 76th graduation ceremony."/>
-            <filter val="Awarded the Vice Chancellor’s Research Excellence Award in the category of Mid-Career Researcher on February 24, 2026, during Makerere University’s 76th graduation ceremony."/>
-            <filter val="Best Abstract Award"/>
-            <filter val="Best Poster presentation at the Joint Annual Scientific Health Conference held in Kampala Uganda from September 23 - 25, 2022."/>
-            <filter val="Claude- leone- Distinguished Scholars Award"/>
-            <filter val="Distinguished Science and Technology Award worth 10.000 USD"/>
-            <filter val="Elected Co-Chair of the African Diplomacy Group of the Global Young Academy  Elected to the Editorial Board of BMC Complementary &amp; Alternative Medicine"/>
-            <filter val="Fellowship - FCS - Training Programme in Orthopaedic surgery (Orthopaedic Surgeon and Fellow of COSECSA)"/>
-            <filter val="He was ranked among the top eight applicants of the Jennifer Ward Oppenheimer (JWO) Research Grant aimed at supporting early career African Scientists"/>
-            <filter val="He was recognized as one of the best PhD student in the faculty of  Health Sciences for the 2023/2024 academic year."/>
-            <filter val="He was selected to join the Emerging Leaders Programme by the World Heart Federation"/>
-            <filter val="I have been awarded a recognition certificate as someone who promoted the CPD program among in-service professionals. The CPD program was about multi-discipline collaboration to manage infectious diseases."/>
-            <filter val="I have received a two-year scholarship to attend a fellowship in epidemiology focused on TB and HIV. I also received a scholarship t attend short online research trainings with the University of Washington"/>
-            <filter val="IADS-Rahamon Bello Award for Best Ph.D Thesis in African and Diaspora Studies-2020"/>
-            <filter val="Iconic Award awarded by The Teen Awareness Movement in recognition of outstanding support for educational development for the less privileged young secondary students. 31st October 2020."/>
-            <filter val="International Association for Dental Research-  South Africa (IADR-SA) Postgraduate divisional award."/>
-            <filter val="ISN Travel Awards to attend the ISN-APSN 2022 meeting in Honolulu, USA from August 28 to September 1, 2022."/>
-            <filter val="MG200Young"/>
-            <filter val="nominated for the prestigious Vice Chancellor's Research Excellence Award 2025. This nomination recognizes his outstanding contributions to research excellence."/>
-            <filter val="Prestigious Postgraduate Degree Award"/>
-            <filter val="Research award. This was a seed grant for family planning and comprehensive abortion care. Offered by the University of Michigan."/>
-            <filter val="she received a commendation award for diligent service from the management board of the hospital"/>
-            <filter val="she was inducted as a fellow of the International College of Dentists (FICD), an international recognition of her professional excellence, ethical standards, and commitment to improving oral health globally."/>
-            <filter val="she was inducted as a fellow of the Nigerian Academy of Medicine (FNAMed), joining a distinguished body of experts dedicated to advancing medical research, shaping health policy, and mentoring the next generation of leaders in medicine and health."/>
-            <filter val="Special recognition award of the World Glaucoma Association"/>
-            <filter val="Top 25 World Heart Federation (WHF) Salim Yusuf Emerging Leaders."/>
-            <filter val="Transition Award Professional Development [TAPROD] Program"/>
-            <filter val="Was awarded a Senior Fellowship in Global Health Communications Leadership for 2025 - 2026 on July 14, 2025, by the Center for Communications Leadership and Policy (CCLP)"/>
-            <filter val="Was selected as one of four recipients of this year’s Uganda Textbook Academic and Non-Fiction Authors’ Association (UTANA) Grant Scheme Award to complete and publish his book titled ‘A handbook on medicinal plants and HIV/AIDS’"/>
-            <filter val="Winner of Vice Chancellor's Transformation Award (in the team category) at the University of the Witwatersrand"/>
-            <filter val="Winning Poster"/>
-            <filter val="Won the most supportive lecturer award for the 2019-2021 academic session, from the Library, Archival and Information Studies Students Association at the University of Ibadan."/>
-            <filter val="Young Investigator Fellowship for the 19th International Congress of the International Society of Ethnopharmacology"/>
-          </mc:Fallback>
-        </mc:AlternateContent>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:T366" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
     <hyperlink ref="D273" r:id="rId1" xr:uid="{8A734EB4-5543-4AA7-920A-16AF9B04BD29}"/>
     <hyperlink ref="D275" r:id="rId2" xr:uid="{48CC1384-5BA5-4E70-93B7-12C03EB7E8CB}"/>
@@ -44917,12 +44921,12 @@
         <v>9</v>
       </c>
       <c r="B1" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="13" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>4</v>
@@ -44939,7 +44943,7 @@
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -44983,7 +44987,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="B8">
         <v>2</v>
@@ -44994,7 +44998,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="B9">
         <v>114</v>
@@ -45011,7 +45015,7 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -45030,7 +45034,7 @@
         <v>36</v>
       </c>
       <c r="H17" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -45044,7 +45048,7 @@
         <v>28</v>
       </c>
       <c r="E18" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="F18" t="s">
         <v>57</v>
@@ -45055,7 +45059,7 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -45215,13 +45219,13 @@
         <v>13</v>
       </c>
       <c r="B1" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D1" s="13" t="s">
         <v>11</v>
       </c>
       <c r="E1" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -45229,13 +45233,13 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D2" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -45243,7 +45247,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="C4">
         <f>COUNTA(A4:A93)</f>
@@ -45253,7 +45257,7 @@
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -46800,10 +46804,10 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D137" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -46896,13 +46900,13 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="B146">
         <v>162</v>
       </c>
       <c r="D146" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="E146">
         <v>91</v>
@@ -46925,7 +46929,7 @@
   <sheetData>
     <row r="2" spans="2:2">
       <c r="B2" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
   </sheetData>
@@ -46995,13 +46999,13 @@
         <v>15</v>
       </c>
       <c r="B1" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>14</v>
       </c>
       <c r="D1" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -47009,13 +47013,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="C3" s="13" t="s">
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -47390,7 +47394,7 @@
         <v>2</v>
       </c>
       <c r="C30" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="D30">
         <v>32</v>
@@ -47430,7 +47434,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="B35">
         <v>47</v>

--- a/data/Recognitions_latest.xlsx
+++ b/data/Recognitions_latest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aphrcorg-my.sharepoint.com/personal/nnjenga_aphrc_org/Documents/CARTA Dashboard/ECRS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="746" documentId="13_ncr:1_{74C5384D-9D49-4106-BD43-FCAED859190D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4810BA06-6DCB-4B0B-9070-65E5FDBD30E7}"/>
+  <xr:revisionPtr revIDLastSave="755" documentId="13_ncr:1_{74C5384D-9D49-4106-BD43-FCAED859190D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6997F9E1-9AD9-4AB1-94B5-D0D96AB3A1B2}"/>
   <bookViews>
     <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,10 +24,10 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="330" r:id="rId6"/>
-    <pivotCache cacheId="331" r:id="rId7"/>
-    <pivotCache cacheId="332" r:id="rId8"/>
-    <pivotCache cacheId="333" r:id="rId9"/>
+    <pivotCache cacheId="471" r:id="rId6"/>
+    <pivotCache cacheId="472" r:id="rId7"/>
+    <pivotCache cacheId="473" r:id="rId8"/>
+    <pivotCache cacheId="474" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -121,7 +121,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3080" uniqueCount="808">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3088" uniqueCount="809">
   <si>
     <t>No</t>
   </si>
@@ -2520,6 +2520,9 @@
   </si>
   <si>
     <t>Appointed Extraordinary Research Fellow at the Africa Center for Inclusive Health Management at Stellenbosch University, South Africa, from July 1, 2026, to June 30, 2029. I</t>
+  </si>
+  <si>
+    <t>Appointed Director, Ifakara Health Institute</t>
   </si>
   <si>
     <t>(All)</t>
@@ -26972,106 +26975,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{55E369D5-46AA-45F8-B4A0-AC6C0CED6464}" name="PivotTable2" cacheId="330" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="A3:D9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="16">
-    <pivotField dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField axis="axisCol" compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item m="1" x="2"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="5">
-        <item x="0"/>
-        <item m="1" x="4"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" defaultSubtotal="0">
-      <items count="9">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="1"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="3"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="8" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Count of No" fld="0" subtotal="count" baseField="4" baseItem="3"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{414D3242-6D58-4EC3-BE1F-E4596803BECC}" name="PivotTable10" cacheId="330" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{414D3242-6D58-4EC3-BE1F-E4596803BECC}" name="PivotTable10" cacheId="471" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A16:H19" firstHeaderRow="1" firstDataRow="3" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="16">
     <pivotField dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -27213,8 +27117,815 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{55E369D5-46AA-45F8-B4A0-AC6C0CED6464}" name="PivotTable2" cacheId="471" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A3:D9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="16">
+    <pivotField dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisCol" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item m="1" x="2"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="5">
+        <item x="0"/>
+        <item m="1" x="4"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" defaultSubtotal="0">
+      <items count="9">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="1"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="3"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="8" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Count of No" fld="0" subtotal="count" baseField="4" baseItem="3"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C759C715-A218-40D6-B8AD-8DD0CC6815DF}" name="PivotTable1" cacheId="333" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{90770DB3-F829-4E9E-88FA-FB5C22EB6463}" name="PivotTable2" cacheId="473" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="D4:E146" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="18">
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="142">
+        <item x="57"/>
+        <item x="116"/>
+        <item x="10"/>
+        <item x="27"/>
+        <item x="88"/>
+        <item x="19"/>
+        <item x="14"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="125"/>
+        <item x="128"/>
+        <item x="121"/>
+        <item x="41"/>
+        <item x="80"/>
+        <item x="93"/>
+        <item x="81"/>
+        <item x="111"/>
+        <item x="82"/>
+        <item x="49"/>
+        <item x="48"/>
+        <item x="68"/>
+        <item x="107"/>
+        <item x="83"/>
+        <item x="42"/>
+        <item x="97"/>
+        <item x="5"/>
+        <item x="11"/>
+        <item x="8"/>
+        <item x="35"/>
+        <item x="25"/>
+        <item x="99"/>
+        <item x="32"/>
+        <item x="22"/>
+        <item x="9"/>
+        <item x="13"/>
+        <item x="126"/>
+        <item x="54"/>
+        <item x="28"/>
+        <item x="53"/>
+        <item x="21"/>
+        <item x="84"/>
+        <item x="20"/>
+        <item x="12"/>
+        <item x="1"/>
+        <item x="86"/>
+        <item x="102"/>
+        <item x="127"/>
+        <item x="30"/>
+        <item x="43"/>
+        <item x="85"/>
+        <item x="112"/>
+        <item x="62"/>
+        <item x="50"/>
+        <item x="98"/>
+        <item x="36"/>
+        <item x="106"/>
+        <item x="17"/>
+        <item x="6"/>
+        <item x="122"/>
+        <item x="52"/>
+        <item x="104"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="18"/>
+        <item x="26"/>
+        <item x="103"/>
+        <item x="31"/>
+        <item x="89"/>
+        <item x="118"/>
+        <item x="2"/>
+        <item x="16"/>
+        <item x="55"/>
+        <item x="58"/>
+        <item x="114"/>
+        <item x="33"/>
+        <item x="87"/>
+        <item x="113"/>
+        <item x="69"/>
+        <item x="51"/>
+        <item x="59"/>
+        <item x="101"/>
+        <item x="34"/>
+        <item x="109"/>
+        <item x="61"/>
+        <item x="132"/>
+        <item x="56"/>
+        <item x="64"/>
+        <item x="117"/>
+        <item x="63"/>
+        <item x="100"/>
+        <item x="124"/>
+        <item x="108"/>
+        <item x="115"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="4"/>
+        <item x="15"/>
+        <item x="65"/>
+        <item x="44"/>
+        <item x="119"/>
+        <item x="105"/>
+        <item x="66"/>
+        <item x="120"/>
+        <item x="123"/>
+        <item x="45"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="39"/>
+        <item x="73"/>
+        <item x="110"/>
+        <item x="46"/>
+        <item x="94"/>
+        <item x="74"/>
+        <item x="29"/>
+        <item x="75"/>
+        <item x="90"/>
+        <item x="67"/>
+        <item x="76"/>
+        <item x="38"/>
+        <item x="91"/>
+        <item x="37"/>
+        <item x="40"/>
+        <item x="60"/>
+        <item x="95"/>
+        <item x="77"/>
+        <item x="47"/>
+        <item x="78"/>
+        <item x="131"/>
+        <item x="96"/>
+        <item x="92"/>
+        <item x="79"/>
+        <item x="0"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
+      <items count="12">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="1"/>
+        <item x="10"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="69">
+        <item x="57"/>
+        <item x="56"/>
+        <item x="55"/>
+        <item x="39"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="43"/>
+        <item x="20"/>
+        <item x="35"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="50"/>
+        <item x="23"/>
+        <item x="16"/>
+        <item x="52"/>
+        <item x="30"/>
+        <item x="12"/>
+        <item x="24"/>
+        <item x="63"/>
+        <item x="31"/>
+        <item x="17"/>
+        <item x="28"/>
+        <item x="37"/>
+        <item x="48"/>
+        <item x="13"/>
+        <item x="32"/>
+        <item x="51"/>
+        <item x="22"/>
+        <item x="36"/>
+        <item x="54"/>
+        <item x="49"/>
+        <item x="18"/>
+        <item x="53"/>
+        <item x="19"/>
+        <item x="26"/>
+        <item x="45"/>
+        <item x="64"/>
+        <item x="42"/>
+        <item x="62"/>
+        <item x="29"/>
+        <item x="38"/>
+        <item x="15"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="44"/>
+        <item x="21"/>
+        <item x="25"/>
+        <item x="27"/>
+        <item x="41"/>
+        <item x="61"/>
+        <item x="58"/>
+        <item x="60"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="40"/>
+        <item x="1"/>
+        <item x="14"/>
+        <item x="59"/>
+        <item x="0"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="142">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="26"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="29"/>
+    </i>
+    <i>
+      <x v="30"/>
+    </i>
+    <i>
+      <x v="31"/>
+    </i>
+    <i>
+      <x v="32"/>
+    </i>
+    <i>
+      <x v="33"/>
+    </i>
+    <i>
+      <x v="34"/>
+    </i>
+    <i>
+      <x v="35"/>
+    </i>
+    <i>
+      <x v="36"/>
+    </i>
+    <i>
+      <x v="37"/>
+    </i>
+    <i>
+      <x v="38"/>
+    </i>
+    <i>
+      <x v="39"/>
+    </i>
+    <i>
+      <x v="40"/>
+    </i>
+    <i>
+      <x v="41"/>
+    </i>
+    <i>
+      <x v="42"/>
+    </i>
+    <i>
+      <x v="43"/>
+    </i>
+    <i>
+      <x v="44"/>
+    </i>
+    <i>
+      <x v="45"/>
+    </i>
+    <i>
+      <x v="46"/>
+    </i>
+    <i>
+      <x v="47"/>
+    </i>
+    <i>
+      <x v="48"/>
+    </i>
+    <i>
+      <x v="49"/>
+    </i>
+    <i>
+      <x v="50"/>
+    </i>
+    <i>
+      <x v="51"/>
+    </i>
+    <i>
+      <x v="52"/>
+    </i>
+    <i>
+      <x v="53"/>
+    </i>
+    <i>
+      <x v="54"/>
+    </i>
+    <i>
+      <x v="55"/>
+    </i>
+    <i>
+      <x v="56"/>
+    </i>
+    <i>
+      <x v="57"/>
+    </i>
+    <i>
+      <x v="58"/>
+    </i>
+    <i>
+      <x v="59"/>
+    </i>
+    <i>
+      <x v="60"/>
+    </i>
+    <i>
+      <x v="61"/>
+    </i>
+    <i>
+      <x v="62"/>
+    </i>
+    <i>
+      <x v="63"/>
+    </i>
+    <i>
+      <x v="64"/>
+    </i>
+    <i>
+      <x v="65"/>
+    </i>
+    <i>
+      <x v="66"/>
+    </i>
+    <i>
+      <x v="67"/>
+    </i>
+    <i>
+      <x v="68"/>
+    </i>
+    <i>
+      <x v="69"/>
+    </i>
+    <i>
+      <x v="70"/>
+    </i>
+    <i>
+      <x v="71"/>
+    </i>
+    <i>
+      <x v="72"/>
+    </i>
+    <i>
+      <x v="73"/>
+    </i>
+    <i>
+      <x v="74"/>
+    </i>
+    <i>
+      <x v="75"/>
+    </i>
+    <i>
+      <x v="76"/>
+    </i>
+    <i>
+      <x v="77"/>
+    </i>
+    <i>
+      <x v="78"/>
+    </i>
+    <i>
+      <x v="79"/>
+    </i>
+    <i>
+      <x v="80"/>
+    </i>
+    <i>
+      <x v="81"/>
+    </i>
+    <i>
+      <x v="82"/>
+    </i>
+    <i>
+      <x v="83"/>
+    </i>
+    <i>
+      <x v="84"/>
+    </i>
+    <i>
+      <x v="85"/>
+    </i>
+    <i>
+      <x v="86"/>
+    </i>
+    <i>
+      <x v="87"/>
+    </i>
+    <i>
+      <x v="88"/>
+    </i>
+    <i>
+      <x v="89"/>
+    </i>
+    <i>
+      <x v="90"/>
+    </i>
+    <i>
+      <x v="91"/>
+    </i>
+    <i>
+      <x v="92"/>
+    </i>
+    <i>
+      <x v="93"/>
+    </i>
+    <i>
+      <x v="94"/>
+    </i>
+    <i>
+      <x v="95"/>
+    </i>
+    <i>
+      <x v="96"/>
+    </i>
+    <i>
+      <x v="97"/>
+    </i>
+    <i>
+      <x v="98"/>
+    </i>
+    <i>
+      <x v="99"/>
+    </i>
+    <i>
+      <x v="100"/>
+    </i>
+    <i>
+      <x v="101"/>
+    </i>
+    <i>
+      <x v="102"/>
+    </i>
+    <i>
+      <x v="103"/>
+    </i>
+    <i>
+      <x v="104"/>
+    </i>
+    <i>
+      <x v="105"/>
+    </i>
+    <i>
+      <x v="106"/>
+    </i>
+    <i>
+      <x v="107"/>
+    </i>
+    <i>
+      <x v="108"/>
+    </i>
+    <i>
+      <x v="109"/>
+    </i>
+    <i>
+      <x v="110"/>
+    </i>
+    <i>
+      <x v="111"/>
+    </i>
+    <i>
+      <x v="112"/>
+    </i>
+    <i>
+      <x v="113"/>
+    </i>
+    <i>
+      <x v="114"/>
+    </i>
+    <i>
+      <x v="115"/>
+    </i>
+    <i>
+      <x v="116"/>
+    </i>
+    <i>
+      <x v="117"/>
+    </i>
+    <i>
+      <x v="118"/>
+    </i>
+    <i>
+      <x v="119"/>
+    </i>
+    <i>
+      <x v="120"/>
+    </i>
+    <i>
+      <x v="121"/>
+    </i>
+    <i>
+      <x v="122"/>
+    </i>
+    <i>
+      <x v="123"/>
+    </i>
+    <i>
+      <x v="124"/>
+    </i>
+    <i>
+      <x v="125"/>
+    </i>
+    <i>
+      <x v="126"/>
+    </i>
+    <i>
+      <x v="127"/>
+    </i>
+    <i>
+      <x v="128"/>
+    </i>
+    <i>
+      <x v="129"/>
+    </i>
+    <i>
+      <x v="130"/>
+    </i>
+    <i>
+      <x v="131"/>
+    </i>
+    <i>
+      <x v="132"/>
+    </i>
+    <i>
+      <x v="133"/>
+    </i>
+    <i>
+      <x v="134"/>
+    </i>
+    <i>
+      <x v="135"/>
+    </i>
+    <i>
+      <x v="136"/>
+    </i>
+    <i>
+      <x v="137"/>
+    </i>
+    <i>
+      <x v="138"/>
+    </i>
+    <i>
+      <x v="139"/>
+    </i>
+    <i>
+      <x v="140"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="11" hier="-1"/>
+    <pageField fld="9" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Count of Promotion" fld="11" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C759C715-A218-40D6-B8AD-8DD0CC6815DF}" name="PivotTable1" cacheId="474" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:B146" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="18">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -27996,1021 +28707,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{90770DB3-F829-4E9E-88FA-FB5C22EB6463}" name="PivotTable2" cacheId="332" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="D4:E146" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="18">
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="142">
-        <item x="57"/>
-        <item x="116"/>
-        <item x="10"/>
-        <item x="27"/>
-        <item x="88"/>
-        <item x="19"/>
-        <item x="14"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="125"/>
-        <item x="128"/>
-        <item x="121"/>
-        <item x="41"/>
-        <item x="80"/>
-        <item x="93"/>
-        <item x="81"/>
-        <item x="111"/>
-        <item x="82"/>
-        <item x="49"/>
-        <item x="48"/>
-        <item x="68"/>
-        <item x="107"/>
-        <item x="83"/>
-        <item x="42"/>
-        <item x="97"/>
-        <item x="5"/>
-        <item x="11"/>
-        <item x="8"/>
-        <item x="35"/>
-        <item x="25"/>
-        <item x="99"/>
-        <item x="32"/>
-        <item x="22"/>
-        <item x="9"/>
-        <item x="13"/>
-        <item x="126"/>
-        <item x="54"/>
-        <item x="28"/>
-        <item x="53"/>
-        <item x="21"/>
-        <item x="84"/>
-        <item x="20"/>
-        <item x="12"/>
-        <item x="1"/>
-        <item x="86"/>
-        <item x="102"/>
-        <item x="127"/>
-        <item x="30"/>
-        <item x="43"/>
-        <item x="85"/>
-        <item x="112"/>
-        <item x="62"/>
-        <item x="50"/>
-        <item x="98"/>
-        <item x="36"/>
-        <item x="106"/>
-        <item x="17"/>
-        <item x="6"/>
-        <item x="122"/>
-        <item x="52"/>
-        <item x="104"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="18"/>
-        <item x="26"/>
-        <item x="103"/>
-        <item x="31"/>
-        <item x="89"/>
-        <item x="118"/>
-        <item x="2"/>
-        <item x="16"/>
-        <item x="55"/>
-        <item x="58"/>
-        <item x="114"/>
-        <item x="33"/>
-        <item x="87"/>
-        <item x="113"/>
-        <item x="69"/>
-        <item x="51"/>
-        <item x="59"/>
-        <item x="101"/>
-        <item x="34"/>
-        <item x="109"/>
-        <item x="61"/>
-        <item x="132"/>
-        <item x="56"/>
-        <item x="64"/>
-        <item x="117"/>
-        <item x="63"/>
-        <item x="100"/>
-        <item x="124"/>
-        <item x="108"/>
-        <item x="115"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="4"/>
-        <item x="15"/>
-        <item x="65"/>
-        <item x="44"/>
-        <item x="119"/>
-        <item x="105"/>
-        <item x="66"/>
-        <item x="120"/>
-        <item x="123"/>
-        <item x="45"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="39"/>
-        <item x="73"/>
-        <item x="110"/>
-        <item x="46"/>
-        <item x="94"/>
-        <item x="74"/>
-        <item x="29"/>
-        <item x="75"/>
-        <item x="90"/>
-        <item x="67"/>
-        <item x="76"/>
-        <item x="38"/>
-        <item x="91"/>
-        <item x="37"/>
-        <item x="40"/>
-        <item x="60"/>
-        <item x="95"/>
-        <item x="77"/>
-        <item x="47"/>
-        <item x="78"/>
-        <item x="131"/>
-        <item x="96"/>
-        <item x="92"/>
-        <item x="79"/>
-        <item x="0"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
-      <items count="12">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="9"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="1"/>
-        <item x="10"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisPage" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="69">
-        <item x="57"/>
-        <item x="56"/>
-        <item x="55"/>
-        <item x="39"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="43"/>
-        <item x="20"/>
-        <item x="35"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="50"/>
-        <item x="23"/>
-        <item x="16"/>
-        <item x="52"/>
-        <item x="30"/>
-        <item x="12"/>
-        <item x="24"/>
-        <item x="63"/>
-        <item x="31"/>
-        <item x="17"/>
-        <item x="28"/>
-        <item x="37"/>
-        <item x="48"/>
-        <item x="13"/>
-        <item x="32"/>
-        <item x="51"/>
-        <item x="22"/>
-        <item x="36"/>
-        <item x="54"/>
-        <item x="49"/>
-        <item x="18"/>
-        <item x="53"/>
-        <item x="19"/>
-        <item x="26"/>
-        <item x="45"/>
-        <item x="64"/>
-        <item x="42"/>
-        <item x="62"/>
-        <item x="29"/>
-        <item x="38"/>
-        <item x="15"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="44"/>
-        <item x="21"/>
-        <item x="25"/>
-        <item x="27"/>
-        <item x="41"/>
-        <item x="61"/>
-        <item x="58"/>
-        <item x="60"/>
-        <item x="6"/>
-        <item x="9"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="11"/>
-        <item x="10"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="40"/>
-        <item x="1"/>
-        <item x="14"/>
-        <item x="59"/>
-        <item x="0"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="142">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="19"/>
-    </i>
-    <i>
-      <x v="20"/>
-    </i>
-    <i>
-      <x v="21"/>
-    </i>
-    <i>
-      <x v="22"/>
-    </i>
-    <i>
-      <x v="23"/>
-    </i>
-    <i>
-      <x v="24"/>
-    </i>
-    <i>
-      <x v="25"/>
-    </i>
-    <i>
-      <x v="26"/>
-    </i>
-    <i>
-      <x v="27"/>
-    </i>
-    <i>
-      <x v="28"/>
-    </i>
-    <i>
-      <x v="29"/>
-    </i>
-    <i>
-      <x v="30"/>
-    </i>
-    <i>
-      <x v="31"/>
-    </i>
-    <i>
-      <x v="32"/>
-    </i>
-    <i>
-      <x v="33"/>
-    </i>
-    <i>
-      <x v="34"/>
-    </i>
-    <i>
-      <x v="35"/>
-    </i>
-    <i>
-      <x v="36"/>
-    </i>
-    <i>
-      <x v="37"/>
-    </i>
-    <i>
-      <x v="38"/>
-    </i>
-    <i>
-      <x v="39"/>
-    </i>
-    <i>
-      <x v="40"/>
-    </i>
-    <i>
-      <x v="41"/>
-    </i>
-    <i>
-      <x v="42"/>
-    </i>
-    <i>
-      <x v="43"/>
-    </i>
-    <i>
-      <x v="44"/>
-    </i>
-    <i>
-      <x v="45"/>
-    </i>
-    <i>
-      <x v="46"/>
-    </i>
-    <i>
-      <x v="47"/>
-    </i>
-    <i>
-      <x v="48"/>
-    </i>
-    <i>
-      <x v="49"/>
-    </i>
-    <i>
-      <x v="50"/>
-    </i>
-    <i>
-      <x v="51"/>
-    </i>
-    <i>
-      <x v="52"/>
-    </i>
-    <i>
-      <x v="53"/>
-    </i>
-    <i>
-      <x v="54"/>
-    </i>
-    <i>
-      <x v="55"/>
-    </i>
-    <i>
-      <x v="56"/>
-    </i>
-    <i>
-      <x v="57"/>
-    </i>
-    <i>
-      <x v="58"/>
-    </i>
-    <i>
-      <x v="59"/>
-    </i>
-    <i>
-      <x v="60"/>
-    </i>
-    <i>
-      <x v="61"/>
-    </i>
-    <i>
-      <x v="62"/>
-    </i>
-    <i>
-      <x v="63"/>
-    </i>
-    <i>
-      <x v="64"/>
-    </i>
-    <i>
-      <x v="65"/>
-    </i>
-    <i>
-      <x v="66"/>
-    </i>
-    <i>
-      <x v="67"/>
-    </i>
-    <i>
-      <x v="68"/>
-    </i>
-    <i>
-      <x v="69"/>
-    </i>
-    <i>
-      <x v="70"/>
-    </i>
-    <i>
-      <x v="71"/>
-    </i>
-    <i>
-      <x v="72"/>
-    </i>
-    <i>
-      <x v="73"/>
-    </i>
-    <i>
-      <x v="74"/>
-    </i>
-    <i>
-      <x v="75"/>
-    </i>
-    <i>
-      <x v="76"/>
-    </i>
-    <i>
-      <x v="77"/>
-    </i>
-    <i>
-      <x v="78"/>
-    </i>
-    <i>
-      <x v="79"/>
-    </i>
-    <i>
-      <x v="80"/>
-    </i>
-    <i>
-      <x v="81"/>
-    </i>
-    <i>
-      <x v="82"/>
-    </i>
-    <i>
-      <x v="83"/>
-    </i>
-    <i>
-      <x v="84"/>
-    </i>
-    <i>
-      <x v="85"/>
-    </i>
-    <i>
-      <x v="86"/>
-    </i>
-    <i>
-      <x v="87"/>
-    </i>
-    <i>
-      <x v="88"/>
-    </i>
-    <i>
-      <x v="89"/>
-    </i>
-    <i>
-      <x v="90"/>
-    </i>
-    <i>
-      <x v="91"/>
-    </i>
-    <i>
-      <x v="92"/>
-    </i>
-    <i>
-      <x v="93"/>
-    </i>
-    <i>
-      <x v="94"/>
-    </i>
-    <i>
-      <x v="95"/>
-    </i>
-    <i>
-      <x v="96"/>
-    </i>
-    <i>
-      <x v="97"/>
-    </i>
-    <i>
-      <x v="98"/>
-    </i>
-    <i>
-      <x v="99"/>
-    </i>
-    <i>
-      <x v="100"/>
-    </i>
-    <i>
-      <x v="101"/>
-    </i>
-    <i>
-      <x v="102"/>
-    </i>
-    <i>
-      <x v="103"/>
-    </i>
-    <i>
-      <x v="104"/>
-    </i>
-    <i>
-      <x v="105"/>
-    </i>
-    <i>
-      <x v="106"/>
-    </i>
-    <i>
-      <x v="107"/>
-    </i>
-    <i>
-      <x v="108"/>
-    </i>
-    <i>
-      <x v="109"/>
-    </i>
-    <i>
-      <x v="110"/>
-    </i>
-    <i>
-      <x v="111"/>
-    </i>
-    <i>
-      <x v="112"/>
-    </i>
-    <i>
-      <x v="113"/>
-    </i>
-    <i>
-      <x v="114"/>
-    </i>
-    <i>
-      <x v="115"/>
-    </i>
-    <i>
-      <x v="116"/>
-    </i>
-    <i>
-      <x v="117"/>
-    </i>
-    <i>
-      <x v="118"/>
-    </i>
-    <i>
-      <x v="119"/>
-    </i>
-    <i>
-      <x v="120"/>
-    </i>
-    <i>
-      <x v="121"/>
-    </i>
-    <i>
-      <x v="122"/>
-    </i>
-    <i>
-      <x v="123"/>
-    </i>
-    <i>
-      <x v="124"/>
-    </i>
-    <i>
-      <x v="125"/>
-    </i>
-    <i>
-      <x v="126"/>
-    </i>
-    <i>
-      <x v="127"/>
-    </i>
-    <i>
-      <x v="128"/>
-    </i>
-    <i>
-      <x v="129"/>
-    </i>
-    <i>
-      <x v="130"/>
-    </i>
-    <i>
-      <x v="131"/>
-    </i>
-    <i>
-      <x v="132"/>
-    </i>
-    <i>
-      <x v="133"/>
-    </i>
-    <i>
-      <x v="134"/>
-    </i>
-    <i>
-      <x v="135"/>
-    </i>
-    <i>
-      <x v="136"/>
-    </i>
-    <i>
-      <x v="137"/>
-    </i>
-    <i>
-      <x v="138"/>
-    </i>
-    <i>
-      <x v="139"/>
-    </i>
-    <i>
-      <x v="140"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="11" hier="-1"/>
-    <pageField fld="9" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Count of Promotion" fld="11" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{166599A4-10FF-421A-AFB4-AE0C311C3DFB}" name="PivotTable2" cacheId="331" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="C3:D30" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="18">
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="134">
-        <item x="57"/>
-        <item x="116"/>
-        <item x="10"/>
-        <item x="27"/>
-        <item x="88"/>
-        <item x="19"/>
-        <item x="14"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="125"/>
-        <item x="128"/>
-        <item x="121"/>
-        <item x="41"/>
-        <item x="80"/>
-        <item x="93"/>
-        <item x="81"/>
-        <item x="111"/>
-        <item x="82"/>
-        <item x="49"/>
-        <item x="48"/>
-        <item x="68"/>
-        <item x="107"/>
-        <item x="83"/>
-        <item x="42"/>
-        <item x="97"/>
-        <item x="5"/>
-        <item x="11"/>
-        <item x="8"/>
-        <item x="35"/>
-        <item x="25"/>
-        <item x="99"/>
-        <item x="32"/>
-        <item x="22"/>
-        <item x="9"/>
-        <item x="13"/>
-        <item x="126"/>
-        <item x="54"/>
-        <item x="28"/>
-        <item x="53"/>
-        <item x="21"/>
-        <item x="84"/>
-        <item x="20"/>
-        <item x="12"/>
-        <item x="1"/>
-        <item x="86"/>
-        <item x="102"/>
-        <item x="127"/>
-        <item x="30"/>
-        <item x="43"/>
-        <item x="85"/>
-        <item x="112"/>
-        <item x="62"/>
-        <item x="50"/>
-        <item x="98"/>
-        <item x="36"/>
-        <item x="106"/>
-        <item x="17"/>
-        <item x="6"/>
-        <item x="122"/>
-        <item x="52"/>
-        <item x="104"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="18"/>
-        <item x="26"/>
-        <item x="103"/>
-        <item x="31"/>
-        <item x="89"/>
-        <item x="118"/>
-        <item x="2"/>
-        <item x="16"/>
-        <item x="55"/>
-        <item x="58"/>
-        <item x="114"/>
-        <item x="33"/>
-        <item x="87"/>
-        <item x="113"/>
-        <item x="69"/>
-        <item x="51"/>
-        <item x="59"/>
-        <item x="101"/>
-        <item x="34"/>
-        <item x="109"/>
-        <item x="61"/>
-        <item x="132"/>
-        <item x="56"/>
-        <item x="64"/>
-        <item x="117"/>
-        <item x="63"/>
-        <item x="100"/>
-        <item x="124"/>
-        <item x="108"/>
-        <item x="115"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="4"/>
-        <item x="15"/>
-        <item x="65"/>
-        <item x="44"/>
-        <item x="119"/>
-        <item x="105"/>
-        <item x="66"/>
-        <item x="120"/>
-        <item x="123"/>
-        <item x="45"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="39"/>
-        <item x="73"/>
-        <item x="110"/>
-        <item x="46"/>
-        <item x="94"/>
-        <item x="74"/>
-        <item x="29"/>
-        <item x="75"/>
-        <item x="90"/>
-        <item x="67"/>
-        <item x="76"/>
-        <item x="38"/>
-        <item x="91"/>
-        <item x="37"/>
-        <item x="40"/>
-        <item x="60"/>
-        <item x="95"/>
-        <item x="77"/>
-        <item x="47"/>
-        <item x="78"/>
-        <item x="131"/>
-        <item x="96"/>
-        <item x="92"/>
-        <item x="79"/>
-        <item h="1" x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisPage" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="35">
-        <item x="15"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="12"/>
-        <item x="30"/>
-        <item x="13"/>
-        <item x="19"/>
-        <item x="3"/>
-        <item x="28"/>
-        <item x="1"/>
-        <item x="22"/>
-        <item x="31"/>
-        <item x="16"/>
-        <item x="18"/>
-        <item x="24"/>
-        <item x="26"/>
-        <item x="11"/>
-        <item x="14"/>
-        <item x="27"/>
-        <item x="23"/>
-        <item x="8"/>
-        <item x="21"/>
-        <item x="25"/>
-        <item x="17"/>
-        <item x="10"/>
-        <item x="5"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="29"/>
-        <item x="9"/>
-        <item x="7"/>
-        <item x="20"/>
-        <item x="6"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="27">
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="23"/>
-    </i>
-    <i>
-      <x v="27"/>
-    </i>
-    <i>
-      <x v="33"/>
-    </i>
-    <i>
-      <x v="42"/>
-    </i>
-    <i>
-      <x v="47"/>
-    </i>
-    <i>
-      <x v="49"/>
-    </i>
-    <i>
-      <x v="56"/>
-    </i>
-    <i>
-      <x v="61"/>
-    </i>
-    <i>
-      <x v="69"/>
-    </i>
-    <i>
-      <x v="70"/>
-    </i>
-    <i>
-      <x v="72"/>
-    </i>
-    <i>
-      <x v="74"/>
-    </i>
-    <i>
-      <x v="86"/>
-    </i>
-    <i>
-      <x v="94"/>
-    </i>
-    <i>
-      <x v="96"/>
-    </i>
-    <i>
-      <x v="101"/>
-    </i>
-    <i>
-      <x v="104"/>
-    </i>
-    <i>
-      <x v="108"/>
-    </i>
-    <i>
-      <x v="112"/>
-    </i>
-    <i>
-      <x v="119"/>
-    </i>
-    <i>
-      <x v="120"/>
-    </i>
-    <i>
-      <x v="121"/>
-    </i>
-    <i>
-      <x v="122"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="14" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Count of Recognition (Award" fld="14" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FC177463-ECB6-493F-84C5-BD2B6B5E3667}" name="PivotTable1" cacheId="331" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FC177463-ECB6-493F-84C5-BD2B6B5E3667}" name="PivotTable1" cacheId="472" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:B35" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="18">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -29344,6 +29042,311 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{166599A4-10FF-421A-AFB4-AE0C311C3DFB}" name="PivotTable2" cacheId="472" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="C3:D30" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="18">
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="134">
+        <item x="57"/>
+        <item x="116"/>
+        <item x="10"/>
+        <item x="27"/>
+        <item x="88"/>
+        <item x="19"/>
+        <item x="14"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="125"/>
+        <item x="128"/>
+        <item x="121"/>
+        <item x="41"/>
+        <item x="80"/>
+        <item x="93"/>
+        <item x="81"/>
+        <item x="111"/>
+        <item x="82"/>
+        <item x="49"/>
+        <item x="48"/>
+        <item x="68"/>
+        <item x="107"/>
+        <item x="83"/>
+        <item x="42"/>
+        <item x="97"/>
+        <item x="5"/>
+        <item x="11"/>
+        <item x="8"/>
+        <item x="35"/>
+        <item x="25"/>
+        <item x="99"/>
+        <item x="32"/>
+        <item x="22"/>
+        <item x="9"/>
+        <item x="13"/>
+        <item x="126"/>
+        <item x="54"/>
+        <item x="28"/>
+        <item x="53"/>
+        <item x="21"/>
+        <item x="84"/>
+        <item x="20"/>
+        <item x="12"/>
+        <item x="1"/>
+        <item x="86"/>
+        <item x="102"/>
+        <item x="127"/>
+        <item x="30"/>
+        <item x="43"/>
+        <item x="85"/>
+        <item x="112"/>
+        <item x="62"/>
+        <item x="50"/>
+        <item x="98"/>
+        <item x="36"/>
+        <item x="106"/>
+        <item x="17"/>
+        <item x="6"/>
+        <item x="122"/>
+        <item x="52"/>
+        <item x="104"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="18"/>
+        <item x="26"/>
+        <item x="103"/>
+        <item x="31"/>
+        <item x="89"/>
+        <item x="118"/>
+        <item x="2"/>
+        <item x="16"/>
+        <item x="55"/>
+        <item x="58"/>
+        <item x="114"/>
+        <item x="33"/>
+        <item x="87"/>
+        <item x="113"/>
+        <item x="69"/>
+        <item x="51"/>
+        <item x="59"/>
+        <item x="101"/>
+        <item x="34"/>
+        <item x="109"/>
+        <item x="61"/>
+        <item x="132"/>
+        <item x="56"/>
+        <item x="64"/>
+        <item x="117"/>
+        <item x="63"/>
+        <item x="100"/>
+        <item x="124"/>
+        <item x="108"/>
+        <item x="115"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="4"/>
+        <item x="15"/>
+        <item x="65"/>
+        <item x="44"/>
+        <item x="119"/>
+        <item x="105"/>
+        <item x="66"/>
+        <item x="120"/>
+        <item x="123"/>
+        <item x="45"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="39"/>
+        <item x="73"/>
+        <item x="110"/>
+        <item x="46"/>
+        <item x="94"/>
+        <item x="74"/>
+        <item x="29"/>
+        <item x="75"/>
+        <item x="90"/>
+        <item x="67"/>
+        <item x="76"/>
+        <item x="38"/>
+        <item x="91"/>
+        <item x="37"/>
+        <item x="40"/>
+        <item x="60"/>
+        <item x="95"/>
+        <item x="77"/>
+        <item x="47"/>
+        <item x="78"/>
+        <item x="131"/>
+        <item x="96"/>
+        <item x="92"/>
+        <item x="79"/>
+        <item h="1" x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="35">
+        <item x="15"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="12"/>
+        <item x="30"/>
+        <item x="13"/>
+        <item x="19"/>
+        <item x="3"/>
+        <item x="28"/>
+        <item x="1"/>
+        <item x="22"/>
+        <item x="31"/>
+        <item x="16"/>
+        <item x="18"/>
+        <item x="24"/>
+        <item x="26"/>
+        <item x="11"/>
+        <item x="14"/>
+        <item x="27"/>
+        <item x="23"/>
+        <item x="8"/>
+        <item x="21"/>
+        <item x="25"/>
+        <item x="17"/>
+        <item x="10"/>
+        <item x="5"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="29"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item x="20"/>
+        <item x="6"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="27">
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="33"/>
+    </i>
+    <i>
+      <x v="42"/>
+    </i>
+    <i>
+      <x v="47"/>
+    </i>
+    <i>
+      <x v="49"/>
+    </i>
+    <i>
+      <x v="56"/>
+    </i>
+    <i>
+      <x v="61"/>
+    </i>
+    <i>
+      <x v="69"/>
+    </i>
+    <i>
+      <x v="70"/>
+    </i>
+    <i>
+      <x v="72"/>
+    </i>
+    <i>
+      <x v="74"/>
+    </i>
+    <i>
+      <x v="86"/>
+    </i>
+    <i>
+      <x v="94"/>
+    </i>
+    <i>
+      <x v="96"/>
+    </i>
+    <i>
+      <x v="101"/>
+    </i>
+    <i>
+      <x v="104"/>
+    </i>
+    <i>
+      <x v="108"/>
+    </i>
+    <i>
+      <x v="112"/>
+    </i>
+    <i>
+      <x v="119"/>
+    </i>
+    <i>
+      <x v="120"/>
+    </i>
+    <i>
+      <x v="121"/>
+    </i>
+    <i>
+      <x v="122"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="14" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Count of Recognition (Award" fld="14" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -29635,7 +29638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U366"/>
+  <dimension ref="A1:U367"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.140625" style="1" customWidth="1"/>
@@ -44845,44 +44848,87 @@
       <c r="A366" s="37">
         <v>369</v>
       </c>
-      <c r="B366" s="14" t="s">
+      <c r="B366" s="21" t="s">
         <v>791</v>
       </c>
-      <c r="C366" s="14" t="s">
+      <c r="C366" s="21" t="s">
         <v>549</v>
       </c>
-      <c r="D366" s="14" t="s">
+      <c r="D366" s="21" t="s">
         <v>550</v>
       </c>
-      <c r="E366" s="14" t="s">
+      <c r="E366" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="F366" s="14" t="s">
+      <c r="F366" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="G366" s="14">
+      <c r="G366" s="21">
         <v>8</v>
       </c>
-      <c r="H366" s="14" t="s">
+      <c r="H366" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="I366" s="14" t="s">
+      <c r="I366" s="21" t="s">
         <v>451</v>
       </c>
-      <c r="J366" s="14">
+      <c r="J366" s="21">
         <v>2026</v>
       </c>
-      <c r="K366" s="16"/>
-      <c r="L366" s="16"/>
-      <c r="M366" s="16"/>
-      <c r="N366" s="16"/>
-      <c r="O366" s="16"/>
-      <c r="P366" s="14" t="s">
+      <c r="K366" s="23"/>
+      <c r="L366" s="23"/>
+      <c r="M366" s="23"/>
+      <c r="N366" s="23"/>
+      <c r="O366" s="23"/>
+      <c r="P366" s="21" t="s">
         <v>797</v>
       </c>
-      <c r="Q366" s="16"/>
-      <c r="R366" s="16"/>
+      <c r="Q366" s="23"/>
+      <c r="R366" s="23"/>
       <c r="S366" s="17"/>
+    </row>
+    <row r="367" spans="1:21" ht="15.95" customHeight="1">
+      <c r="A367" s="21">
+        <v>370</v>
+      </c>
+      <c r="B367" s="21" t="s">
+        <v>791</v>
+      </c>
+      <c r="C367" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D367" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="E367" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F367" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G367" s="14">
+        <v>5</v>
+      </c>
+      <c r="H367" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I367" s="14" t="s">
+        <v>465</v>
+      </c>
+      <c r="J367" s="14">
+        <v>2026</v>
+      </c>
+      <c r="K367" s="16"/>
+      <c r="L367" s="16"/>
+      <c r="M367" s="16"/>
+      <c r="N367" s="16" t="s">
+        <v>798</v>
+      </c>
+      <c r="O367" s="16"/>
+      <c r="P367" s="16"/>
+      <c r="Q367" s="16"/>
+      <c r="R367" s="16"/>
+      <c r="S367" s="17"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:T366" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -44921,12 +44967,12 @@
         <v>9</v>
       </c>
       <c r="B1" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="13" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>4</v>
@@ -44943,7 +44989,7 @@
         <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -44987,7 +45033,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B8">
         <v>2</v>
@@ -44998,7 +45044,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B9">
         <v>114</v>
@@ -45015,7 +45061,7 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -45034,7 +45080,7 @@
         <v>36</v>
       </c>
       <c r="H17" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -45048,7 +45094,7 @@
         <v>28</v>
       </c>
       <c r="E18" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="F18" t="s">
         <v>57</v>
@@ -45059,7 +45105,7 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -45219,13 +45265,13 @@
         <v>13</v>
       </c>
       <c r="B1" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="D1" s="13" t="s">
         <v>11</v>
       </c>
       <c r="E1" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -45233,13 +45279,13 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="D2" s="13" t="s">
         <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -45247,7 +45293,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C4">
         <f>COUNTA(A4:A93)</f>
@@ -45257,7 +45303,7 @@
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -46804,10 +46850,10 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D137" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -46900,13 +46946,13 @@
     </row>
     <row r="146" spans="1:5">
       <c r="A146" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B146">
         <v>162</v>
       </c>
       <c r="D146" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="E146">
         <v>91</v>
@@ -46929,7 +46975,7 @@
   <sheetData>
     <row r="2" spans="2:2">
       <c r="B2" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
   </sheetData>
@@ -46999,13 +47045,13 @@
         <v>15</v>
       </c>
       <c r="B1" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>14</v>
       </c>
       <c r="D1" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -47013,13 +47059,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C3" s="13" t="s">
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -47394,7 +47440,7 @@
         <v>2</v>
       </c>
       <c r="C30" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D30">
         <v>32</v>
@@ -47434,7 +47480,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B35">
         <v>47</v>

--- a/data/Recognitions_latest.xlsx
+++ b/data/Recognitions_latest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30611"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aphrcorg-my.sharepoint.com/personal/nnjenga_aphrc_org/Documents/CARTA Dashboard/ECRS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="755" documentId="13_ncr:1_{74C5384D-9D49-4106-BD43-FCAED859190D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6997F9E1-9AD9-4AB1-94B5-D0D96AB3A1B2}"/>
+  <xr:revisionPtr revIDLastSave="758" documentId="13_ncr:1_{74C5384D-9D49-4106-BD43-FCAED859190D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5EE94513-8881-4121-8771-492E26A38EF9}"/>
   <bookViews>
     <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,10 +24,10 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="471" r:id="rId6"/>
-    <pivotCache cacheId="472" r:id="rId7"/>
-    <pivotCache cacheId="473" r:id="rId8"/>
-    <pivotCache cacheId="474" r:id="rId9"/>
+    <pivotCache cacheId="196" r:id="rId6"/>
+    <pivotCache cacheId="197" r:id="rId7"/>
+    <pivotCache cacheId="198" r:id="rId8"/>
+    <pivotCache cacheId="199" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -26975,7 +26975,106 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{414D3242-6D58-4EC3-BE1F-E4596803BECC}" name="PivotTable10" cacheId="471" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{55E369D5-46AA-45F8-B4A0-AC6C0CED6464}" name="PivotTable2" cacheId="196" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A3:D9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="16">
+    <pivotField dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisCol" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item m="1" x="2"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="5">
+        <item x="0"/>
+        <item m="1" x="4"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" defaultSubtotal="0">
+      <items count="9">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="1"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="3"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="8" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Count of No" fld="0" subtotal="count" baseField="4" baseItem="3"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{414D3242-6D58-4EC3-BE1F-E4596803BECC}" name="PivotTable10" cacheId="196" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A16:H19" firstHeaderRow="1" firstDataRow="3" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="16">
     <pivotField dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -27117,815 +27216,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{55E369D5-46AA-45F8-B4A0-AC6C0CED6464}" name="PivotTable2" cacheId="471" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="A3:D9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="16">
-    <pivotField dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField axis="axisCol" compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item m="1" x="2"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="5">
-        <item x="0"/>
-        <item m="1" x="4"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" defaultSubtotal="0">
-      <items count="9">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="1"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="3"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="8" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Count of No" fld="0" subtotal="count" baseField="4" baseItem="3"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{90770DB3-F829-4E9E-88FA-FB5C22EB6463}" name="PivotTable2" cacheId="473" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="D4:E146" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="18">
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="142">
-        <item x="57"/>
-        <item x="116"/>
-        <item x="10"/>
-        <item x="27"/>
-        <item x="88"/>
-        <item x="19"/>
-        <item x="14"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="125"/>
-        <item x="128"/>
-        <item x="121"/>
-        <item x="41"/>
-        <item x="80"/>
-        <item x="93"/>
-        <item x="81"/>
-        <item x="111"/>
-        <item x="82"/>
-        <item x="49"/>
-        <item x="48"/>
-        <item x="68"/>
-        <item x="107"/>
-        <item x="83"/>
-        <item x="42"/>
-        <item x="97"/>
-        <item x="5"/>
-        <item x="11"/>
-        <item x="8"/>
-        <item x="35"/>
-        <item x="25"/>
-        <item x="99"/>
-        <item x="32"/>
-        <item x="22"/>
-        <item x="9"/>
-        <item x="13"/>
-        <item x="126"/>
-        <item x="54"/>
-        <item x="28"/>
-        <item x="53"/>
-        <item x="21"/>
-        <item x="84"/>
-        <item x="20"/>
-        <item x="12"/>
-        <item x="1"/>
-        <item x="86"/>
-        <item x="102"/>
-        <item x="127"/>
-        <item x="30"/>
-        <item x="43"/>
-        <item x="85"/>
-        <item x="112"/>
-        <item x="62"/>
-        <item x="50"/>
-        <item x="98"/>
-        <item x="36"/>
-        <item x="106"/>
-        <item x="17"/>
-        <item x="6"/>
-        <item x="122"/>
-        <item x="52"/>
-        <item x="104"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="18"/>
-        <item x="26"/>
-        <item x="103"/>
-        <item x="31"/>
-        <item x="89"/>
-        <item x="118"/>
-        <item x="2"/>
-        <item x="16"/>
-        <item x="55"/>
-        <item x="58"/>
-        <item x="114"/>
-        <item x="33"/>
-        <item x="87"/>
-        <item x="113"/>
-        <item x="69"/>
-        <item x="51"/>
-        <item x="59"/>
-        <item x="101"/>
-        <item x="34"/>
-        <item x="109"/>
-        <item x="61"/>
-        <item x="132"/>
-        <item x="56"/>
-        <item x="64"/>
-        <item x="117"/>
-        <item x="63"/>
-        <item x="100"/>
-        <item x="124"/>
-        <item x="108"/>
-        <item x="115"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="4"/>
-        <item x="15"/>
-        <item x="65"/>
-        <item x="44"/>
-        <item x="119"/>
-        <item x="105"/>
-        <item x="66"/>
-        <item x="120"/>
-        <item x="123"/>
-        <item x="45"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="39"/>
-        <item x="73"/>
-        <item x="110"/>
-        <item x="46"/>
-        <item x="94"/>
-        <item x="74"/>
-        <item x="29"/>
-        <item x="75"/>
-        <item x="90"/>
-        <item x="67"/>
-        <item x="76"/>
-        <item x="38"/>
-        <item x="91"/>
-        <item x="37"/>
-        <item x="40"/>
-        <item x="60"/>
-        <item x="95"/>
-        <item x="77"/>
-        <item x="47"/>
-        <item x="78"/>
-        <item x="131"/>
-        <item x="96"/>
-        <item x="92"/>
-        <item x="79"/>
-        <item x="0"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
-      <items count="12">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="9"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="1"/>
-        <item x="10"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisPage" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="69">
-        <item x="57"/>
-        <item x="56"/>
-        <item x="55"/>
-        <item x="39"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="43"/>
-        <item x="20"/>
-        <item x="35"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="50"/>
-        <item x="23"/>
-        <item x="16"/>
-        <item x="52"/>
-        <item x="30"/>
-        <item x="12"/>
-        <item x="24"/>
-        <item x="63"/>
-        <item x="31"/>
-        <item x="17"/>
-        <item x="28"/>
-        <item x="37"/>
-        <item x="48"/>
-        <item x="13"/>
-        <item x="32"/>
-        <item x="51"/>
-        <item x="22"/>
-        <item x="36"/>
-        <item x="54"/>
-        <item x="49"/>
-        <item x="18"/>
-        <item x="53"/>
-        <item x="19"/>
-        <item x="26"/>
-        <item x="45"/>
-        <item x="64"/>
-        <item x="42"/>
-        <item x="62"/>
-        <item x="29"/>
-        <item x="38"/>
-        <item x="15"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="44"/>
-        <item x="21"/>
-        <item x="25"/>
-        <item x="27"/>
-        <item x="41"/>
-        <item x="61"/>
-        <item x="58"/>
-        <item x="60"/>
-        <item x="6"/>
-        <item x="9"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="11"/>
-        <item x="10"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="40"/>
-        <item x="1"/>
-        <item x="14"/>
-        <item x="59"/>
-        <item x="0"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="142">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i>
-      <x v="15"/>
-    </i>
-    <i>
-      <x v="16"/>
-    </i>
-    <i>
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="18"/>
-    </i>
-    <i>
-      <x v="19"/>
-    </i>
-    <i>
-      <x v="20"/>
-    </i>
-    <i>
-      <x v="21"/>
-    </i>
-    <i>
-      <x v="22"/>
-    </i>
-    <i>
-      <x v="23"/>
-    </i>
-    <i>
-      <x v="24"/>
-    </i>
-    <i>
-      <x v="25"/>
-    </i>
-    <i>
-      <x v="26"/>
-    </i>
-    <i>
-      <x v="27"/>
-    </i>
-    <i>
-      <x v="28"/>
-    </i>
-    <i>
-      <x v="29"/>
-    </i>
-    <i>
-      <x v="30"/>
-    </i>
-    <i>
-      <x v="31"/>
-    </i>
-    <i>
-      <x v="32"/>
-    </i>
-    <i>
-      <x v="33"/>
-    </i>
-    <i>
-      <x v="34"/>
-    </i>
-    <i>
-      <x v="35"/>
-    </i>
-    <i>
-      <x v="36"/>
-    </i>
-    <i>
-      <x v="37"/>
-    </i>
-    <i>
-      <x v="38"/>
-    </i>
-    <i>
-      <x v="39"/>
-    </i>
-    <i>
-      <x v="40"/>
-    </i>
-    <i>
-      <x v="41"/>
-    </i>
-    <i>
-      <x v="42"/>
-    </i>
-    <i>
-      <x v="43"/>
-    </i>
-    <i>
-      <x v="44"/>
-    </i>
-    <i>
-      <x v="45"/>
-    </i>
-    <i>
-      <x v="46"/>
-    </i>
-    <i>
-      <x v="47"/>
-    </i>
-    <i>
-      <x v="48"/>
-    </i>
-    <i>
-      <x v="49"/>
-    </i>
-    <i>
-      <x v="50"/>
-    </i>
-    <i>
-      <x v="51"/>
-    </i>
-    <i>
-      <x v="52"/>
-    </i>
-    <i>
-      <x v="53"/>
-    </i>
-    <i>
-      <x v="54"/>
-    </i>
-    <i>
-      <x v="55"/>
-    </i>
-    <i>
-      <x v="56"/>
-    </i>
-    <i>
-      <x v="57"/>
-    </i>
-    <i>
-      <x v="58"/>
-    </i>
-    <i>
-      <x v="59"/>
-    </i>
-    <i>
-      <x v="60"/>
-    </i>
-    <i>
-      <x v="61"/>
-    </i>
-    <i>
-      <x v="62"/>
-    </i>
-    <i>
-      <x v="63"/>
-    </i>
-    <i>
-      <x v="64"/>
-    </i>
-    <i>
-      <x v="65"/>
-    </i>
-    <i>
-      <x v="66"/>
-    </i>
-    <i>
-      <x v="67"/>
-    </i>
-    <i>
-      <x v="68"/>
-    </i>
-    <i>
-      <x v="69"/>
-    </i>
-    <i>
-      <x v="70"/>
-    </i>
-    <i>
-      <x v="71"/>
-    </i>
-    <i>
-      <x v="72"/>
-    </i>
-    <i>
-      <x v="73"/>
-    </i>
-    <i>
-      <x v="74"/>
-    </i>
-    <i>
-      <x v="75"/>
-    </i>
-    <i>
-      <x v="76"/>
-    </i>
-    <i>
-      <x v="77"/>
-    </i>
-    <i>
-      <x v="78"/>
-    </i>
-    <i>
-      <x v="79"/>
-    </i>
-    <i>
-      <x v="80"/>
-    </i>
-    <i>
-      <x v="81"/>
-    </i>
-    <i>
-      <x v="82"/>
-    </i>
-    <i>
-      <x v="83"/>
-    </i>
-    <i>
-      <x v="84"/>
-    </i>
-    <i>
-      <x v="85"/>
-    </i>
-    <i>
-      <x v="86"/>
-    </i>
-    <i>
-      <x v="87"/>
-    </i>
-    <i>
-      <x v="88"/>
-    </i>
-    <i>
-      <x v="89"/>
-    </i>
-    <i>
-      <x v="90"/>
-    </i>
-    <i>
-      <x v="91"/>
-    </i>
-    <i>
-      <x v="92"/>
-    </i>
-    <i>
-      <x v="93"/>
-    </i>
-    <i>
-      <x v="94"/>
-    </i>
-    <i>
-      <x v="95"/>
-    </i>
-    <i>
-      <x v="96"/>
-    </i>
-    <i>
-      <x v="97"/>
-    </i>
-    <i>
-      <x v="98"/>
-    </i>
-    <i>
-      <x v="99"/>
-    </i>
-    <i>
-      <x v="100"/>
-    </i>
-    <i>
-      <x v="101"/>
-    </i>
-    <i>
-      <x v="102"/>
-    </i>
-    <i>
-      <x v="103"/>
-    </i>
-    <i>
-      <x v="104"/>
-    </i>
-    <i>
-      <x v="105"/>
-    </i>
-    <i>
-      <x v="106"/>
-    </i>
-    <i>
-      <x v="107"/>
-    </i>
-    <i>
-      <x v="108"/>
-    </i>
-    <i>
-      <x v="109"/>
-    </i>
-    <i>
-      <x v="110"/>
-    </i>
-    <i>
-      <x v="111"/>
-    </i>
-    <i>
-      <x v="112"/>
-    </i>
-    <i>
-      <x v="113"/>
-    </i>
-    <i>
-      <x v="114"/>
-    </i>
-    <i>
-      <x v="115"/>
-    </i>
-    <i>
-      <x v="116"/>
-    </i>
-    <i>
-      <x v="117"/>
-    </i>
-    <i>
-      <x v="118"/>
-    </i>
-    <i>
-      <x v="119"/>
-    </i>
-    <i>
-      <x v="120"/>
-    </i>
-    <i>
-      <x v="121"/>
-    </i>
-    <i>
-      <x v="122"/>
-    </i>
-    <i>
-      <x v="123"/>
-    </i>
-    <i>
-      <x v="124"/>
-    </i>
-    <i>
-      <x v="125"/>
-    </i>
-    <i>
-      <x v="126"/>
-    </i>
-    <i>
-      <x v="127"/>
-    </i>
-    <i>
-      <x v="128"/>
-    </i>
-    <i>
-      <x v="129"/>
-    </i>
-    <i>
-      <x v="130"/>
-    </i>
-    <i>
-      <x v="131"/>
-    </i>
-    <i>
-      <x v="132"/>
-    </i>
-    <i>
-      <x v="133"/>
-    </i>
-    <i>
-      <x v="134"/>
-    </i>
-    <i>
-      <x v="135"/>
-    </i>
-    <i>
-      <x v="136"/>
-    </i>
-    <i>
-      <x v="137"/>
-    </i>
-    <i>
-      <x v="138"/>
-    </i>
-    <i>
-      <x v="139"/>
-    </i>
-    <i>
-      <x v="140"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="11" hier="-1"/>
-    <pageField fld="9" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Count of Promotion" fld="11" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C759C715-A218-40D6-B8AD-8DD0CC6815DF}" name="PivotTable1" cacheId="474" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C759C715-A218-40D6-B8AD-8DD0CC6815DF}" name="PivotTable1" cacheId="199" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:B146" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="18">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -28707,8 +27999,1021 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{90770DB3-F829-4E9E-88FA-FB5C22EB6463}" name="PivotTable2" cacheId="198" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="D4:E146" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="18">
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="142">
+        <item x="57"/>
+        <item x="116"/>
+        <item x="10"/>
+        <item x="27"/>
+        <item x="88"/>
+        <item x="19"/>
+        <item x="14"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="125"/>
+        <item x="128"/>
+        <item x="121"/>
+        <item x="41"/>
+        <item x="80"/>
+        <item x="93"/>
+        <item x="81"/>
+        <item x="111"/>
+        <item x="82"/>
+        <item x="49"/>
+        <item x="48"/>
+        <item x="68"/>
+        <item x="107"/>
+        <item x="83"/>
+        <item x="42"/>
+        <item x="97"/>
+        <item x="5"/>
+        <item x="11"/>
+        <item x="8"/>
+        <item x="35"/>
+        <item x="25"/>
+        <item x="99"/>
+        <item x="32"/>
+        <item x="22"/>
+        <item x="9"/>
+        <item x="13"/>
+        <item x="126"/>
+        <item x="54"/>
+        <item x="28"/>
+        <item x="53"/>
+        <item x="21"/>
+        <item x="84"/>
+        <item x="20"/>
+        <item x="12"/>
+        <item x="1"/>
+        <item x="86"/>
+        <item x="102"/>
+        <item x="127"/>
+        <item x="30"/>
+        <item x="43"/>
+        <item x="85"/>
+        <item x="112"/>
+        <item x="62"/>
+        <item x="50"/>
+        <item x="98"/>
+        <item x="36"/>
+        <item x="106"/>
+        <item x="17"/>
+        <item x="6"/>
+        <item x="122"/>
+        <item x="52"/>
+        <item x="104"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="18"/>
+        <item x="26"/>
+        <item x="103"/>
+        <item x="31"/>
+        <item x="89"/>
+        <item x="118"/>
+        <item x="2"/>
+        <item x="16"/>
+        <item x="55"/>
+        <item x="58"/>
+        <item x="114"/>
+        <item x="33"/>
+        <item x="87"/>
+        <item x="113"/>
+        <item x="69"/>
+        <item x="51"/>
+        <item x="59"/>
+        <item x="101"/>
+        <item x="34"/>
+        <item x="109"/>
+        <item x="61"/>
+        <item x="132"/>
+        <item x="56"/>
+        <item x="64"/>
+        <item x="117"/>
+        <item x="63"/>
+        <item x="100"/>
+        <item x="124"/>
+        <item x="108"/>
+        <item x="115"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="4"/>
+        <item x="15"/>
+        <item x="65"/>
+        <item x="44"/>
+        <item x="119"/>
+        <item x="105"/>
+        <item x="66"/>
+        <item x="120"/>
+        <item x="123"/>
+        <item x="45"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="39"/>
+        <item x="73"/>
+        <item x="110"/>
+        <item x="46"/>
+        <item x="94"/>
+        <item x="74"/>
+        <item x="29"/>
+        <item x="75"/>
+        <item x="90"/>
+        <item x="67"/>
+        <item x="76"/>
+        <item x="38"/>
+        <item x="91"/>
+        <item x="37"/>
+        <item x="40"/>
+        <item x="60"/>
+        <item x="95"/>
+        <item x="77"/>
+        <item x="47"/>
+        <item x="78"/>
+        <item x="131"/>
+        <item x="96"/>
+        <item x="92"/>
+        <item x="79"/>
+        <item x="0"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
+      <items count="12">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="1"/>
+        <item x="10"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="69">
+        <item x="57"/>
+        <item x="56"/>
+        <item x="55"/>
+        <item x="39"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="43"/>
+        <item x="20"/>
+        <item x="35"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="50"/>
+        <item x="23"/>
+        <item x="16"/>
+        <item x="52"/>
+        <item x="30"/>
+        <item x="12"/>
+        <item x="24"/>
+        <item x="63"/>
+        <item x="31"/>
+        <item x="17"/>
+        <item x="28"/>
+        <item x="37"/>
+        <item x="48"/>
+        <item x="13"/>
+        <item x="32"/>
+        <item x="51"/>
+        <item x="22"/>
+        <item x="36"/>
+        <item x="54"/>
+        <item x="49"/>
+        <item x="18"/>
+        <item x="53"/>
+        <item x="19"/>
+        <item x="26"/>
+        <item x="45"/>
+        <item x="64"/>
+        <item x="42"/>
+        <item x="62"/>
+        <item x="29"/>
+        <item x="38"/>
+        <item x="15"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="44"/>
+        <item x="21"/>
+        <item x="25"/>
+        <item x="27"/>
+        <item x="41"/>
+        <item x="61"/>
+        <item x="58"/>
+        <item x="60"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="40"/>
+        <item x="1"/>
+        <item x="14"/>
+        <item x="59"/>
+        <item x="0"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="142">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="26"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="29"/>
+    </i>
+    <i>
+      <x v="30"/>
+    </i>
+    <i>
+      <x v="31"/>
+    </i>
+    <i>
+      <x v="32"/>
+    </i>
+    <i>
+      <x v="33"/>
+    </i>
+    <i>
+      <x v="34"/>
+    </i>
+    <i>
+      <x v="35"/>
+    </i>
+    <i>
+      <x v="36"/>
+    </i>
+    <i>
+      <x v="37"/>
+    </i>
+    <i>
+      <x v="38"/>
+    </i>
+    <i>
+      <x v="39"/>
+    </i>
+    <i>
+      <x v="40"/>
+    </i>
+    <i>
+      <x v="41"/>
+    </i>
+    <i>
+      <x v="42"/>
+    </i>
+    <i>
+      <x v="43"/>
+    </i>
+    <i>
+      <x v="44"/>
+    </i>
+    <i>
+      <x v="45"/>
+    </i>
+    <i>
+      <x v="46"/>
+    </i>
+    <i>
+      <x v="47"/>
+    </i>
+    <i>
+      <x v="48"/>
+    </i>
+    <i>
+      <x v="49"/>
+    </i>
+    <i>
+      <x v="50"/>
+    </i>
+    <i>
+      <x v="51"/>
+    </i>
+    <i>
+      <x v="52"/>
+    </i>
+    <i>
+      <x v="53"/>
+    </i>
+    <i>
+      <x v="54"/>
+    </i>
+    <i>
+      <x v="55"/>
+    </i>
+    <i>
+      <x v="56"/>
+    </i>
+    <i>
+      <x v="57"/>
+    </i>
+    <i>
+      <x v="58"/>
+    </i>
+    <i>
+      <x v="59"/>
+    </i>
+    <i>
+      <x v="60"/>
+    </i>
+    <i>
+      <x v="61"/>
+    </i>
+    <i>
+      <x v="62"/>
+    </i>
+    <i>
+      <x v="63"/>
+    </i>
+    <i>
+      <x v="64"/>
+    </i>
+    <i>
+      <x v="65"/>
+    </i>
+    <i>
+      <x v="66"/>
+    </i>
+    <i>
+      <x v="67"/>
+    </i>
+    <i>
+      <x v="68"/>
+    </i>
+    <i>
+      <x v="69"/>
+    </i>
+    <i>
+      <x v="70"/>
+    </i>
+    <i>
+      <x v="71"/>
+    </i>
+    <i>
+      <x v="72"/>
+    </i>
+    <i>
+      <x v="73"/>
+    </i>
+    <i>
+      <x v="74"/>
+    </i>
+    <i>
+      <x v="75"/>
+    </i>
+    <i>
+      <x v="76"/>
+    </i>
+    <i>
+      <x v="77"/>
+    </i>
+    <i>
+      <x v="78"/>
+    </i>
+    <i>
+      <x v="79"/>
+    </i>
+    <i>
+      <x v="80"/>
+    </i>
+    <i>
+      <x v="81"/>
+    </i>
+    <i>
+      <x v="82"/>
+    </i>
+    <i>
+      <x v="83"/>
+    </i>
+    <i>
+      <x v="84"/>
+    </i>
+    <i>
+      <x v="85"/>
+    </i>
+    <i>
+      <x v="86"/>
+    </i>
+    <i>
+      <x v="87"/>
+    </i>
+    <i>
+      <x v="88"/>
+    </i>
+    <i>
+      <x v="89"/>
+    </i>
+    <i>
+      <x v="90"/>
+    </i>
+    <i>
+      <x v="91"/>
+    </i>
+    <i>
+      <x v="92"/>
+    </i>
+    <i>
+      <x v="93"/>
+    </i>
+    <i>
+      <x v="94"/>
+    </i>
+    <i>
+      <x v="95"/>
+    </i>
+    <i>
+      <x v="96"/>
+    </i>
+    <i>
+      <x v="97"/>
+    </i>
+    <i>
+      <x v="98"/>
+    </i>
+    <i>
+      <x v="99"/>
+    </i>
+    <i>
+      <x v="100"/>
+    </i>
+    <i>
+      <x v="101"/>
+    </i>
+    <i>
+      <x v="102"/>
+    </i>
+    <i>
+      <x v="103"/>
+    </i>
+    <i>
+      <x v="104"/>
+    </i>
+    <i>
+      <x v="105"/>
+    </i>
+    <i>
+      <x v="106"/>
+    </i>
+    <i>
+      <x v="107"/>
+    </i>
+    <i>
+      <x v="108"/>
+    </i>
+    <i>
+      <x v="109"/>
+    </i>
+    <i>
+      <x v="110"/>
+    </i>
+    <i>
+      <x v="111"/>
+    </i>
+    <i>
+      <x v="112"/>
+    </i>
+    <i>
+      <x v="113"/>
+    </i>
+    <i>
+      <x v="114"/>
+    </i>
+    <i>
+      <x v="115"/>
+    </i>
+    <i>
+      <x v="116"/>
+    </i>
+    <i>
+      <x v="117"/>
+    </i>
+    <i>
+      <x v="118"/>
+    </i>
+    <i>
+      <x v="119"/>
+    </i>
+    <i>
+      <x v="120"/>
+    </i>
+    <i>
+      <x v="121"/>
+    </i>
+    <i>
+      <x v="122"/>
+    </i>
+    <i>
+      <x v="123"/>
+    </i>
+    <i>
+      <x v="124"/>
+    </i>
+    <i>
+      <x v="125"/>
+    </i>
+    <i>
+      <x v="126"/>
+    </i>
+    <i>
+      <x v="127"/>
+    </i>
+    <i>
+      <x v="128"/>
+    </i>
+    <i>
+      <x v="129"/>
+    </i>
+    <i>
+      <x v="130"/>
+    </i>
+    <i>
+      <x v="131"/>
+    </i>
+    <i>
+      <x v="132"/>
+    </i>
+    <i>
+      <x v="133"/>
+    </i>
+    <i>
+      <x v="134"/>
+    </i>
+    <i>
+      <x v="135"/>
+    </i>
+    <i>
+      <x v="136"/>
+    </i>
+    <i>
+      <x v="137"/>
+    </i>
+    <i>
+      <x v="138"/>
+    </i>
+    <i>
+      <x v="139"/>
+    </i>
+    <i>
+      <x v="140"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="11" hier="-1"/>
+    <pageField fld="9" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Count of Promotion" fld="11" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FC177463-ECB6-493F-84C5-BD2B6B5E3667}" name="PivotTable1" cacheId="472" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{166599A4-10FF-421A-AFB4-AE0C311C3DFB}" name="PivotTable2" cacheId="197" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="C3:D30" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="18">
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="134">
+        <item x="57"/>
+        <item x="116"/>
+        <item x="10"/>
+        <item x="27"/>
+        <item x="88"/>
+        <item x="19"/>
+        <item x="14"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="125"/>
+        <item x="128"/>
+        <item x="121"/>
+        <item x="41"/>
+        <item x="80"/>
+        <item x="93"/>
+        <item x="81"/>
+        <item x="111"/>
+        <item x="82"/>
+        <item x="49"/>
+        <item x="48"/>
+        <item x="68"/>
+        <item x="107"/>
+        <item x="83"/>
+        <item x="42"/>
+        <item x="97"/>
+        <item x="5"/>
+        <item x="11"/>
+        <item x="8"/>
+        <item x="35"/>
+        <item x="25"/>
+        <item x="99"/>
+        <item x="32"/>
+        <item x="22"/>
+        <item x="9"/>
+        <item x="13"/>
+        <item x="126"/>
+        <item x="54"/>
+        <item x="28"/>
+        <item x="53"/>
+        <item x="21"/>
+        <item x="84"/>
+        <item x="20"/>
+        <item x="12"/>
+        <item x="1"/>
+        <item x="86"/>
+        <item x="102"/>
+        <item x="127"/>
+        <item x="30"/>
+        <item x="43"/>
+        <item x="85"/>
+        <item x="112"/>
+        <item x="62"/>
+        <item x="50"/>
+        <item x="98"/>
+        <item x="36"/>
+        <item x="106"/>
+        <item x="17"/>
+        <item x="6"/>
+        <item x="122"/>
+        <item x="52"/>
+        <item x="104"/>
+        <item x="3"/>
+        <item x="7"/>
+        <item x="18"/>
+        <item x="26"/>
+        <item x="103"/>
+        <item x="31"/>
+        <item x="89"/>
+        <item x="118"/>
+        <item x="2"/>
+        <item x="16"/>
+        <item x="55"/>
+        <item x="58"/>
+        <item x="114"/>
+        <item x="33"/>
+        <item x="87"/>
+        <item x="113"/>
+        <item x="69"/>
+        <item x="51"/>
+        <item x="59"/>
+        <item x="101"/>
+        <item x="34"/>
+        <item x="109"/>
+        <item x="61"/>
+        <item x="132"/>
+        <item x="56"/>
+        <item x="64"/>
+        <item x="117"/>
+        <item x="63"/>
+        <item x="100"/>
+        <item x="124"/>
+        <item x="108"/>
+        <item x="115"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="4"/>
+        <item x="15"/>
+        <item x="65"/>
+        <item x="44"/>
+        <item x="119"/>
+        <item x="105"/>
+        <item x="66"/>
+        <item x="120"/>
+        <item x="123"/>
+        <item x="45"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="39"/>
+        <item x="73"/>
+        <item x="110"/>
+        <item x="46"/>
+        <item x="94"/>
+        <item x="74"/>
+        <item x="29"/>
+        <item x="75"/>
+        <item x="90"/>
+        <item x="67"/>
+        <item x="76"/>
+        <item x="38"/>
+        <item x="91"/>
+        <item x="37"/>
+        <item x="40"/>
+        <item x="60"/>
+        <item x="95"/>
+        <item x="77"/>
+        <item x="47"/>
+        <item x="78"/>
+        <item x="131"/>
+        <item x="96"/>
+        <item x="92"/>
+        <item x="79"/>
+        <item h="1" x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="35">
+        <item x="15"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="12"/>
+        <item x="30"/>
+        <item x="13"/>
+        <item x="19"/>
+        <item x="3"/>
+        <item x="28"/>
+        <item x="1"/>
+        <item x="22"/>
+        <item x="31"/>
+        <item x="16"/>
+        <item x="18"/>
+        <item x="24"/>
+        <item x="26"/>
+        <item x="11"/>
+        <item x="14"/>
+        <item x="27"/>
+        <item x="23"/>
+        <item x="8"/>
+        <item x="21"/>
+        <item x="25"/>
+        <item x="17"/>
+        <item x="10"/>
+        <item x="5"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="29"/>
+        <item x="9"/>
+        <item x="7"/>
+        <item x="20"/>
+        <item x="6"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="27">
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="33"/>
+    </i>
+    <i>
+      <x v="42"/>
+    </i>
+    <i>
+      <x v="47"/>
+    </i>
+    <i>
+      <x v="49"/>
+    </i>
+    <i>
+      <x v="56"/>
+    </i>
+    <i>
+      <x v="61"/>
+    </i>
+    <i>
+      <x v="69"/>
+    </i>
+    <i>
+      <x v="70"/>
+    </i>
+    <i>
+      <x v="72"/>
+    </i>
+    <i>
+      <x v="74"/>
+    </i>
+    <i>
+      <x v="86"/>
+    </i>
+    <i>
+      <x v="94"/>
+    </i>
+    <i>
+      <x v="96"/>
+    </i>
+    <i>
+      <x v="101"/>
+    </i>
+    <i>
+      <x v="104"/>
+    </i>
+    <i>
+      <x v="108"/>
+    </i>
+    <i>
+      <x v="112"/>
+    </i>
+    <i>
+      <x v="119"/>
+    </i>
+    <i>
+      <x v="120"/>
+    </i>
+    <i>
+      <x v="121"/>
+    </i>
+    <i>
+      <x v="122"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="14" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Count of Recognition (Award" fld="14" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FC177463-ECB6-493F-84C5-BD2B6B5E3667}" name="PivotTable1" cacheId="197" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:B35" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="18">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -29042,311 +29347,6 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{166599A4-10FF-421A-AFB4-AE0C311C3DFB}" name="PivotTable2" cacheId="472" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="C3:D30" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="18">
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="134">
-        <item x="57"/>
-        <item x="116"/>
-        <item x="10"/>
-        <item x="27"/>
-        <item x="88"/>
-        <item x="19"/>
-        <item x="14"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="125"/>
-        <item x="128"/>
-        <item x="121"/>
-        <item x="41"/>
-        <item x="80"/>
-        <item x="93"/>
-        <item x="81"/>
-        <item x="111"/>
-        <item x="82"/>
-        <item x="49"/>
-        <item x="48"/>
-        <item x="68"/>
-        <item x="107"/>
-        <item x="83"/>
-        <item x="42"/>
-        <item x="97"/>
-        <item x="5"/>
-        <item x="11"/>
-        <item x="8"/>
-        <item x="35"/>
-        <item x="25"/>
-        <item x="99"/>
-        <item x="32"/>
-        <item x="22"/>
-        <item x="9"/>
-        <item x="13"/>
-        <item x="126"/>
-        <item x="54"/>
-        <item x="28"/>
-        <item x="53"/>
-        <item x="21"/>
-        <item x="84"/>
-        <item x="20"/>
-        <item x="12"/>
-        <item x="1"/>
-        <item x="86"/>
-        <item x="102"/>
-        <item x="127"/>
-        <item x="30"/>
-        <item x="43"/>
-        <item x="85"/>
-        <item x="112"/>
-        <item x="62"/>
-        <item x="50"/>
-        <item x="98"/>
-        <item x="36"/>
-        <item x="106"/>
-        <item x="17"/>
-        <item x="6"/>
-        <item x="122"/>
-        <item x="52"/>
-        <item x="104"/>
-        <item x="3"/>
-        <item x="7"/>
-        <item x="18"/>
-        <item x="26"/>
-        <item x="103"/>
-        <item x="31"/>
-        <item x="89"/>
-        <item x="118"/>
-        <item x="2"/>
-        <item x="16"/>
-        <item x="55"/>
-        <item x="58"/>
-        <item x="114"/>
-        <item x="33"/>
-        <item x="87"/>
-        <item x="113"/>
-        <item x="69"/>
-        <item x="51"/>
-        <item x="59"/>
-        <item x="101"/>
-        <item x="34"/>
-        <item x="109"/>
-        <item x="61"/>
-        <item x="132"/>
-        <item x="56"/>
-        <item x="64"/>
-        <item x="117"/>
-        <item x="63"/>
-        <item x="100"/>
-        <item x="124"/>
-        <item x="108"/>
-        <item x="115"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="4"/>
-        <item x="15"/>
-        <item x="65"/>
-        <item x="44"/>
-        <item x="119"/>
-        <item x="105"/>
-        <item x="66"/>
-        <item x="120"/>
-        <item x="123"/>
-        <item x="45"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="39"/>
-        <item x="73"/>
-        <item x="110"/>
-        <item x="46"/>
-        <item x="94"/>
-        <item x="74"/>
-        <item x="29"/>
-        <item x="75"/>
-        <item x="90"/>
-        <item x="67"/>
-        <item x="76"/>
-        <item x="38"/>
-        <item x="91"/>
-        <item x="37"/>
-        <item x="40"/>
-        <item x="60"/>
-        <item x="95"/>
-        <item x="77"/>
-        <item x="47"/>
-        <item x="78"/>
-        <item x="131"/>
-        <item x="96"/>
-        <item x="92"/>
-        <item x="79"/>
-        <item h="1" x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField axis="axisPage" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="35">
-        <item x="15"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="12"/>
-        <item x="30"/>
-        <item x="13"/>
-        <item x="19"/>
-        <item x="3"/>
-        <item x="28"/>
-        <item x="1"/>
-        <item x="22"/>
-        <item x="31"/>
-        <item x="16"/>
-        <item x="18"/>
-        <item x="24"/>
-        <item x="26"/>
-        <item x="11"/>
-        <item x="14"/>
-        <item x="27"/>
-        <item x="23"/>
-        <item x="8"/>
-        <item x="21"/>
-        <item x="25"/>
-        <item x="17"/>
-        <item x="10"/>
-        <item x="5"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="29"/>
-        <item x="9"/>
-        <item x="7"/>
-        <item x="20"/>
-        <item x="6"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="27">
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="23"/>
-    </i>
-    <i>
-      <x v="27"/>
-    </i>
-    <i>
-      <x v="33"/>
-    </i>
-    <i>
-      <x v="42"/>
-    </i>
-    <i>
-      <x v="47"/>
-    </i>
-    <i>
-      <x v="49"/>
-    </i>
-    <i>
-      <x v="56"/>
-    </i>
-    <i>
-      <x v="61"/>
-    </i>
-    <i>
-      <x v="69"/>
-    </i>
-    <i>
-      <x v="70"/>
-    </i>
-    <i>
-      <x v="72"/>
-    </i>
-    <i>
-      <x v="74"/>
-    </i>
-    <i>
-      <x v="86"/>
-    </i>
-    <i>
-      <x v="94"/>
-    </i>
-    <i>
-      <x v="96"/>
-    </i>
-    <i>
-      <x v="101"/>
-    </i>
-    <i>
-      <x v="104"/>
-    </i>
-    <i>
-      <x v="108"/>
-    </i>
-    <i>
-      <x v="112"/>
-    </i>
-    <i>
-      <x v="119"/>
-    </i>
-    <i>
-      <x v="120"/>
-    </i>
-    <i>
-      <x v="121"/>
-    </i>
-    <i>
-      <x v="122"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="1">
-    <pageField fld="14" hier="-1"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField name="Count of Recognition (Award" fld="14" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -29638,6 +29638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:U367"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.95" customHeight="1"/>
   <cols>
@@ -29718,7 +29719,7 @@
       </c>
       <c r="S1" s="11"/>
     </row>
-    <row r="2" spans="1:19" ht="15.95" customHeight="1">
+    <row r="2" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -29753,7 +29754,7 @@
       <c r="R2" s="12"/>
       <c r="S2" s="12"/>
     </row>
-    <row r="3" spans="1:19" ht="15.95" customHeight="1">
+    <row r="3" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -29786,7 +29787,7 @@
       <c r="R3" s="12"/>
       <c r="S3" s="12"/>
     </row>
-    <row r="4" spans="1:19" ht="15.95" customHeight="1">
+    <row r="4" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -29817,7 +29818,7 @@
       <c r="R4" s="12"/>
       <c r="S4" s="12"/>
     </row>
-    <row r="5" spans="1:19" ht="15.95" customHeight="1">
+    <row r="5" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -29856,7 +29857,7 @@
       <c r="R5" s="12"/>
       <c r="S5" s="12"/>
     </row>
-    <row r="6" spans="1:19" ht="15.95" customHeight="1">
+    <row r="6" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -29895,7 +29896,7 @@
       <c r="R6" s="12"/>
       <c r="S6" s="12"/>
     </row>
-    <row r="7" spans="1:19" ht="15.95" customHeight="1">
+    <row r="7" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -29936,7 +29937,7 @@
       <c r="R7" s="12"/>
       <c r="S7" s="12"/>
     </row>
-    <row r="8" spans="1:19" ht="15.95" customHeight="1">
+    <row r="8" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -29975,7 +29976,7 @@
       <c r="R8" s="12"/>
       <c r="S8" s="12"/>
     </row>
-    <row r="9" spans="1:19" ht="15.95" customHeight="1">
+    <row r="9" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -30016,7 +30017,7 @@
       <c r="R9" s="12"/>
       <c r="S9" s="12"/>
     </row>
-    <row r="10" spans="1:19" ht="15.95" customHeight="1">
+    <row r="10" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -30053,7 +30054,7 @@
       <c r="R10" s="12"/>
       <c r="S10" s="12"/>
     </row>
-    <row r="11" spans="1:19" ht="15.95" customHeight="1">
+    <row r="11" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -30092,7 +30093,7 @@
       <c r="R11" s="12"/>
       <c r="S11" s="12"/>
     </row>
-    <row r="12" spans="1:19" ht="15.95" customHeight="1">
+    <row r="12" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -30131,7 +30132,7 @@
       <c r="R12" s="12"/>
       <c r="S12" s="12"/>
     </row>
-    <row r="13" spans="1:19" ht="15.95" customHeight="1">
+    <row r="13" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -30170,7 +30171,7 @@
       <c r="R13" s="12"/>
       <c r="S13" s="12"/>
     </row>
-    <row r="14" spans="1:19" ht="15.95" customHeight="1">
+    <row r="14" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -30209,7 +30210,7 @@
       <c r="R14" s="12"/>
       <c r="S14" s="12"/>
     </row>
-    <row r="15" spans="1:19" ht="15.95" customHeight="1">
+    <row r="15" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -30248,7 +30249,7 @@
       <c r="R15" s="12"/>
       <c r="S15" s="12"/>
     </row>
-    <row r="16" spans="1:19" ht="15.95" customHeight="1">
+    <row r="16" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -30289,7 +30290,7 @@
       <c r="R16" s="12"/>
       <c r="S16" s="12"/>
     </row>
-    <row r="17" spans="1:19" ht="15.95" customHeight="1">
+    <row r="17" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -30328,7 +30329,7 @@
       <c r="R17" s="12"/>
       <c r="S17" s="12"/>
     </row>
-    <row r="18" spans="1:19" ht="15.95" customHeight="1">
+    <row r="18" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -30367,7 +30368,7 @@
       <c r="R18" s="12"/>
       <c r="S18" s="12"/>
     </row>
-    <row r="19" spans="1:19" ht="15.95" customHeight="1">
+    <row r="19" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -30406,7 +30407,7 @@
       <c r="R19" s="12"/>
       <c r="S19" s="12"/>
     </row>
-    <row r="20" spans="1:19" ht="15.95" customHeight="1">
+    <row r="20" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -30445,7 +30446,7 @@
       <c r="R20" s="12"/>
       <c r="S20" s="12"/>
     </row>
-    <row r="21" spans="1:19" ht="15.95" customHeight="1">
+    <row r="21" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -30486,7 +30487,7 @@
       <c r="R21" s="12"/>
       <c r="S21" s="12"/>
     </row>
-    <row r="22" spans="1:19" ht="15.95" customHeight="1">
+    <row r="22" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -30525,7 +30526,7 @@
       <c r="R22" s="12"/>
       <c r="S22" s="12"/>
     </row>
-    <row r="23" spans="1:19" ht="15.95" customHeight="1">
+    <row r="23" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -30564,7 +30565,7 @@
       <c r="R23" s="12"/>
       <c r="S23" s="12"/>
     </row>
-    <row r="24" spans="1:19" ht="15.95" customHeight="1">
+    <row r="24" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -30603,7 +30604,7 @@
       <c r="R24" s="12"/>
       <c r="S24" s="12"/>
     </row>
-    <row r="25" spans="1:19" ht="15.95" customHeight="1">
+    <row r="25" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -30642,7 +30643,7 @@
       <c r="R25" s="12"/>
       <c r="S25" s="12"/>
     </row>
-    <row r="26" spans="1:19" ht="15.95" customHeight="1">
+    <row r="26" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -30681,7 +30682,7 @@
       <c r="R26" s="12"/>
       <c r="S26" s="12"/>
     </row>
-    <row r="27" spans="1:19" ht="15.95" customHeight="1">
+    <row r="27" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -30720,7 +30721,7 @@
       <c r="R27" s="12"/>
       <c r="S27" s="12"/>
     </row>
-    <row r="28" spans="1:19" ht="15.95" customHeight="1">
+    <row r="28" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -30757,7 +30758,7 @@
       <c r="R28" s="12"/>
       <c r="S28" s="12"/>
     </row>
-    <row r="29" spans="1:19" ht="15.95" customHeight="1">
+    <row r="29" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -30794,7 +30795,7 @@
       <c r="R29" s="12"/>
       <c r="S29" s="12"/>
     </row>
-    <row r="30" spans="1:19" ht="15.95" customHeight="1">
+    <row r="30" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -30831,7 +30832,7 @@
       <c r="R30" s="12"/>
       <c r="S30" s="12"/>
     </row>
-    <row r="31" spans="1:19" ht="15.95" customHeight="1">
+    <row r="31" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -30870,7 +30871,7 @@
       <c r="R31" s="12"/>
       <c r="S31" s="12"/>
     </row>
-    <row r="32" spans="1:19" ht="15.95" customHeight="1">
+    <row r="32" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -30909,7 +30910,7 @@
       <c r="R32" s="12"/>
       <c r="S32" s="12"/>
     </row>
-    <row r="33" spans="1:19" ht="15.95" customHeight="1">
+    <row r="33" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -30946,7 +30947,7 @@
       <c r="R33" s="12"/>
       <c r="S33" s="12"/>
     </row>
-    <row r="34" spans="1:19" ht="15.95" customHeight="1">
+    <row r="34" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -30983,7 +30984,7 @@
       <c r="R34" s="12"/>
       <c r="S34" s="12"/>
     </row>
-    <row r="35" spans="1:19" ht="15.95" customHeight="1">
+    <row r="35" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -31022,7 +31023,7 @@
       <c r="R35" s="12"/>
       <c r="S35" s="12"/>
     </row>
-    <row r="36" spans="1:19" ht="15.95" customHeight="1">
+    <row r="36" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -31059,7 +31060,7 @@
       <c r="R36" s="12"/>
       <c r="S36" s="12"/>
     </row>
-    <row r="37" spans="1:19" ht="15.95" customHeight="1">
+    <row r="37" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -31098,7 +31099,7 @@
       <c r="R37" s="12"/>
       <c r="S37" s="12"/>
     </row>
-    <row r="38" spans="1:19" ht="15.95" customHeight="1">
+    <row r="38" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -31135,7 +31136,7 @@
       <c r="R38" s="12"/>
       <c r="S38" s="12"/>
     </row>
-    <row r="39" spans="1:19" ht="15.95" customHeight="1">
+    <row r="39" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -31174,7 +31175,7 @@
       <c r="R39" s="12"/>
       <c r="S39" s="12"/>
     </row>
-    <row r="40" spans="1:19" ht="15.95" customHeight="1">
+    <row r="40" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -31213,7 +31214,7 @@
       <c r="R40" s="12"/>
       <c r="S40" s="12"/>
     </row>
-    <row r="41" spans="1:19" ht="15.95" customHeight="1">
+    <row r="41" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -31252,7 +31253,7 @@
       <c r="R41" s="12"/>
       <c r="S41" s="12"/>
     </row>
-    <row r="42" spans="1:19" ht="15.95" customHeight="1">
+    <row r="42" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -31293,7 +31294,7 @@
       <c r="R42" s="12"/>
       <c r="S42" s="12"/>
     </row>
-    <row r="43" spans="1:19" ht="15.95" customHeight="1">
+    <row r="43" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -31332,7 +31333,7 @@
       <c r="R43" s="12"/>
       <c r="S43" s="12"/>
     </row>
-    <row r="44" spans="1:19" ht="15.95" customHeight="1">
+    <row r="44" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -31371,7 +31372,7 @@
       <c r="R44" s="12"/>
       <c r="S44" s="12"/>
     </row>
-    <row r="45" spans="1:19" ht="15.95" customHeight="1">
+    <row r="45" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -31412,7 +31413,7 @@
       <c r="R45" s="12"/>
       <c r="S45" s="12"/>
     </row>
-    <row r="46" spans="1:19" ht="15.95" customHeight="1">
+    <row r="46" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -31451,7 +31452,7 @@
       <c r="R46" s="12"/>
       <c r="S46" s="12"/>
     </row>
-    <row r="47" spans="1:19" ht="15.95" customHeight="1">
+    <row r="47" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -31492,7 +31493,7 @@
       <c r="R47" s="12"/>
       <c r="S47" s="12"/>
     </row>
-    <row r="48" spans="1:19" ht="15.95" customHeight="1">
+    <row r="48" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A48" s="3">
         <v>47</v>
       </c>
@@ -31531,7 +31532,7 @@
       <c r="R48" s="12"/>
       <c r="S48" s="12"/>
     </row>
-    <row r="49" spans="1:19" ht="15.95" customHeight="1">
+    <row r="49" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -31570,7 +31571,7 @@
       <c r="R49" s="12"/>
       <c r="S49" s="12"/>
     </row>
-    <row r="50" spans="1:19" ht="15.95" customHeight="1">
+    <row r="50" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -31611,7 +31612,7 @@
       <c r="R50" s="12"/>
       <c r="S50" s="12"/>
     </row>
-    <row r="51" spans="1:19" ht="15.95" customHeight="1">
+    <row r="51" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A51" s="3">
         <v>50</v>
       </c>
@@ -31650,7 +31651,7 @@
       <c r="R51" s="12"/>
       <c r="S51" s="12"/>
     </row>
-    <row r="52" spans="1:19" ht="15.95" customHeight="1">
+    <row r="52" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A52" s="3">
         <v>51</v>
       </c>
@@ -31689,7 +31690,7 @@
       <c r="R52" s="12"/>
       <c r="S52" s="12"/>
     </row>
-    <row r="53" spans="1:19" ht="15.95" customHeight="1">
+    <row r="53" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A53" s="3">
         <v>53</v>
       </c>
@@ -31728,7 +31729,7 @@
       <c r="R53" s="12"/>
       <c r="S53" s="12"/>
     </row>
-    <row r="54" spans="1:19" ht="15.95" customHeight="1">
+    <row r="54" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A54" s="3">
         <v>54</v>
       </c>
@@ -31767,7 +31768,7 @@
       <c r="R54" s="12"/>
       <c r="S54" s="12"/>
     </row>
-    <row r="55" spans="1:19" ht="15.95" customHeight="1">
+    <row r="55" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A55" s="3">
         <v>55</v>
       </c>
@@ -31806,7 +31807,7 @@
       <c r="R55" s="12"/>
       <c r="S55" s="12"/>
     </row>
-    <row r="56" spans="1:19" ht="15.95" customHeight="1">
+    <row r="56" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A56" s="3">
         <v>56</v>
       </c>
@@ -31845,7 +31846,7 @@
       <c r="R56" s="12"/>
       <c r="S56" s="12"/>
     </row>
-    <row r="57" spans="1:19" ht="15.95" customHeight="1">
+    <row r="57" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A57" s="3">
         <v>57</v>
       </c>
@@ -31884,7 +31885,7 @@
       <c r="R57" s="12"/>
       <c r="S57" s="12"/>
     </row>
-    <row r="58" spans="1:19" ht="15.95" customHeight="1">
+    <row r="58" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A58" s="3">
         <v>58</v>
       </c>
@@ -31923,7 +31924,7 @@
       <c r="R58" s="12"/>
       <c r="S58" s="12"/>
     </row>
-    <row r="59" spans="1:19" ht="15.95" customHeight="1">
+    <row r="59" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A59" s="3">
         <v>59</v>
       </c>
@@ -31962,7 +31963,7 @@
       <c r="R59" s="12"/>
       <c r="S59" s="12"/>
     </row>
-    <row r="60" spans="1:19" ht="15.95" customHeight="1">
+    <row r="60" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A60" s="3">
         <v>60</v>
       </c>
@@ -32001,7 +32002,7 @@
       <c r="R60" s="12"/>
       <c r="S60" s="12"/>
     </row>
-    <row r="61" spans="1:19" ht="15.95" customHeight="1">
+    <row r="61" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A61" s="3">
         <v>61</v>
       </c>
@@ -32120,7 +32121,7 @@
       <c r="R63" s="3"/>
       <c r="S63" s="3"/>
     </row>
-    <row r="64" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="64" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A64" s="3">
         <v>64</v>
       </c>
@@ -32161,7 +32162,7 @@
       <c r="R64" s="3"/>
       <c r="S64" s="3"/>
     </row>
-    <row r="65" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="65" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A65" s="3">
         <v>65</v>
       </c>
@@ -32202,7 +32203,7 @@
       <c r="R65" s="3"/>
       <c r="S65" s="3"/>
     </row>
-    <row r="66" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="66" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A66" s="3">
         <v>66</v>
       </c>
@@ -32243,7 +32244,7 @@
       <c r="R66" s="3"/>
       <c r="S66" s="3"/>
     </row>
-    <row r="67" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="67" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A67" s="3">
         <v>67</v>
       </c>
@@ -32284,7 +32285,7 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
     </row>
-    <row r="68" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="68" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A68" s="3">
         <v>68</v>
       </c>
@@ -32325,7 +32326,7 @@
       <c r="R68" s="3"/>
       <c r="S68" s="3"/>
     </row>
-    <row r="69" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="69" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A69" s="3">
         <v>69</v>
       </c>
@@ -32368,7 +32369,7 @@
       <c r="R69" s="3"/>
       <c r="S69" s="3"/>
     </row>
-    <row r="70" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="70" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A70" s="3">
         <v>70</v>
       </c>
@@ -32409,7 +32410,7 @@
       <c r="R70" s="3"/>
       <c r="S70" s="3"/>
     </row>
-    <row r="71" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="71" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A71" s="3">
         <v>71</v>
       </c>
@@ -32448,7 +32449,7 @@
       <c r="R71" s="3"/>
       <c r="S71" s="3"/>
     </row>
-    <row r="72" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="72" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A72" s="3">
         <v>72</v>
       </c>
@@ -32487,7 +32488,7 @@
       <c r="R72" s="3"/>
       <c r="S72" s="3"/>
     </row>
-    <row r="73" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="73" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A73" s="3">
         <v>73</v>
       </c>
@@ -32528,7 +32529,7 @@
       <c r="R73" s="3"/>
       <c r="S73" s="3"/>
     </row>
-    <row r="74" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="74" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A74" s="3">
         <v>74</v>
       </c>
@@ -32569,7 +32570,7 @@
       <c r="R74" s="3"/>
       <c r="S74" s="3"/>
     </row>
-    <row r="75" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="75" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A75" s="3">
         <v>75</v>
       </c>
@@ -32608,7 +32609,7 @@
       <c r="R75" s="3"/>
       <c r="S75" s="3"/>
     </row>
-    <row r="76" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="76" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A76" s="3">
         <v>76</v>
       </c>
@@ -32649,7 +32650,7 @@
       <c r="R76" s="3"/>
       <c r="S76" s="3"/>
     </row>
-    <row r="77" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="77" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A77" s="3">
         <v>77</v>
       </c>
@@ -32688,7 +32689,7 @@
       <c r="R77" s="3"/>
       <c r="S77" s="3"/>
     </row>
-    <row r="78" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="78" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A78" s="3">
         <v>78</v>
       </c>
@@ -32727,7 +32728,7 @@
       <c r="R78" s="3"/>
       <c r="S78" s="3"/>
     </row>
-    <row r="79" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="79" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A79" s="3">
         <v>79</v>
       </c>
@@ -32766,7 +32767,7 @@
       <c r="R79" s="3"/>
       <c r="S79" s="3"/>
     </row>
-    <row r="80" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="80" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A80" s="3">
         <v>80</v>
       </c>
@@ -32807,7 +32808,7 @@
       <c r="R80" s="3"/>
       <c r="S80" s="3"/>
     </row>
-    <row r="81" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="81" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A81" s="3">
         <v>81</v>
       </c>
@@ -32846,7 +32847,7 @@
       <c r="R81" s="3"/>
       <c r="S81" s="3"/>
     </row>
-    <row r="82" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="82" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A82" s="3">
         <v>82</v>
       </c>
@@ -32891,7 +32892,7 @@
       </c>
       <c r="S82" s="3"/>
     </row>
-    <row r="83" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="83" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A83" s="3">
         <v>83</v>
       </c>
@@ -32934,7 +32935,7 @@
       <c r="R83" s="3"/>
       <c r="S83" s="3"/>
     </row>
-    <row r="84" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="84" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A84" s="3">
         <v>84</v>
       </c>
@@ -32973,7 +32974,7 @@
       <c r="R84" s="3"/>
       <c r="S84" s="3"/>
     </row>
-    <row r="85" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="85" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A85" s="3">
         <v>85</v>
       </c>
@@ -33012,7 +33013,7 @@
       <c r="R85" s="3"/>
       <c r="S85" s="3"/>
     </row>
-    <row r="86" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="86" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A86" s="3">
         <v>86</v>
       </c>
@@ -33051,7 +33052,7 @@
       <c r="R86" s="3"/>
       <c r="S86" s="3"/>
     </row>
-    <row r="87" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="87" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A87" s="3">
         <v>87</v>
       </c>
@@ -33092,7 +33093,7 @@
       <c r="R87" s="3"/>
       <c r="S87" s="3"/>
     </row>
-    <row r="88" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="88" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A88" s="3">
         <v>88</v>
       </c>
@@ -33133,7 +33134,7 @@
       <c r="R88" s="3"/>
       <c r="S88" s="3"/>
     </row>
-    <row r="89" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="89" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A89" s="3">
         <v>89</v>
       </c>
@@ -33176,7 +33177,7 @@
       </c>
       <c r="S89" s="3"/>
     </row>
-    <row r="90" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="90" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A90" s="3">
         <v>90</v>
       </c>
@@ -33217,7 +33218,7 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
     </row>
-    <row r="91" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="91" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A91" s="3">
         <v>91</v>
       </c>
@@ -33258,7 +33259,7 @@
       </c>
       <c r="S91" s="3"/>
     </row>
-    <row r="92" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="92" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A92" s="3">
         <v>92</v>
       </c>
@@ -33297,7 +33298,7 @@
       <c r="R92" s="3"/>
       <c r="S92" s="3"/>
     </row>
-    <row r="93" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="93" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A93" s="3">
         <v>93</v>
       </c>
@@ -33338,7 +33339,7 @@
       <c r="R93" s="3"/>
       <c r="S93" s="3"/>
     </row>
-    <row r="94" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="94" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A94" s="3">
         <v>94</v>
       </c>
@@ -33377,7 +33378,7 @@
       <c r="R94" s="3"/>
       <c r="S94" s="3"/>
     </row>
-    <row r="95" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="95" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A95" s="3">
         <v>95</v>
       </c>
@@ -33420,7 +33421,7 @@
       </c>
       <c r="S95" s="3"/>
     </row>
-    <row r="96" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="96" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A96" s="3">
         <v>96</v>
       </c>
@@ -33463,7 +33464,7 @@
       </c>
       <c r="S96" s="3"/>
     </row>
-    <row r="97" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="97" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A97" s="3">
         <v>97</v>
       </c>
@@ -33508,7 +33509,7 @@
       </c>
       <c r="S97" s="3"/>
     </row>
-    <row r="98" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="98" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A98" s="3">
         <v>223</v>
       </c>
@@ -33549,7 +33550,7 @@
       <c r="R98" s="3"/>
       <c r="S98" s="3"/>
     </row>
-    <row r="99" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="99" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A99" s="3">
         <v>99</v>
       </c>
@@ -33588,7 +33589,7 @@
       <c r="R99" s="3"/>
       <c r="S99" s="3"/>
     </row>
-    <row r="100" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="100" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A100" s="3">
         <v>100</v>
       </c>
@@ -33627,7 +33628,7 @@
       <c r="R100" s="3"/>
       <c r="S100" s="3"/>
     </row>
-    <row r="101" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="101" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A101" s="3">
         <v>101</v>
       </c>
@@ -33666,7 +33667,7 @@
       <c r="R101" s="3"/>
       <c r="S101" s="3"/>
     </row>
-    <row r="102" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="102" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A102" s="3">
         <v>102</v>
       </c>
@@ -33705,7 +33706,7 @@
       <c r="R102" s="3"/>
       <c r="S102" s="3"/>
     </row>
-    <row r="103" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="103" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A103" s="3">
         <v>103</v>
       </c>
@@ -33748,7 +33749,7 @@
       </c>
       <c r="S103" s="3"/>
     </row>
-    <row r="104" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="104" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A104" s="3">
         <v>104</v>
       </c>
@@ -33785,7 +33786,7 @@
       <c r="R104" s="3"/>
       <c r="S104" s="3"/>
     </row>
-    <row r="105" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="105" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A105" s="3">
         <v>105</v>
       </c>
@@ -33824,7 +33825,7 @@
       <c r="R105" s="3"/>
       <c r="S105" s="3"/>
     </row>
-    <row r="106" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="106" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A106" s="3">
         <v>106</v>
       </c>
@@ -33863,7 +33864,7 @@
       <c r="R106" s="3"/>
       <c r="S106" s="3"/>
     </row>
-    <row r="107" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="107" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A107" s="3">
         <v>107</v>
       </c>
@@ -33902,7 +33903,7 @@
       <c r="R107" s="3"/>
       <c r="S107" s="3"/>
     </row>
-    <row r="108" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="108" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A108" s="3">
         <v>108</v>
       </c>
@@ -33941,7 +33942,7 @@
       <c r="R108" s="3"/>
       <c r="S108" s="3"/>
     </row>
-    <row r="109" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="109" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A109" s="3">
         <v>109</v>
       </c>
@@ -33980,7 +33981,7 @@
       <c r="R109" s="3"/>
       <c r="S109" s="3"/>
     </row>
-    <row r="110" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="110" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A110" s="3">
         <v>110</v>
       </c>
@@ -34019,7 +34020,7 @@
       <c r="R110" s="3"/>
       <c r="S110" s="3"/>
     </row>
-    <row r="111" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="111" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A111" s="3">
         <v>111</v>
       </c>
@@ -34058,7 +34059,7 @@
       <c r="R111" s="3"/>
       <c r="S111" s="3"/>
     </row>
-    <row r="112" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="112" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A112" s="3">
         <v>112</v>
       </c>
@@ -34097,7 +34098,7 @@
       <c r="R112" s="3"/>
       <c r="S112" s="3"/>
     </row>
-    <row r="113" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="113" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A113" s="3">
         <v>113</v>
       </c>
@@ -34136,7 +34137,7 @@
       <c r="R113" s="3"/>
       <c r="S113" s="3"/>
     </row>
-    <row r="114" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="114" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A114" s="3">
         <v>114</v>
       </c>
@@ -34175,7 +34176,7 @@
       <c r="R114" s="3"/>
       <c r="S114" s="3"/>
     </row>
-    <row r="115" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="115" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A115" s="3">
         <v>115</v>
       </c>
@@ -34214,7 +34215,7 @@
       <c r="R115" s="3"/>
       <c r="S115" s="3"/>
     </row>
-    <row r="116" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="116" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A116" s="3">
         <v>116</v>
       </c>
@@ -34253,7 +34254,7 @@
       <c r="R116" s="3"/>
       <c r="S116" s="3"/>
     </row>
-    <row r="117" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="117" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A117" s="3">
         <v>117</v>
       </c>
@@ -34292,7 +34293,7 @@
       <c r="R117" s="3"/>
       <c r="S117" s="3"/>
     </row>
-    <row r="118" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="118" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A118" s="3">
         <v>290</v>
       </c>
@@ -34335,7 +34336,7 @@
       <c r="R118" s="3"/>
       <c r="S118" s="3"/>
     </row>
-    <row r="119" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="119" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A119" s="3">
         <v>119</v>
       </c>
@@ -34374,7 +34375,7 @@
       <c r="R119" s="3"/>
       <c r="S119" s="3"/>
     </row>
-    <row r="120" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="120" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A120" s="3">
         <v>120</v>
       </c>
@@ -34413,7 +34414,7 @@
       <c r="R120" s="3"/>
       <c r="S120" s="3"/>
     </row>
-    <row r="121" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="121" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A121" s="3">
         <v>121</v>
       </c>
@@ -34454,7 +34455,7 @@
       </c>
       <c r="S121" s="3"/>
     </row>
-    <row r="122" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="122" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A122" s="3">
         <v>122</v>
       </c>
@@ -34497,7 +34498,7 @@
       </c>
       <c r="S122" s="3"/>
     </row>
-    <row r="123" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="123" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A123" s="3">
         <v>123</v>
       </c>
@@ -34538,7 +34539,7 @@
       </c>
       <c r="S123" s="3"/>
     </row>
-    <row r="124" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="124" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A124" s="3">
         <v>124</v>
       </c>
@@ -34577,7 +34578,7 @@
       <c r="R124" s="3"/>
       <c r="S124" s="3"/>
     </row>
-    <row r="125" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="125" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A125" s="3">
         <v>125</v>
       </c>
@@ -34616,7 +34617,7 @@
       <c r="R125" s="3"/>
       <c r="S125" s="3"/>
     </row>
-    <row r="126" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="126" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A126" s="3">
         <v>126</v>
       </c>
@@ -34657,7 +34658,7 @@
       <c r="R126" s="3"/>
       <c r="S126" s="3"/>
     </row>
-    <row r="127" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="127" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A127" s="3">
         <v>127</v>
       </c>
@@ -34696,7 +34697,7 @@
       <c r="R127" s="3"/>
       <c r="S127" s="3"/>
     </row>
-    <row r="128" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="128" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A128" s="3">
         <v>128</v>
       </c>
@@ -34741,7 +34742,7 @@
       </c>
       <c r="S128" s="3"/>
     </row>
-    <row r="129" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="129" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A129" s="3">
         <v>129</v>
       </c>
@@ -34784,7 +34785,7 @@
       <c r="R129" s="3"/>
       <c r="S129" s="3"/>
     </row>
-    <row r="130" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="130" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A130" s="3">
         <v>130</v>
       </c>
@@ -34823,7 +34824,7 @@
       <c r="R130" s="3"/>
       <c r="S130" s="3"/>
     </row>
-    <row r="131" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="131" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A131" s="3">
         <v>131</v>
       </c>
@@ -34864,7 +34865,7 @@
       <c r="R131" s="3"/>
       <c r="S131" s="3"/>
     </row>
-    <row r="132" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="132" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A132" s="3">
         <v>132</v>
       </c>
@@ -34903,7 +34904,7 @@
       <c r="R132" s="3"/>
       <c r="S132" s="3"/>
     </row>
-    <row r="133" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="133" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A133" s="3">
         <v>133</v>
       </c>
@@ -34948,7 +34949,7 @@
       </c>
       <c r="S133" s="3"/>
     </row>
-    <row r="134" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="134" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A134" s="3">
         <v>134</v>
       </c>
@@ -34989,7 +34990,7 @@
       <c r="R134" s="3"/>
       <c r="S134" s="3"/>
     </row>
-    <row r="135" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="135" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A135" s="3">
         <v>135</v>
       </c>
@@ -35026,7 +35027,7 @@
       <c r="R135" s="3"/>
       <c r="S135" s="3"/>
     </row>
-    <row r="136" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="136" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A136" s="3">
         <v>136</v>
       </c>
@@ -35067,7 +35068,7 @@
       </c>
       <c r="S136" s="3"/>
     </row>
-    <row r="137" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="137" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A137" s="3">
         <v>137</v>
       </c>
@@ -35108,7 +35109,7 @@
       <c r="R137" s="3"/>
       <c r="S137" s="3"/>
     </row>
-    <row r="138" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="138" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A138" s="3">
         <v>138</v>
       </c>
@@ -35151,7 +35152,7 @@
       <c r="R138" s="3"/>
       <c r="S138" s="3"/>
     </row>
-    <row r="139" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="139" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A139" s="3">
         <v>139</v>
       </c>
@@ -35192,7 +35193,7 @@
       <c r="R139" s="3"/>
       <c r="S139" s="3"/>
     </row>
-    <row r="140" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="140" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A140" s="3">
         <v>118</v>
       </c>
@@ -35231,7 +35232,7 @@
       <c r="R140" s="3"/>
       <c r="S140" s="3"/>
     </row>
-    <row r="141" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="141" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A141" s="3">
         <v>141</v>
       </c>
@@ -35270,7 +35271,7 @@
       <c r="R141" s="3"/>
       <c r="S141" s="3"/>
     </row>
-    <row r="142" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="142" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A142" s="3">
         <v>142</v>
       </c>
@@ -35309,7 +35310,7 @@
       <c r="R142" s="3"/>
       <c r="S142" s="3"/>
     </row>
-    <row r="143" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="143" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A143" s="3">
         <v>143</v>
       </c>
@@ -35348,7 +35349,7 @@
       <c r="R143" s="3"/>
       <c r="S143" s="3"/>
     </row>
-    <row r="144" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="144" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A144" s="3">
         <v>144</v>
       </c>
@@ -35387,7 +35388,7 @@
       <c r="R144" s="3"/>
       <c r="S144" s="3"/>
     </row>
-    <row r="145" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="145" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A145" s="3">
         <v>145</v>
       </c>
@@ -35426,7 +35427,7 @@
       <c r="R145" s="3"/>
       <c r="S145" s="3"/>
     </row>
-    <row r="146" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="146" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A146" s="3">
         <v>146</v>
       </c>
@@ -35463,7 +35464,7 @@
       <c r="R146" s="3"/>
       <c r="S146" s="3"/>
     </row>
-    <row r="147" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="147" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A147" s="3">
         <v>147</v>
       </c>
@@ -35502,7 +35503,7 @@
       <c r="R147" s="3"/>
       <c r="S147" s="3"/>
     </row>
-    <row r="148" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="148" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A148" s="3">
         <v>148</v>
       </c>
@@ -35541,7 +35542,7 @@
       <c r="R148" s="3"/>
       <c r="S148" s="3"/>
     </row>
-    <row r="149" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="149" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A149" s="3">
         <v>149</v>
       </c>
@@ -35580,7 +35581,7 @@
       <c r="R149" s="3"/>
       <c r="S149" s="3"/>
     </row>
-    <row r="150" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="150" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A150" s="3">
         <v>150</v>
       </c>
@@ -35619,7 +35620,7 @@
       <c r="R150" s="3"/>
       <c r="S150" s="3"/>
     </row>
-    <row r="151" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="151" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A151" s="3">
         <v>151</v>
       </c>
@@ -35697,7 +35698,7 @@
       <c r="R152" s="3"/>
       <c r="S152" s="3"/>
     </row>
-    <row r="153" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="153" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A153" s="3">
         <v>153</v>
       </c>
@@ -35736,7 +35737,7 @@
       <c r="R153" s="3"/>
       <c r="S153" s="3"/>
     </row>
-    <row r="154" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="154" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A154" s="3">
         <v>154</v>
       </c>
@@ -35775,7 +35776,7 @@
       <c r="R154" s="3"/>
       <c r="S154" s="3"/>
     </row>
-    <row r="155" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="155" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A155" s="3">
         <v>155</v>
       </c>
@@ -35814,7 +35815,7 @@
       <c r="R155" s="3"/>
       <c r="S155" s="3"/>
     </row>
-    <row r="156" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="156" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A156" s="3">
         <v>156</v>
       </c>
@@ -35853,7 +35854,7 @@
       <c r="R156" s="3"/>
       <c r="S156" s="3"/>
     </row>
-    <row r="157" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="157" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A157" s="3">
         <v>157</v>
       </c>
@@ -35892,7 +35893,7 @@
       <c r="R157" s="3"/>
       <c r="S157" s="3"/>
     </row>
-    <row r="158" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="158" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A158" s="3">
         <v>158</v>
       </c>
@@ -35931,7 +35932,7 @@
       <c r="R158" s="3"/>
       <c r="S158" s="3"/>
     </row>
-    <row r="159" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="159" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A159" s="3">
         <v>159</v>
       </c>
@@ -35970,7 +35971,7 @@
       <c r="R159" s="3"/>
       <c r="S159" s="3"/>
     </row>
-    <row r="160" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="160" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A160" s="3">
         <v>160</v>
       </c>
@@ -36011,7 +36012,7 @@
       <c r="R160" s="3"/>
       <c r="S160" s="3"/>
     </row>
-    <row r="161" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="161" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A161" s="3">
         <v>161</v>
       </c>
@@ -36050,7 +36051,7 @@
       <c r="R161" s="3"/>
       <c r="S161" s="3"/>
     </row>
-    <row r="162" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="162" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A162" s="3">
         <v>162</v>
       </c>
@@ -36089,7 +36090,7 @@
       <c r="R162" s="3"/>
       <c r="S162" s="3"/>
     </row>
-    <row r="163" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="163" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A163" s="3">
         <v>163</v>
       </c>
@@ -36130,7 +36131,7 @@
       </c>
       <c r="S163" s="3"/>
     </row>
-    <row r="164" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="164" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A164" s="3">
         <v>164</v>
       </c>
@@ -36173,7 +36174,7 @@
       <c r="R164" s="3"/>
       <c r="S164" s="3"/>
     </row>
-    <row r="165" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="165" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A165" s="3">
         <v>165</v>
       </c>
@@ -36214,7 +36215,7 @@
       <c r="R165" s="3"/>
       <c r="S165" s="3"/>
     </row>
-    <row r="166" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="166" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A166" s="3">
         <v>166</v>
       </c>
@@ -36255,7 +36256,7 @@
       <c r="R166" s="3"/>
       <c r="S166" s="3"/>
     </row>
-    <row r="167" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="167" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A167" s="3">
         <v>167</v>
       </c>
@@ -36296,7 +36297,7 @@
       <c r="R167" s="3"/>
       <c r="S167" s="3"/>
     </row>
-    <row r="168" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="168" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A168" s="3">
         <v>168</v>
       </c>
@@ -36343,7 +36344,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="169" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="169" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A169" s="3">
         <v>169</v>
       </c>
@@ -36386,7 +36387,7 @@
       <c r="R169" s="3"/>
       <c r="S169" s="3"/>
     </row>
-    <row r="170" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="170" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A170" s="3">
         <v>170</v>
       </c>
@@ -36427,7 +36428,7 @@
       <c r="R170" s="3"/>
       <c r="S170" s="3"/>
     </row>
-    <row r="171" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="171" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A171" s="3">
         <v>171</v>
       </c>
@@ -36468,7 +36469,7 @@
       <c r="R171" s="3"/>
       <c r="S171" s="3"/>
     </row>
-    <row r="172" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="172" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A172" s="3">
         <v>172</v>
       </c>
@@ -36509,7 +36510,7 @@
       <c r="R172" s="3"/>
       <c r="S172" s="3"/>
     </row>
-    <row r="173" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="173" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A173" s="3">
         <v>173</v>
       </c>
@@ -36550,7 +36551,7 @@
       <c r="R173" s="3"/>
       <c r="S173" s="3"/>
     </row>
-    <row r="174" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="174" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A174" s="3">
         <v>174</v>
       </c>
@@ -36589,7 +36590,7 @@
       <c r="R174" s="3"/>
       <c r="S174" s="3"/>
     </row>
-    <row r="175" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="175" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A175" s="3">
         <v>175</v>
       </c>
@@ -36630,7 +36631,7 @@
       <c r="R175" s="3"/>
       <c r="S175" s="3"/>
     </row>
-    <row r="176" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="176" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A176" s="3">
         <v>176</v>
       </c>
@@ -36671,7 +36672,7 @@
       <c r="R176" s="3"/>
       <c r="S176" s="3"/>
     </row>
-    <row r="177" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="177" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A177" s="3">
         <v>177</v>
       </c>
@@ -36712,7 +36713,7 @@
       <c r="R177" s="3"/>
       <c r="S177" s="3"/>
     </row>
-    <row r="178" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="178" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A178" s="3">
         <v>178</v>
       </c>
@@ -36751,7 +36752,7 @@
       <c r="R178" s="3"/>
       <c r="S178" s="3"/>
     </row>
-    <row r="179" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="179" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A179" s="3">
         <v>179</v>
       </c>
@@ -36792,7 +36793,7 @@
       <c r="R179" s="3"/>
       <c r="S179" s="3"/>
     </row>
-    <row r="180" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="180" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A180" s="3">
         <v>180</v>
       </c>
@@ -36833,7 +36834,7 @@
       <c r="R180" s="3"/>
       <c r="S180" s="3"/>
     </row>
-    <row r="181" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="181" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A181" s="3">
         <v>181</v>
       </c>
@@ -36874,7 +36875,7 @@
       <c r="R181" s="3"/>
       <c r="S181" s="3"/>
     </row>
-    <row r="182" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="182" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A182" s="3">
         <v>182</v>
       </c>
@@ -36915,7 +36916,7 @@
       <c r="R182" s="3"/>
       <c r="S182" s="3"/>
     </row>
-    <row r="183" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="183" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A183" s="3">
         <v>183</v>
       </c>
@@ -36964,7 +36965,7 @@
       </c>
       <c r="S183" s="3"/>
     </row>
-    <row r="184" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="184" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A184" s="3">
         <v>184</v>
       </c>
@@ -37005,7 +37006,7 @@
       <c r="R184" s="3"/>
       <c r="S184" s="3"/>
     </row>
-    <row r="185" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="185" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A185" s="3">
         <v>185</v>
       </c>
@@ -37046,7 +37047,7 @@
       <c r="R185" s="3"/>
       <c r="S185" s="3"/>
     </row>
-    <row r="186" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="186" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A186" s="3">
         <v>186</v>
       </c>
@@ -37091,7 +37092,7 @@
       </c>
       <c r="S186" s="3"/>
     </row>
-    <row r="187" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="187" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A187" s="3">
         <v>187</v>
       </c>
@@ -37132,7 +37133,7 @@
       <c r="R187" s="3"/>
       <c r="S187" s="3"/>
     </row>
-    <row r="188" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="188" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A188" s="3">
         <v>188</v>
       </c>
@@ -37173,7 +37174,7 @@
       <c r="R188" s="3"/>
       <c r="S188" s="3"/>
     </row>
-    <row r="189" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="189" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A189" s="3">
         <v>189</v>
       </c>
@@ -37218,7 +37219,7 @@
       <c r="R189" s="3"/>
       <c r="S189" s="3"/>
     </row>
-    <row r="190" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="190" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A190" s="3">
         <v>190</v>
       </c>
@@ -37259,7 +37260,7 @@
       <c r="R190" s="3"/>
       <c r="S190" s="3"/>
     </row>
-    <row r="191" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="191" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A191" s="3">
         <v>191</v>
       </c>
@@ -37304,7 +37305,7 @@
       <c r="R191" s="3"/>
       <c r="S191" s="3"/>
     </row>
-    <row r="192" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="192" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A192" s="3">
         <v>192</v>
       </c>
@@ -37345,7 +37346,7 @@
       <c r="R192" s="3"/>
       <c r="S192" s="3"/>
     </row>
-    <row r="193" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="193" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A193" s="3">
         <v>193</v>
       </c>
@@ -37386,7 +37387,7 @@
       <c r="R193" s="3"/>
       <c r="S193" s="3"/>
     </row>
-    <row r="194" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="194" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A194" s="3">
         <v>194</v>
       </c>
@@ -37427,7 +37428,7 @@
       <c r="R194" s="3"/>
       <c r="S194" s="3"/>
     </row>
-    <row r="195" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="195" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A195" s="3">
         <v>195</v>
       </c>
@@ -37470,7 +37471,7 @@
       <c r="R195" s="3"/>
       <c r="S195" s="3"/>
     </row>
-    <row r="196" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="196" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A196" s="3">
         <v>196</v>
       </c>
@@ -37513,7 +37514,7 @@
       <c r="R196" s="3"/>
       <c r="S196" s="3"/>
     </row>
-    <row r="197" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="197" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A197" s="3">
         <v>197</v>
       </c>
@@ -37554,7 +37555,7 @@
       <c r="R197" s="3"/>
       <c r="S197" s="3"/>
     </row>
-    <row r="198" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="198" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A198" s="3">
         <v>198</v>
       </c>
@@ -37597,7 +37598,7 @@
       <c r="R198" s="3"/>
       <c r="S198" s="3"/>
     </row>
-    <row r="199" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="199" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A199" s="3">
         <v>199</v>
       </c>
@@ -37640,7 +37641,7 @@
       <c r="R199" s="3"/>
       <c r="S199" s="3"/>
     </row>
-    <row r="200" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="200" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A200" s="3">
         <v>200</v>
       </c>
@@ -37683,7 +37684,7 @@
       <c r="R200" s="3"/>
       <c r="S200" s="3"/>
     </row>
-    <row r="201" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="201" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A201" s="3">
         <v>201</v>
       </c>
@@ -37726,7 +37727,7 @@
       <c r="R201" s="3"/>
       <c r="S201" s="3"/>
     </row>
-    <row r="202" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="202" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A202" s="3">
         <v>202</v>
       </c>
@@ -37771,7 +37772,7 @@
       </c>
       <c r="S202" s="3"/>
     </row>
-    <row r="203" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="203" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A203" s="3">
         <v>203</v>
       </c>
@@ -37814,7 +37815,7 @@
       <c r="R203" s="3"/>
       <c r="S203" s="3"/>
     </row>
-    <row r="204" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="204" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A204" s="3">
         <v>204</v>
       </c>
@@ -37855,7 +37856,7 @@
       <c r="R204" s="3"/>
       <c r="S204" s="3"/>
     </row>
-    <row r="205" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="205" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A205" s="3">
         <v>205</v>
       </c>
@@ -37896,7 +37897,7 @@
       <c r="R205" s="3"/>
       <c r="S205" s="3"/>
     </row>
-    <row r="206" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="206" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A206" s="3">
         <v>206</v>
       </c>
@@ -37937,7 +37938,7 @@
       <c r="R206" s="3"/>
       <c r="S206" s="3"/>
     </row>
-    <row r="207" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="207" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A207" s="3">
         <v>207</v>
       </c>
@@ -37978,7 +37979,7 @@
       <c r="R207" s="3"/>
       <c r="S207" s="3"/>
     </row>
-    <row r="208" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="208" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A208" s="3">
         <v>208</v>
       </c>
@@ -38019,7 +38020,7 @@
       <c r="R208" s="3"/>
       <c r="S208" s="3"/>
     </row>
-    <row r="209" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="209" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A209" s="3">
         <v>209</v>
       </c>
@@ -38064,7 +38065,7 @@
       </c>
       <c r="S209" s="3"/>
     </row>
-    <row r="210" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="210" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A210" s="3">
         <v>210</v>
       </c>
@@ -38105,7 +38106,7 @@
       <c r="R210" s="3"/>
       <c r="S210" s="3"/>
     </row>
-    <row r="211" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="211" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A211" s="3">
         <v>211</v>
       </c>
@@ -38148,7 +38149,7 @@
       <c r="R211" s="3"/>
       <c r="S211" s="3"/>
     </row>
-    <row r="212" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="212" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A212" s="3">
         <v>212</v>
       </c>
@@ -38191,7 +38192,7 @@
       <c r="R212" s="3"/>
       <c r="S212" s="3"/>
     </row>
-    <row r="213" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="213" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A213" s="3">
         <v>213</v>
       </c>
@@ -38232,7 +38233,7 @@
       <c r="R213" s="3"/>
       <c r="S213" s="3"/>
     </row>
-    <row r="214" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="214" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A214" s="3">
         <v>214</v>
       </c>
@@ -38273,7 +38274,7 @@
       <c r="R214" s="3"/>
       <c r="S214" s="3"/>
     </row>
-    <row r="215" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="215" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A215" s="3">
         <v>215</v>
       </c>
@@ -38314,7 +38315,7 @@
       <c r="R215" s="3"/>
       <c r="S215" s="3"/>
     </row>
-    <row r="216" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="216" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A216" s="3">
         <v>216</v>
       </c>
@@ -38355,7 +38356,7 @@
       <c r="R216" s="3"/>
       <c r="S216" s="3"/>
     </row>
-    <row r="217" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="217" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A217" s="3">
         <v>217</v>
       </c>
@@ -38396,7 +38397,7 @@
       <c r="R217" s="3"/>
       <c r="S217" s="3"/>
     </row>
-    <row r="218" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="218" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A218" s="3">
         <v>218</v>
       </c>
@@ -38437,7 +38438,7 @@
       <c r="R218" s="3"/>
       <c r="S218" s="3"/>
     </row>
-    <row r="219" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="219" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A219" s="3">
         <v>219</v>
       </c>
@@ -38478,7 +38479,7 @@
       <c r="R219" s="3"/>
       <c r="S219" s="3"/>
     </row>
-    <row r="220" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="220" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A220" s="3">
         <v>220</v>
       </c>
@@ -38519,7 +38520,7 @@
       <c r="R220" s="3"/>
       <c r="S220" s="3"/>
     </row>
-    <row r="221" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="221" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A221" s="3">
         <v>221</v>
       </c>
@@ -38560,7 +38561,7 @@
       <c r="R221" s="3"/>
       <c r="S221" s="3"/>
     </row>
-    <row r="222" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="222" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A222" s="3">
         <v>222</v>
       </c>
@@ -38601,7 +38602,7 @@
       <c r="R222" s="3"/>
       <c r="S222" s="3"/>
     </row>
-    <row r="223" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="223" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A223" s="3">
         <v>98</v>
       </c>
@@ -38644,7 +38645,7 @@
       </c>
       <c r="S223" s="3"/>
     </row>
-    <row r="224" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="224" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A224" s="3">
         <v>224</v>
       </c>
@@ -38685,7 +38686,7 @@
       <c r="R224" s="3"/>
       <c r="S224" s="3"/>
     </row>
-    <row r="225" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="225" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A225" s="3">
         <v>225</v>
       </c>
@@ -38728,7 +38729,7 @@
       <c r="R225" s="3"/>
       <c r="S225" s="3"/>
     </row>
-    <row r="226" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="226" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A226" s="3">
         <v>226</v>
       </c>
@@ -38771,7 +38772,7 @@
       <c r="R226" s="3"/>
       <c r="S226" s="3"/>
     </row>
-    <row r="227" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="227" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A227" s="3">
         <v>227</v>
       </c>
@@ -38816,7 +38817,7 @@
       <c r="R227" s="3"/>
       <c r="S227" s="3"/>
     </row>
-    <row r="228" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="228" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A228" s="3">
         <v>228</v>
       </c>
@@ -38861,7 +38862,7 @@
       <c r="R228" s="3"/>
       <c r="S228" s="3"/>
     </row>
-    <row r="229" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="229" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A229" s="3">
         <v>229</v>
       </c>
@@ -38906,7 +38907,7 @@
       <c r="R229" s="3"/>
       <c r="S229" s="3"/>
     </row>
-    <row r="230" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="230" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A230" s="3">
         <v>230</v>
       </c>
@@ -38951,7 +38952,7 @@
       <c r="R230" s="3"/>
       <c r="S230" s="3"/>
     </row>
-    <row r="231" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="231" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A231" s="3">
         <v>231</v>
       </c>
@@ -38996,7 +38997,7 @@
       <c r="R231" s="3"/>
       <c r="S231" s="3"/>
     </row>
-    <row r="232" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="232" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A232" s="3">
         <v>232</v>
       </c>
@@ -39041,7 +39042,7 @@
       <c r="R232" s="3"/>
       <c r="S232" s="3"/>
     </row>
-    <row r="233" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="233" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A233" s="3">
         <v>233</v>
       </c>
@@ -39086,7 +39087,7 @@
       <c r="R233" s="3"/>
       <c r="S233" s="3"/>
     </row>
-    <row r="234" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="234" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A234" s="3">
         <v>234</v>
       </c>
@@ -39131,7 +39132,7 @@
       <c r="R234" s="3"/>
       <c r="S234" s="3"/>
     </row>
-    <row r="235" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="235" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A235" s="3">
         <v>235</v>
       </c>
@@ -39174,7 +39175,7 @@
       <c r="R235" s="3"/>
       <c r="S235" s="3"/>
     </row>
-    <row r="236" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="236" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A236" s="3">
         <v>236</v>
       </c>
@@ -39217,7 +39218,7 @@
       <c r="R236" s="3"/>
       <c r="S236" s="3"/>
     </row>
-    <row r="237" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="237" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A237" s="3">
         <v>237</v>
       </c>
@@ -39264,7 +39265,7 @@
       <c r="R237" s="3"/>
       <c r="S237" s="3"/>
     </row>
-    <row r="238" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="238" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A238" s="3">
         <v>238</v>
       </c>
@@ -39309,7 +39310,7 @@
       <c r="R238" s="3"/>
       <c r="S238" s="3"/>
     </row>
-    <row r="239" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="239" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A239" s="3">
         <v>239</v>
       </c>
@@ -39352,7 +39353,7 @@
       <c r="R239" s="3"/>
       <c r="S239" s="3"/>
     </row>
-    <row r="240" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="240" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A240" s="3">
         <v>240</v>
       </c>
@@ -39395,7 +39396,7 @@
       <c r="R240" s="3"/>
       <c r="S240" s="3"/>
     </row>
-    <row r="241" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="241" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A241" s="3">
         <v>241</v>
       </c>
@@ -39440,7 +39441,7 @@
       <c r="R241" s="3"/>
       <c r="S241" s="3"/>
     </row>
-    <row r="242" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="242" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A242" s="3">
         <v>242</v>
       </c>
@@ -39487,7 +39488,7 @@
       <c r="R242" s="3"/>
       <c r="S242" s="3"/>
     </row>
-    <row r="243" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="243" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A243" s="3">
         <v>243</v>
       </c>
@@ -39530,7 +39531,7 @@
       <c r="R243" s="3"/>
       <c r="S243" s="3"/>
     </row>
-    <row r="244" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="244" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A244" s="3">
         <v>244</v>
       </c>
@@ -39575,7 +39576,7 @@
       <c r="R244" s="3"/>
       <c r="S244" s="3"/>
     </row>
-    <row r="245" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="245" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A245" s="3">
         <v>245</v>
       </c>
@@ -39618,7 +39619,7 @@
       <c r="R245" s="3"/>
       <c r="S245" s="3"/>
     </row>
-    <row r="246" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="246" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A246" s="3">
         <v>246</v>
       </c>
@@ -39661,7 +39662,7 @@
       <c r="R246" s="3"/>
       <c r="S246" s="3"/>
     </row>
-    <row r="247" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="247" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A247" s="3">
         <v>247</v>
       </c>
@@ -39704,7 +39705,7 @@
       <c r="R247" s="3"/>
       <c r="S247" s="3"/>
     </row>
-    <row r="248" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="248" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A248" s="3">
         <v>248</v>
       </c>
@@ -39747,7 +39748,7 @@
       <c r="R248" s="3"/>
       <c r="S248" s="3"/>
     </row>
-    <row r="249" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="249" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A249" s="3">
         <v>249</v>
       </c>
@@ -39790,7 +39791,7 @@
       <c r="R249" s="3"/>
       <c r="S249" s="3"/>
     </row>
-    <row r="250" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="250" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A250" s="3">
         <v>250</v>
       </c>
@@ -39833,7 +39834,7 @@
       <c r="R250" s="3"/>
       <c r="S250" s="3"/>
     </row>
-    <row r="251" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="251" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A251" s="3">
         <v>251</v>
       </c>
@@ -39876,7 +39877,7 @@
       <c r="R251" s="3"/>
       <c r="S251" s="3"/>
     </row>
-    <row r="252" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="252" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A252" s="3">
         <v>252</v>
       </c>
@@ -39919,7 +39920,7 @@
       <c r="R252" s="3"/>
       <c r="S252" s="3"/>
     </row>
-    <row r="253" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="253" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A253" s="3">
         <v>253</v>
       </c>
@@ -39964,7 +39965,7 @@
       <c r="R253" s="3"/>
       <c r="S253" s="3"/>
     </row>
-    <row r="254" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="254" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A254" s="3">
         <v>254</v>
       </c>
@@ -40007,7 +40008,7 @@
       <c r="R254" s="3"/>
       <c r="S254" s="3"/>
     </row>
-    <row r="255" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="255" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A255" s="3">
         <v>255</v>
       </c>
@@ -40052,7 +40053,7 @@
       </c>
       <c r="S255" s="3"/>
     </row>
-    <row r="256" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="256" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A256" s="3">
         <v>256</v>
       </c>
@@ -40095,7 +40096,7 @@
       <c r="R256" s="3"/>
       <c r="S256" s="3"/>
     </row>
-    <row r="257" spans="1:19" ht="15.95" customHeight="1">
+    <row r="257" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A257" s="3">
         <v>257</v>
       </c>
@@ -40144,7 +40145,7 @@
       </c>
       <c r="S257" s="3"/>
     </row>
-    <row r="258" spans="1:19" ht="15.95" customHeight="1">
+    <row r="258" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A258" s="3">
         <v>258</v>
       </c>
@@ -40187,7 +40188,7 @@
       <c r="R258" s="3"/>
       <c r="S258" s="3"/>
     </row>
-    <row r="259" spans="1:19" ht="15.95" customHeight="1">
+    <row r="259" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A259" s="3">
         <v>259</v>
       </c>
@@ -40232,7 +40233,7 @@
       <c r="R259" s="3"/>
       <c r="S259" s="3"/>
     </row>
-    <row r="260" spans="1:19" ht="15.95" customHeight="1">
+    <row r="260" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A260" s="3">
         <v>260</v>
       </c>
@@ -40277,7 +40278,7 @@
       <c r="R260" s="3"/>
       <c r="S260" s="3"/>
     </row>
-    <row r="261" spans="1:19" ht="15.95" customHeight="1">
+    <row r="261" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A261" s="3">
         <v>261</v>
       </c>
@@ -40322,7 +40323,7 @@
       <c r="R261" s="3"/>
       <c r="S261" s="3"/>
     </row>
-    <row r="262" spans="1:19" ht="15.95" customHeight="1">
+    <row r="262" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A262" s="3">
         <v>262</v>
       </c>
@@ -40369,7 +40370,7 @@
       <c r="R262" s="3"/>
       <c r="S262" s="3"/>
     </row>
-    <row r="263" spans="1:19" ht="15.95" customHeight="1">
+    <row r="263" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A263" s="3">
         <v>263</v>
       </c>
@@ -40416,7 +40417,7 @@
       </c>
       <c r="S263" s="3"/>
     </row>
-    <row r="264" spans="1:19" ht="15.95" customHeight="1">
+    <row r="264" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A264" s="3">
         <v>264</v>
       </c>
@@ -40506,7 +40507,7 @@
       <c r="R265" s="3"/>
       <c r="S265" s="3"/>
     </row>
-    <row r="266" spans="1:19" ht="15.95" customHeight="1">
+    <row r="266" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A266" s="3">
         <v>266</v>
       </c>
@@ -40553,7 +40554,7 @@
       </c>
       <c r="S266" s="3"/>
     </row>
-    <row r="267" spans="1:19" ht="15.95" customHeight="1">
+    <row r="267" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A267" s="3">
         <v>267</v>
       </c>
@@ -40596,7 +40597,7 @@
       <c r="R267" s="3"/>
       <c r="S267" s="3"/>
     </row>
-    <row r="268" spans="1:19" ht="15.95" customHeight="1">
+    <row r="268" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A268" s="3">
         <v>268</v>
       </c>
@@ -40639,7 +40640,7 @@
       <c r="R268" s="3"/>
       <c r="S268" s="3"/>
     </row>
-    <row r="269" spans="1:19" ht="15.95" customHeight="1">
+    <row r="269" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A269" s="3">
         <v>269</v>
       </c>
@@ -40684,7 +40685,7 @@
       <c r="R269" s="3"/>
       <c r="S269" s="3"/>
     </row>
-    <row r="270" spans="1:19" ht="15.95" customHeight="1">
+    <row r="270" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A270" s="3">
         <v>270</v>
       </c>
@@ -40729,7 +40730,7 @@
       <c r="R270" s="3"/>
       <c r="S270" s="3"/>
     </row>
-    <row r="271" spans="1:19" ht="15.95" customHeight="1">
+    <row r="271" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A271" s="3">
         <v>271</v>
       </c>
@@ -40774,7 +40775,7 @@
       <c r="R271" s="3"/>
       <c r="S271" s="3"/>
     </row>
-    <row r="272" spans="1:19" ht="15.95" customHeight="1">
+    <row r="272" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A272" s="3">
         <v>272</v>
       </c>
@@ -40817,7 +40818,7 @@
       <c r="R272" s="3"/>
       <c r="S272" s="3"/>
     </row>
-    <row r="273" spans="1:19" ht="15.95" customHeight="1">
+    <row r="273" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A273" s="3">
         <v>273</v>
       </c>
@@ -40862,7 +40863,7 @@
       <c r="R273" s="3"/>
       <c r="S273" s="3"/>
     </row>
-    <row r="274" spans="1:19" ht="15.95" customHeight="1">
+    <row r="274" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A274" s="3">
         <v>274</v>
       </c>
@@ -40905,7 +40906,7 @@
       <c r="R274" s="3"/>
       <c r="S274" s="3"/>
     </row>
-    <row r="275" spans="1:19" ht="15.95" customHeight="1">
+    <row r="275" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A275" s="3">
         <v>275</v>
       </c>
@@ -40950,7 +40951,7 @@
       <c r="R275" s="3"/>
       <c r="S275" s="3"/>
     </row>
-    <row r="276" spans="1:19" ht="15.95" customHeight="1">
+    <row r="276" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A276" s="3">
         <v>277</v>
       </c>
@@ -40993,7 +40994,7 @@
       <c r="R276" s="3"/>
       <c r="S276" s="3"/>
     </row>
-    <row r="277" spans="1:19" ht="15.95" customHeight="1">
+    <row r="277" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A277" s="3">
         <v>278</v>
       </c>
@@ -41036,7 +41037,7 @@
       <c r="R277" s="3"/>
       <c r="S277" s="3"/>
     </row>
-    <row r="278" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="278" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A278" s="3">
         <v>279</v>
       </c>
@@ -41079,7 +41080,7 @@
       <c r="R278" s="3"/>
       <c r="S278" s="3"/>
     </row>
-    <row r="279" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="279" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A279" s="3">
         <v>280</v>
       </c>
@@ -41122,7 +41123,7 @@
       <c r="R279" s="3"/>
       <c r="S279" s="3"/>
     </row>
-    <row r="280" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="280" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A280" s="3">
         <v>281</v>
       </c>
@@ -41165,7 +41166,7 @@
       <c r="R280" s="3"/>
       <c r="S280" s="3"/>
     </row>
-    <row r="281" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="281" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A281" s="3">
         <v>282</v>
       </c>
@@ -41208,7 +41209,7 @@
       <c r="R281" s="3"/>
       <c r="S281" s="3"/>
     </row>
-    <row r="282" spans="1:19" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="282" spans="1:19" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A282" s="3">
         <v>283</v>
       </c>
@@ -41251,7 +41252,7 @@
       <c r="R282" s="3"/>
       <c r="S282" s="3"/>
     </row>
-    <row r="283" spans="1:19" ht="15.95" customHeight="1">
+    <row r="283" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A283" s="3">
         <v>284</v>
       </c>
@@ -41294,7 +41295,7 @@
       <c r="R283" s="3"/>
       <c r="S283" s="3"/>
     </row>
-    <row r="284" spans="1:19" ht="15.95" customHeight="1">
+    <row r="284" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A284" s="3">
         <v>285</v>
       </c>
@@ -41337,7 +41338,7 @@
       <c r="R284" s="3"/>
       <c r="S284" s="3"/>
     </row>
-    <row r="285" spans="1:19" ht="15.95" customHeight="1">
+    <row r="285" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A285" s="3">
         <v>286</v>
       </c>
@@ -41380,7 +41381,7 @@
       <c r="R285" s="3"/>
       <c r="S285" s="3"/>
     </row>
-    <row r="286" spans="1:19" ht="15.95" customHeight="1">
+    <row r="286" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A286" s="3">
         <v>287</v>
       </c>
@@ -41423,7 +41424,7 @@
       <c r="R286" s="3"/>
       <c r="S286" s="3"/>
     </row>
-    <row r="287" spans="1:19" ht="15.95" customHeight="1">
+    <row r="287" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A287" s="3">
         <v>288</v>
       </c>
@@ -41466,7 +41467,7 @@
       <c r="R287" s="3"/>
       <c r="S287" s="3"/>
     </row>
-    <row r="288" spans="1:19" ht="15.95" customHeight="1">
+    <row r="288" spans="1:19" ht="15.95" hidden="1" customHeight="1">
       <c r="A288" s="3">
         <v>289</v>
       </c>
@@ -41509,7 +41510,7 @@
       <c r="R288" s="3"/>
       <c r="S288" s="3"/>
     </row>
-    <row r="289" spans="1:20" ht="15.95" customHeight="1">
+    <row r="289" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A289" s="3">
         <v>140</v>
       </c>
@@ -41554,7 +41555,7 @@
       </c>
       <c r="S289" s="3"/>
     </row>
-    <row r="290" spans="1:20" ht="15.95" customHeight="1">
+    <row r="290" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A290" s="3">
         <v>291</v>
       </c>
@@ -41597,7 +41598,7 @@
       <c r="R290" s="3"/>
       <c r="S290" s="3"/>
     </row>
-    <row r="291" spans="1:20" ht="15.95" customHeight="1">
+    <row r="291" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A291" s="3">
         <v>293</v>
       </c>
@@ -41640,7 +41641,7 @@
       <c r="R291" s="3"/>
       <c r="S291" s="3"/>
     </row>
-    <row r="292" spans="1:20" ht="15.95" customHeight="1">
+    <row r="292" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A292" s="3">
         <v>294</v>
       </c>
@@ -41685,7 +41686,7 @@
       <c r="R292" s="3"/>
       <c r="S292" s="3"/>
     </row>
-    <row r="293" spans="1:20" ht="15.95" customHeight="1">
+    <row r="293" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A293" s="3">
         <v>295</v>
       </c>
@@ -41730,7 +41731,7 @@
       <c r="R293" s="3"/>
       <c r="S293" s="3"/>
     </row>
-    <row r="294" spans="1:20" ht="15.95" customHeight="1">
+    <row r="294" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A294" s="3">
         <v>296</v>
       </c>
@@ -41773,7 +41774,7 @@
       <c r="R294" s="3"/>
       <c r="S294" s="3"/>
     </row>
-    <row r="295" spans="1:20" ht="15.95" customHeight="1">
+    <row r="295" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A295" s="3">
         <v>297</v>
       </c>
@@ -41818,7 +41819,7 @@
       <c r="R295" s="3"/>
       <c r="S295" s="3"/>
     </row>
-    <row r="296" spans="1:20" ht="15.95" customHeight="1">
+    <row r="296" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A296" s="3">
         <v>299</v>
       </c>
@@ -41861,7 +41862,7 @@
       <c r="R296" s="3"/>
       <c r="S296" s="3"/>
     </row>
-    <row r="297" spans="1:20" ht="15.95" customHeight="1">
+    <row r="297" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A297" s="3">
         <v>300</v>
       </c>
@@ -41902,7 +41903,7 @@
       <c r="R297" s="3"/>
       <c r="S297" s="3"/>
     </row>
-    <row r="298" spans="1:20" ht="15.95" customHeight="1">
+    <row r="298" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A298" s="3">
         <v>301</v>
       </c>
@@ -41949,7 +41950,7 @@
       <c r="R298" s="3"/>
       <c r="S298" s="3"/>
     </row>
-    <row r="299" spans="1:20" ht="15.95" customHeight="1">
+    <row r="299" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A299" s="3">
         <v>302</v>
       </c>
@@ -41994,7 +41995,7 @@
       <c r="R299" s="3"/>
       <c r="S299" s="3"/>
     </row>
-    <row r="300" spans="1:20" ht="15.95" customHeight="1">
+    <row r="300" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A300" s="3">
         <v>303</v>
       </c>
@@ -42037,7 +42038,7 @@
       <c r="R300" s="3"/>
       <c r="S300" s="3"/>
     </row>
-    <row r="301" spans="1:20" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="301" spans="1:20" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A301" s="3">
         <v>304</v>
       </c>
@@ -42082,7 +42083,7 @@
       <c r="R301" s="3"/>
       <c r="S301" s="3"/>
     </row>
-    <row r="302" spans="1:20" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="302" spans="1:20" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A302" s="3">
         <v>305</v>
       </c>
@@ -42129,7 +42130,7 @@
       </c>
       <c r="S302" s="3"/>
     </row>
-    <row r="303" spans="1:20" s="7" customFormat="1" ht="15.95" customHeight="1">
+    <row r="303" spans="1:20" s="7" customFormat="1" ht="15.95" hidden="1" customHeight="1">
       <c r="A303" s="3">
         <v>306</v>
       </c>
@@ -42174,7 +42175,7 @@
       <c r="R303" s="18"/>
       <c r="S303" s="18"/>
     </row>
-    <row r="304" spans="1:20" ht="15.95" customHeight="1">
+    <row r="304" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A304" s="3">
         <v>307</v>
       </c>
@@ -42218,7 +42219,7 @@
       <c r="S304" s="16"/>
       <c r="T304" s="17"/>
     </row>
-    <row r="305" spans="1:20" ht="15.95" customHeight="1">
+    <row r="305" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A305" s="18">
         <v>308</v>
       </c>
@@ -42266,7 +42267,7 @@
       <c r="S305" s="23"/>
       <c r="T305" s="17"/>
     </row>
-    <row r="306" spans="1:20" ht="15.95" customHeight="1">
+    <row r="306" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A306" s="3">
         <v>309</v>
       </c>
@@ -42310,7 +42311,7 @@
       <c r="S306" s="16"/>
       <c r="T306" s="17"/>
     </row>
-    <row r="307" spans="1:20" ht="15.95" customHeight="1">
+    <row r="307" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A307" s="3">
         <v>310</v>
       </c>
@@ -42353,7 +42354,7 @@
       <c r="R307" s="16"/>
       <c r="S307" s="16"/>
     </row>
-    <row r="308" spans="1:20" ht="15.95" customHeight="1">
+    <row r="308" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A308" s="18">
         <v>311</v>
       </c>
@@ -42396,7 +42397,7 @@
       <c r="R308" s="3"/>
       <c r="S308" s="3"/>
     </row>
-    <row r="309" spans="1:20" ht="15.95" customHeight="1">
+    <row r="309" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A309" s="3">
         <v>312</v>
       </c>
@@ -42476,7 +42477,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="311" spans="1:20" ht="15.95" customHeight="1">
+    <row r="311" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A311" s="18">
         <v>314</v>
       </c>
@@ -42516,7 +42517,7 @@
       <c r="Q311" s="3"/>
       <c r="R311" s="3"/>
     </row>
-    <row r="312" spans="1:20" ht="15.95" customHeight="1">
+    <row r="312" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A312" s="3">
         <v>315</v>
       </c>
@@ -42558,7 +42559,7 @@
       <c r="Q312" s="18"/>
       <c r="R312" s="18"/>
     </row>
-    <row r="313" spans="1:20" ht="15.95" customHeight="1">
+    <row r="313" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A313" s="3">
         <v>316</v>
       </c>
@@ -42600,7 +42601,7 @@
       <c r="Q313" s="18"/>
       <c r="R313" s="18"/>
     </row>
-    <row r="314" spans="1:20" ht="15.95" customHeight="1">
+    <row r="314" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A314" s="18">
         <v>317</v>
       </c>
@@ -42642,7 +42643,7 @@
       <c r="Q314" s="18"/>
       <c r="R314" s="18"/>
     </row>
-    <row r="315" spans="1:20" ht="15.95" customHeight="1">
+    <row r="315" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A315" s="27">
         <v>318</v>
       </c>
@@ -42685,7 +42686,7 @@
       <c r="R315" s="14"/>
       <c r="S315" s="17"/>
     </row>
-    <row r="316" spans="1:20" ht="15.95" customHeight="1">
+    <row r="316" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A316" s="3">
         <v>319</v>
       </c>
@@ -42727,7 +42728,7 @@
       <c r="Q316" s="14"/>
       <c r="R316" s="14"/>
     </row>
-    <row r="317" spans="1:20" ht="15.95" customHeight="1">
+    <row r="317" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A317" s="18">
         <v>320</v>
       </c>
@@ -42769,7 +42770,7 @@
       <c r="Q317" s="14"/>
       <c r="R317" s="14"/>
     </row>
-    <row r="318" spans="1:20" ht="15.95" customHeight="1">
+    <row r="318" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A318" s="27">
         <v>321</v>
       </c>
@@ -42811,7 +42812,7 @@
       <c r="Q318" s="14"/>
       <c r="R318" s="14"/>
     </row>
-    <row r="319" spans="1:20" ht="15.95" customHeight="1">
+    <row r="319" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A319" s="3">
         <v>322</v>
       </c>
@@ -42853,7 +42854,7 @@
       <c r="Q319" s="14"/>
       <c r="R319" s="14"/>
     </row>
-    <row r="320" spans="1:20" ht="15.95" customHeight="1">
+    <row r="320" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A320" s="18">
         <v>323</v>
       </c>
@@ -42895,7 +42896,7 @@
       <c r="Q320" s="14"/>
       <c r="R320" s="14"/>
     </row>
-    <row r="321" spans="1:20" ht="15.95" customHeight="1">
+    <row r="321" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A321" s="27">
         <v>324</v>
       </c>
@@ -42937,7 +42938,7 @@
       <c r="Q321" s="14"/>
       <c r="R321" s="14"/>
     </row>
-    <row r="322" spans="1:20" ht="15.95" customHeight="1">
+    <row r="322" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A322" s="3">
         <v>325</v>
       </c>
@@ -42979,7 +42980,7 @@
       <c r="Q322" s="14"/>
       <c r="R322" s="14"/>
     </row>
-    <row r="323" spans="1:20" ht="15.95" customHeight="1">
+    <row r="323" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A323" s="18">
         <v>326</v>
       </c>
@@ -43021,7 +43022,7 @@
       <c r="Q323" s="3"/>
       <c r="R323" s="3"/>
     </row>
-    <row r="324" spans="1:20" ht="15.95" customHeight="1">
+    <row r="324" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A324" s="27">
         <v>327</v>
       </c>
@@ -43063,7 +43064,7 @@
       <c r="Q324" s="30"/>
       <c r="R324" s="30"/>
     </row>
-    <row r="325" spans="1:20" ht="15.95" customHeight="1">
+    <row r="325" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A325" s="18">
         <v>328</v>
       </c>
@@ -43103,7 +43104,7 @@
       <c r="Q325" s="3"/>
       <c r="R325" s="3"/>
     </row>
-    <row r="326" spans="1:20" ht="15.95" customHeight="1">
+    <row r="326" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A326" s="18">
         <v>329</v>
       </c>
@@ -43143,7 +43144,7 @@
       <c r="Q326" s="3"/>
       <c r="R326" s="3"/>
     </row>
-    <row r="327" spans="1:20" ht="15.95" customHeight="1">
+    <row r="327" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A327" s="18">
         <v>330</v>
       </c>
@@ -43185,7 +43186,7 @@
       <c r="Q327" s="3"/>
       <c r="R327" s="3"/>
     </row>
-    <row r="328" spans="1:20" ht="15.95" customHeight="1">
+    <row r="328" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A328" s="18">
         <v>331</v>
       </c>
@@ -43312,7 +43313,7 @@
       <c r="Q330" s="16"/>
       <c r="R330" s="16"/>
     </row>
-    <row r="331" spans="1:20" ht="15.95" customHeight="1">
+    <row r="331" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A331" s="3">
         <v>334</v>
       </c>
@@ -43354,7 +43355,7 @@
       <c r="Q331" s="16"/>
       <c r="R331" s="16"/>
     </row>
-    <row r="332" spans="1:20" ht="15.95" customHeight="1">
+    <row r="332" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A332" s="18">
         <v>335</v>
       </c>
@@ -43397,7 +43398,7 @@
       <c r="R332" s="23"/>
       <c r="S332" s="16"/>
     </row>
-    <row r="333" spans="1:20" ht="15.95" customHeight="1">
+    <row r="333" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A333" s="18">
         <v>336</v>
       </c>
@@ -43484,7 +43485,7 @@
       <c r="S334" s="23"/>
       <c r="T334" s="17"/>
     </row>
-    <row r="335" spans="1:20" ht="15.95" customHeight="1">
+    <row r="335" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A335" s="14">
         <v>338</v>
       </c>
@@ -43528,7 +43529,7 @@
       <c r="S335" s="16"/>
       <c r="T335" s="17"/>
     </row>
-    <row r="336" spans="1:20" ht="15.95" customHeight="1">
+    <row r="336" spans="1:20" ht="15.95" hidden="1" customHeight="1">
       <c r="A336" s="14">
         <v>339</v>
       </c>
@@ -43572,7 +43573,7 @@
       <c r="S336" s="16"/>
       <c r="T336" s="17"/>
     </row>
-    <row r="337" spans="1:21" ht="15.95" customHeight="1">
+    <row r="337" spans="1:21" ht="15.95" hidden="1" customHeight="1">
       <c r="A337" s="14">
         <v>340</v>
       </c>
@@ -43618,7 +43619,7 @@
       <c r="S337" s="23"/>
       <c r="T337" s="17"/>
     </row>
-    <row r="338" spans="1:21" ht="15.95" customHeight="1">
+    <row r="338" spans="1:21" ht="15.95" hidden="1" customHeight="1">
       <c r="A338" s="14">
         <v>341</v>
       </c>
@@ -43662,7 +43663,7 @@
       <c r="S338" s="23"/>
       <c r="T338" s="17"/>
     </row>
-    <row r="339" spans="1:21" ht="15.95" customHeight="1">
+    <row r="339" spans="1:21" ht="15.95" hidden="1" customHeight="1">
       <c r="A339" s="14">
         <v>342</v>
       </c>
@@ -43706,7 +43707,7 @@
       <c r="S339" s="23"/>
       <c r="T339" s="17"/>
     </row>
-    <row r="340" spans="1:21" ht="15.95" customHeight="1">
+    <row r="340" spans="1:21" ht="15.95" hidden="1" customHeight="1">
       <c r="A340" s="14">
         <v>343</v>
       </c>
@@ -43749,7 +43750,7 @@
       <c r="S340" s="23"/>
       <c r="T340" s="17"/>
     </row>
-    <row r="341" spans="1:21" ht="15.95" customHeight="1">
+    <row r="341" spans="1:21" ht="15.95" hidden="1" customHeight="1">
       <c r="A341" s="14">
         <v>344</v>
       </c>
@@ -43793,7 +43794,7 @@
       <c r="S341" s="16"/>
       <c r="T341" s="17"/>
     </row>
-    <row r="342" spans="1:21" ht="15.95" customHeight="1">
+    <row r="342" spans="1:21" ht="15.95" hidden="1" customHeight="1">
       <c r="A342" s="14">
         <v>345</v>
       </c>
@@ -43837,7 +43838,7 @@
       <c r="S342" s="16"/>
       <c r="T342" s="17"/>
     </row>
-    <row r="343" spans="1:21" ht="15.95" customHeight="1">
+    <row r="343" spans="1:21" ht="15.95" hidden="1" customHeight="1">
       <c r="A343" s="14">
         <v>346</v>
       </c>
@@ -43879,7 +43880,7 @@
       <c r="Q343" s="23"/>
       <c r="R343" s="17"/>
     </row>
-    <row r="344" spans="1:21" ht="15.95" customHeight="1">
+    <row r="344" spans="1:21" ht="15.95" hidden="1" customHeight="1">
       <c r="A344" s="21">
         <v>347</v>
       </c>
@@ -43922,7 +43923,7 @@
       <c r="R344" s="23"/>
       <c r="S344" s="17"/>
     </row>
-    <row r="345" spans="1:21" ht="15.95" customHeight="1">
+    <row r="345" spans="1:21" ht="15.95" hidden="1" customHeight="1">
       <c r="A345" s="34">
         <v>348</v>
       </c>
@@ -43966,7 +43967,7 @@
       <c r="S345" s="23"/>
       <c r="T345" s="17"/>
     </row>
-    <row r="346" spans="1:21" ht="15.95" customHeight="1">
+    <row r="346" spans="1:21" ht="15.95" hidden="1" customHeight="1">
       <c r="A346" s="37">
         <v>349</v>
       </c>
@@ -44010,7 +44011,7 @@
       <c r="S346" s="23"/>
       <c r="T346" s="17"/>
     </row>
-    <row r="347" spans="1:21" ht="15.95" customHeight="1">
+    <row r="347" spans="1:21" ht="15.95" hidden="1" customHeight="1">
       <c r="A347" s="21">
         <v>350</v>
       </c>
@@ -44055,7 +44056,7 @@
       <c r="T347" s="16"/>
       <c r="U347" s="17"/>
     </row>
-    <row r="348" spans="1:21" ht="15.95" customHeight="1">
+    <row r="348" spans="1:21" ht="15.95" hidden="1" customHeight="1">
       <c r="A348" s="34">
         <v>351</v>
       </c>
@@ -44100,7 +44101,7 @@
       <c r="T348" s="16"/>
       <c r="U348" s="17"/>
     </row>
-    <row r="349" spans="1:21" ht="15.95" customHeight="1">
+    <row r="349" spans="1:21" ht="15.95" hidden="1" customHeight="1">
       <c r="A349" s="37">
         <v>352</v>
       </c>
@@ -44145,7 +44146,7 @@
       <c r="T349" s="16"/>
       <c r="U349" s="17"/>
     </row>
-    <row r="350" spans="1:21" ht="15.95" customHeight="1">
+    <row r="350" spans="1:21" ht="15.95" hidden="1" customHeight="1">
       <c r="A350" s="21">
         <v>353</v>
       </c>
@@ -44190,7 +44191,7 @@
       <c r="T350" s="16"/>
       <c r="U350" s="17"/>
     </row>
-    <row r="351" spans="1:21" ht="15.95" customHeight="1">
+    <row r="351" spans="1:21" ht="15.95" hidden="1" customHeight="1">
       <c r="A351" s="34">
         <v>354</v>
       </c>
@@ -44235,7 +44236,7 @@
       <c r="T351" s="16"/>
       <c r="U351" s="17"/>
     </row>
-    <row r="352" spans="1:21" ht="15.95" customHeight="1">
+    <row r="352" spans="1:21" ht="15.95" hidden="1" customHeight="1">
       <c r="A352" s="37">
         <v>355</v>
       </c>
@@ -44280,7 +44281,7 @@
       <c r="T352" s="16"/>
       <c r="U352" s="17"/>
     </row>
-    <row r="353" spans="1:21" ht="15.95" customHeight="1">
+    <row r="353" spans="1:21" ht="15.95" hidden="1" customHeight="1">
       <c r="A353" s="37">
         <v>356</v>
       </c>
@@ -44325,7 +44326,7 @@
       <c r="T353" s="16"/>
       <c r="U353" s="17"/>
     </row>
-    <row r="354" spans="1:21" ht="15.95" customHeight="1">
+    <row r="354" spans="1:21" ht="15.95" hidden="1" customHeight="1">
       <c r="A354" s="34">
         <v>357</v>
       </c>
@@ -44369,7 +44370,7 @@
       <c r="S354" s="16"/>
       <c r="T354" s="17"/>
     </row>
-    <row r="355" spans="1:21" ht="15.95" customHeight="1">
+    <row r="355" spans="1:21" ht="15.95" hidden="1" customHeight="1">
       <c r="A355" s="37">
         <v>358</v>
       </c>
@@ -44414,7 +44415,7 @@
       <c r="R355" s="23"/>
       <c r="S355" s="17"/>
     </row>
-    <row r="356" spans="1:21" ht="15.95" customHeight="1">
+    <row r="356" spans="1:21" ht="15.95" hidden="1" customHeight="1">
       <c r="A356" s="21">
         <v>359</v>
       </c>
@@ -44457,7 +44458,7 @@
       <c r="R356" s="23"/>
       <c r="S356" s="17"/>
     </row>
-    <row r="357" spans="1:21" ht="15.95" customHeight="1">
+    <row r="357" spans="1:21" ht="15.95" hidden="1" customHeight="1">
       <c r="A357" s="34">
         <v>360</v>
       </c>
@@ -44500,7 +44501,7 @@
       <c r="R357" s="23"/>
       <c r="S357" s="17"/>
     </row>
-    <row r="358" spans="1:21" ht="15.95" customHeight="1">
+    <row r="358" spans="1:21" ht="15.95" hidden="1" customHeight="1">
       <c r="A358" s="37">
         <v>361</v>
       </c>
@@ -44543,7 +44544,7 @@
       <c r="R358" s="23"/>
       <c r="S358" s="17"/>
     </row>
-    <row r="359" spans="1:21" ht="15.95" customHeight="1">
+    <row r="359" spans="1:21" ht="15.95" hidden="1" customHeight="1">
       <c r="A359" s="34">
         <v>362</v>
       </c>
@@ -44586,7 +44587,7 @@
       <c r="R359" s="16"/>
       <c r="S359" s="17"/>
     </row>
-    <row r="360" spans="1:21" ht="15.95" customHeight="1">
+    <row r="360" spans="1:21" ht="15.95" hidden="1" customHeight="1">
       <c r="A360" s="37">
         <v>363</v>
       </c>
@@ -44629,7 +44630,7 @@
       <c r="R360" s="23"/>
       <c r="S360" s="17"/>
     </row>
-    <row r="361" spans="1:21" ht="15.95" customHeight="1">
+    <row r="361" spans="1:21" ht="15.95" hidden="1" customHeight="1">
       <c r="A361" s="14">
         <v>364</v>
       </c>
@@ -44672,7 +44673,7 @@
       <c r="R361" s="16"/>
       <c r="S361" s="17"/>
     </row>
-    <row r="362" spans="1:21" ht="15.95" customHeight="1">
+    <row r="362" spans="1:21" ht="15.95" hidden="1" customHeight="1">
       <c r="A362" s="21">
         <v>365</v>
       </c>
@@ -44715,7 +44716,7 @@
       <c r="R362" s="23"/>
       <c r="S362" s="17"/>
     </row>
-    <row r="363" spans="1:21" ht="15.95" customHeight="1">
+    <row r="363" spans="1:21" ht="15.95" hidden="1" customHeight="1">
       <c r="A363" s="37">
         <v>366</v>
       </c>
@@ -44758,7 +44759,7 @@
       <c r="R363" s="23"/>
       <c r="S363" s="17"/>
     </row>
-    <row r="364" spans="1:21" ht="15.95" customHeight="1">
+    <row r="364" spans="1:21" ht="15.95" hidden="1" customHeight="1">
       <c r="A364" s="21">
         <v>367</v>
       </c>
@@ -44801,7 +44802,7 @@
       <c r="R364" s="23"/>
       <c r="S364" s="17"/>
     </row>
-    <row r="365" spans="1:21" ht="15.95" customHeight="1">
+    <row r="365" spans="1:21" ht="15.95" hidden="1" customHeight="1">
       <c r="A365" s="21">
         <v>368</v>
       </c>
@@ -44844,7 +44845,7 @@
       <c r="R365" s="23"/>
       <c r="S365" s="17"/>
     </row>
-    <row r="366" spans="1:21" ht="15.95" customHeight="1">
+    <row r="366" spans="1:21" ht="15.95" hidden="1" customHeight="1">
       <c r="A366" s="37">
         <v>369</v>
       </c>
@@ -44887,7 +44888,7 @@
       <c r="R366" s="23"/>
       <c r="S366" s="17"/>
     </row>
-    <row r="367" spans="1:21" ht="15.95" customHeight="1">
+    <row r="367" spans="1:21" ht="15.95" hidden="1" customHeight="1">
       <c r="A367" s="21">
         <v>370</v>
       </c>
@@ -44931,7 +44932,118 @@
       <c r="S367" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T366" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" ref="A1:T367" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Alice Muhayimana"/>
+        <filter val="Christine Minoo Mbindyo"/>
+        <filter val="Henry Zakumumpa"/>
+        <filter val="James Mburu Kangethe"/>
+        <filter val="Jean de la Croix Allen Ingabire"/>
+        <filter val="Priscille Musabirema"/>
+        <filter val="Samuel Waweru Mwaniki"/>
+        <filter val="Temitope Olumuyiwa Ojo"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="14">
+      <filters>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <x14:filter val=" Award of Excellent Performance in Research awarded by the Intellectual Property and Technology Transfer Office (IPTTO), Obafemi Awolowo University, Ile – Ife, Osun State, Nigeria for outstanding achievements in research and exceptional contributions to promoting intellectual property assets in Obafemi Awolowo University."/>
+            <x14:filter val="Academic Citizenship Award"/>
+            <x14:filter val="Affiliate AAS"/>
+            <x14:filter val="Apointed  Research Lead at the Center for the Study of the Economies of Africa (CSEA)"/>
+            <x14:filter val="Appointed Guest Editor of the BMC Health Services Research special collection on HIV-related stigma as a barrier to accessing health care on August 8, 2025."/>
+            <x14:filter val="Appointed Joint Staff (Researcher) at the University of the Witwatersrand Reproductive Health and HIV Institute (Wits RHI), Faculty of Health Sciences, effective August 1, 2025."/>
+            <x14:filter val="Appointment as Hall Fellow_ Clinical Hostel"/>
+            <x14:filter val="Awarded ‘Outstanding German Academic Exchange Service (DAAD) alumnus"/>
+            <x14:filter val="Awarded by the Southwest Nigeria Education Awards as Southwest Nigeria outstanding lecturer of the year 2020"/>
+            <x14:filter val="Awarded the Atlantic Fellowship for Equity in Brain Health at the Global Brain Health Institute (GBHI)"/>
+            <x14:filter val="Awarded the Royal Society of Tropical Medicine anf Hygiene fund. He was also granted a complimentary RSTMH membership for the duration of the three years of the fund which aims to support potential RSTMH members from low- and low-middle income countries by paying awardees’ annual membership subscription for three years."/>
+            <x14:filter val="Awarded the Vice Chancellor’s Research Excellence Award in the category of Best Mid-Career Researcher in the College of Natural Sciences on February 25, 2026, during Makerere University’s 76th graduation ceremony."/>
+            <x14:filter val="Awarded the Vice Chancellor’s Research Excellence Award in the category of Mid-Career Researcher on February 24, 2026, during Makerere University’s 76th graduation ceremony."/>
+            <x14:filter val="Best Abstract Award"/>
+            <x14:filter val="Best Poster presentation at the Joint Annual Scientific Health Conference held in Kampala Uganda from September 23 - 25, 2022."/>
+            <x14:filter val="Claude- leone- Distinguished Scholars Award"/>
+            <x14:filter val="Distinguished Science and Technology Award worth 10.000 USD"/>
+            <x14:filter val="Elected Co-Chair of the African Diplomacy Group of the Global Young Academy  Elected to the Editorial Board of BMC Complementary &amp; Alternative Medicine"/>
+            <x14:filter val="Fellowship - FCS - Training Programme in Orthopaedic surgery (Orthopaedic Surgeon and Fellow of COSECSA)"/>
+            <x14:filter val="He was ranked among the top eight applicants of the Jennifer Ward Oppenheimer (JWO) Research Grant aimed at supporting early career African Scientists"/>
+            <x14:filter val="He was recognized as one of the best PhD student in the faculty of  Health Sciences for the 2023/2024 academic year."/>
+            <x14:filter val="He was selected to join the Emerging Leaders Programme by the World Heart Federation"/>
+            <x14:filter val="I have been awarded a recognition certificate as someone who promoted the CPD program among in-service professionals. The CPD program was about multi-discipline collaboration to manage infectious diseases."/>
+            <x14:filter val="I have received a two-year scholarship to attend a fellowship in epidemiology focused on TB and HIV. I also received a scholarship t attend short online research trainings with the University of Washington"/>
+            <x14:filter val="IADS-Rahamon Bello Award for Best Ph.D Thesis in African and Diaspora Studies-2020"/>
+            <x14:filter val="Iconic Award awarded by The Teen Awareness Movement in recognition of outstanding support for educational development for the less privileged young secondary students. 31st October 2020."/>
+            <x14:filter val="International Association for Dental Research-  South Africa (IADR-SA) Postgraduate divisional award."/>
+            <x14:filter val="ISN Travel Awards to attend the ISN-APSN 2022 meeting in Honolulu, USA from August 28 to September 1, 2022."/>
+            <x14:filter val="MG200Young"/>
+            <x14:filter val="nominated for the prestigious Vice Chancellor's Research Excellence Award 2025. This nomination recognizes his outstanding contributions to research excellence."/>
+            <x14:filter val="Prestigious Postgraduate Degree Award"/>
+            <x14:filter val="Research award. This was a seed grant for family planning and comprehensive abortion care. Offered by the University of Michigan."/>
+            <x14:filter val="she received a commendation award for diligent service from the management board of the hospital"/>
+            <x14:filter val="She was awarded a Postgraduate Certificate in Learning and Teaching in Higher Education (PGCLTHE) during a congregation ceremony held at the University of Rwanda on October 17, 2025. The certification recognizes her  commitment to enhancing teaching excellence and promoting innovative learning approaches in higher education."/>
+            <x14:filter val="she was inducted as a fellow of the International College of Dentists (FICD), an international recognition of her professional excellence, ethical standards, and commitment to improving oral health globally."/>
+            <x14:filter val="she was inducted as a fellow of the Nigerian Academy of Medicine (FNAMed), joining a distinguished body of experts dedicated to advancing medical research, shaping health policy, and mentoring the next generation of leaders in medicine and health."/>
+            <x14:filter val="Special recognition award of the World Glaucoma Association"/>
+            <x14:filter val="Top 25 World Heart Federation (WHF) Salim Yusuf Emerging Leaders."/>
+            <x14:filter val="Transition Award Professional Development [TAPROD] Program"/>
+            <x14:filter val="was appointed an Associate Fellow of interRAI, a collaborative network of researchers in over 35 countries committed to improving health care for vulnerable populations with complex needs on June 6, 2024. InterRAI aims to promote evidence-informed clinical practice and policy decisions by collecting and interpreting high-quality data about the characteristics and outcomes of persons served across various health and social services setting"/>
+            <x14:filter val="Was awarded a Senior Fellowship in Global Health Communications Leadership for 2025 - 2026 on July 14, 2025, by the Center for Communications Leadership and Policy (CCLP)"/>
+            <x14:filter val="Was selected as one of four recipients of this year’s Uganda Textbook Academic and Non-Fiction Authors’ Association (UTANA) Grant Scheme Award to complete and publish his book titled ‘A handbook on medicinal plants and HIV/AIDS’"/>
+            <x14:filter val="Winner of Vice Chancellor's Transformation Award (in the team category) at the University of the Witwatersrand"/>
+            <x14:filter val="Winning Poster"/>
+            <x14:filter val="Won the most supportive lecturer award for the 2019-2021 academic session, from the Library, Archival and Information Studies Students Association at the University of Ibadan."/>
+            <x14:filter val="Young Investigator Fellowship for the 19th International Congress of the International Society of Ethnopharmacology"/>
+          </mc:Choice>
+          <mc:Fallback>
+            <filter val="Academic Citizenship Award"/>
+            <filter val="Affiliate AAS"/>
+            <filter val="Apointed  Research Lead at the Center for the Study of the Economies of Africa (CSEA)"/>
+            <filter val="Appointed Guest Editor of the BMC Health Services Research special collection on HIV-related stigma as a barrier to accessing health care on August 8, 2025."/>
+            <filter val="Appointed Joint Staff (Researcher) at the University of the Witwatersrand Reproductive Health and HIV Institute (Wits RHI), Faculty of Health Sciences, effective August 1, 2025."/>
+            <filter val="Appointment as Hall Fellow_ Clinical Hostel"/>
+            <filter val="Awarded ‘Outstanding German Academic Exchange Service (DAAD) alumnus"/>
+            <filter val="Awarded by the Southwest Nigeria Education Awards as Southwest Nigeria outstanding lecturer of the year 2020"/>
+            <filter val="Awarded the Atlantic Fellowship for Equity in Brain Health at the Global Brain Health Institute (GBHI)"/>
+            <filter val="Awarded the Vice Chancellor’s Research Excellence Award in the category of Best Mid-Career Researcher in the College of Natural Sciences on February 25, 2026, during Makerere University’s 76th graduation ceremony."/>
+            <filter val="Awarded the Vice Chancellor’s Research Excellence Award in the category of Mid-Career Researcher on February 24, 2026, during Makerere University’s 76th graduation ceremony."/>
+            <filter val="Best Abstract Award"/>
+            <filter val="Best Poster presentation at the Joint Annual Scientific Health Conference held in Kampala Uganda from September 23 - 25, 2022."/>
+            <filter val="Claude- leone- Distinguished Scholars Award"/>
+            <filter val="Distinguished Science and Technology Award worth 10.000 USD"/>
+            <filter val="Elected Co-Chair of the African Diplomacy Group of the Global Young Academy  Elected to the Editorial Board of BMC Complementary &amp; Alternative Medicine"/>
+            <filter val="Fellowship - FCS - Training Programme in Orthopaedic surgery (Orthopaedic Surgeon and Fellow of COSECSA)"/>
+            <filter val="He was ranked among the top eight applicants of the Jennifer Ward Oppenheimer (JWO) Research Grant aimed at supporting early career African Scientists"/>
+            <filter val="He was recognized as one of the best PhD student in the faculty of  Health Sciences for the 2023/2024 academic year."/>
+            <filter val="He was selected to join the Emerging Leaders Programme by the World Heart Federation"/>
+            <filter val="I have been awarded a recognition certificate as someone who promoted the CPD program among in-service professionals. The CPD program was about multi-discipline collaboration to manage infectious diseases."/>
+            <filter val="I have received a two-year scholarship to attend a fellowship in epidemiology focused on TB and HIV. I also received a scholarship t attend short online research trainings with the University of Washington"/>
+            <filter val="IADS-Rahamon Bello Award for Best Ph.D Thesis in African and Diaspora Studies-2020"/>
+            <filter val="Iconic Award awarded by The Teen Awareness Movement in recognition of outstanding support for educational development for the less privileged young secondary students. 31st October 2020."/>
+            <filter val="International Association for Dental Research-  South Africa (IADR-SA) Postgraduate divisional award."/>
+            <filter val="ISN Travel Awards to attend the ISN-APSN 2022 meeting in Honolulu, USA from August 28 to September 1, 2022."/>
+            <filter val="MG200Young"/>
+            <filter val="nominated for the prestigious Vice Chancellor's Research Excellence Award 2025. This nomination recognizes his outstanding contributions to research excellence."/>
+            <filter val="Prestigious Postgraduate Degree Award"/>
+            <filter val="Research award. This was a seed grant for family planning and comprehensive abortion care. Offered by the University of Michigan."/>
+            <filter val="she received a commendation award for diligent service from the management board of the hospital"/>
+            <filter val="she was inducted as a fellow of the International College of Dentists (FICD), an international recognition of her professional excellence, ethical standards, and commitment to improving oral health globally."/>
+            <filter val="she was inducted as a fellow of the Nigerian Academy of Medicine (FNAMed), joining a distinguished body of experts dedicated to advancing medical research, shaping health policy, and mentoring the next generation of leaders in medicine and health."/>
+            <filter val="Special recognition award of the World Glaucoma Association"/>
+            <filter val="Top 25 World Heart Federation (WHF) Salim Yusuf Emerging Leaders."/>
+            <filter val="Transition Award Professional Development [TAPROD] Program"/>
+            <filter val="Was awarded a Senior Fellowship in Global Health Communications Leadership for 2025 - 2026 on July 14, 2025, by the Center for Communications Leadership and Policy (CCLP)"/>
+            <filter val="Was selected as one of four recipients of this year’s Uganda Textbook Academic and Non-Fiction Authors’ Association (UTANA) Grant Scheme Award to complete and publish his book titled ‘A handbook on medicinal plants and HIV/AIDS’"/>
+            <filter val="Winner of Vice Chancellor's Transformation Award (in the team category) at the University of the Witwatersrand"/>
+            <filter val="Winning Poster"/>
+            <filter val="Won the most supportive lecturer award for the 2019-2021 academic session, from the Library, Archival and Information Studies Students Association at the University of Ibadan."/>
+            <filter val="Young Investigator Fellowship for the 19th International Congress of the International Society of Ethnopharmacology"/>
+          </mc:Fallback>
+        </mc:AlternateContent>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <hyperlinks>
     <hyperlink ref="D273" r:id="rId1" xr:uid="{8A734EB4-5543-4AA7-920A-16AF9B04BD29}"/>
     <hyperlink ref="D275" r:id="rId2" xr:uid="{48CC1384-5BA5-4E70-93B7-12C03EB7E8CB}"/>
